--- a/data/tyovuorot_2026.xlsx
+++ b/data/tyovuorot_2026.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solemofi-my.sharepoint.com/personal/pirjo_kleemola_sol_fi/Documents/Vuorolistat/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="336" documentId="8_{F7973BC1-41AE-4E6A-B0A3-B34DE794A113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C055E8F5-DCEF-4C8D-95EE-B3460B7BDE2D}"/>
+  <xr:revisionPtr revIDLastSave="624" documentId="8_{F7973BC1-41AE-4E6A-B0A3-B34DE794A113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDA9B6FA-CBEC-4E53-9C1C-753B71D7C357}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{72DDB042-8082-4351-9446-F508A0968C0B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{72DDB042-8082-4351-9446-F508A0968C0B}"/>
   </bookViews>
   <sheets>
     <sheet name="vko 2" sheetId="1" r:id="rId1"/>
+    <sheet name="vko 3" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="196">
   <si>
     <t>Ashim Acharya</t>
   </si>
@@ -413,9 +414,6 @@
     <t>Wetteri Äimäkuja 3 valkoinen lattia</t>
   </si>
   <si>
-    <t>Wetteri Äimäkuja 2 matot klo 16-</t>
-  </si>
-  <si>
     <t>Wetteri Fiksaamo kaikki tilat</t>
   </si>
   <si>
@@ -443,12 +441,6 @@
     <t>CM Kaakkuri klo 5 palvelutiski ja sen takatilat tsekkaus ja tiski</t>
   </si>
   <si>
-    <t>CM Rusko aamuvuoroa</t>
-  </si>
-  <si>
-    <t>CM Rusko aamuvuoro loppuun</t>
-  </si>
-  <si>
     <t>Kotivara kahvio ja sostliat</t>
   </si>
   <si>
@@ -495,6 +487,144 @@
   </si>
   <si>
     <t>asuntosiivouksia Eliahin kanssa</t>
+  </si>
+  <si>
+    <t>CM Rusko tiskialue klo 5-</t>
+  </si>
+  <si>
+    <t>asuntosiivouksia klo 9-</t>
+  </si>
+  <si>
+    <t>vko 3</t>
+  </si>
+  <si>
+    <t>MA 12.1</t>
+  </si>
+  <si>
+    <t>TI 13.1</t>
+  </si>
+  <si>
+    <t>KE 14.1</t>
+  </si>
+  <si>
+    <t>TO 15.1</t>
+  </si>
+  <si>
+    <t>PE 16.1</t>
+  </si>
+  <si>
+    <t>LA 17.1</t>
+  </si>
+  <si>
+    <t>SU 18.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CM Raksila liha-alue</t>
+  </si>
+  <si>
+    <t>CM Rusko Apteekki takatilojen lattioiden pesut Mirjan kanssa</t>
+  </si>
+  <si>
+    <t>CM Kaakkuri desinfiointi klo 5- (maidot etureuna)</t>
+  </si>
+  <si>
+    <t>HH Haukipudas asty klo 9-</t>
+  </si>
+  <si>
+    <t>CM Kaakkuri Leipomo Juuri, parempi lattian pesu koneellisesti Raimon kanssa</t>
+  </si>
+  <si>
+    <t>PAO rekrypäivä klo 9-11, Katja K kanssa</t>
+  </si>
+  <si>
+    <t>116 palaveri klo 9-11</t>
+  </si>
+  <si>
+    <t>CM Raksila pesuja (palvelutiski ympäristö)</t>
+  </si>
+  <si>
+    <t>Esperi Tuhkimokaarre</t>
+  </si>
+  <si>
+    <t>Esperi Tuhkimokaarre B3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esperi Tuhkimokaarre B4 </t>
+  </si>
+  <si>
+    <t>Esperi Tuhkimokaarre ja asunto B2</t>
+  </si>
+  <si>
+    <t>Caverion Vesuritie 4 kaikki tilat</t>
+  </si>
+  <si>
+    <t>Bauhaus klo 9-17</t>
+  </si>
+  <si>
+    <t>Wetteri Fiksaamo only hall max 1,5h</t>
+  </si>
+  <si>
+    <t>Wetteri Fiksaamo all max 3h</t>
+  </si>
+  <si>
+    <t>Wetteri autoliike aamuvuoro</t>
+  </si>
+  <si>
+    <t>CM Kaakkuri Leipomo Juuri lattioiden parempi pesu Nadjan kanssa</t>
+  </si>
+  <si>
+    <t>asuntosiivouksia klo 8.45-</t>
+  </si>
+  <si>
+    <t>Wetteri Äimäkuja 2 matot</t>
+  </si>
+  <si>
+    <t>CM Rusko aamuvuoroa Nadjan kanssa</t>
+  </si>
+  <si>
+    <t>CM Rusko aamuvuoro Emtiuz kanssa</t>
+  </si>
+  <si>
+    <t>SL</t>
+  </si>
+  <si>
+    <t>myös maitokylmiö</t>
+  </si>
+  <si>
+    <t>CM Rusko verkkokaupan kylmiö klo 17.30-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CM Rusko Fazer leipomo ja myymälä </t>
+  </si>
+  <si>
+    <t>Wetteri Äimäkuja 3 valkoinen lattia, myös Skoda ja Mersu matot</t>
+  </si>
+  <si>
+    <t>Wetteri Power hallin urat</t>
+  </si>
+  <si>
+    <t>Bauhaus 2.krs lattiat ja valvomo lattia pesu ja vahaus klo 14- Nadjan kanssa</t>
+  </si>
+  <si>
+    <t>Bauhaus 2.krs lattiat ja valvomo lattia pesu ja vahaus klo 14- Raimon kanssa</t>
+  </si>
+  <si>
+    <t>Bauhaus asiakas wc-tilojen lattioiden pesut ja asiakas wc-tilojen käytävän lattian pesu Pekan kanssa</t>
+  </si>
+  <si>
+    <t>Bauhaus asiakas wc-tilojen lattioiden pesut ja asiakas wc-tilojen käytävän lattian pesu Raimon kanssa</t>
+  </si>
+  <si>
+    <t>Bauhaus klo 8-n.12 (siihen saakka kun Marja-Liisa tulee)</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>Raimo</t>
+  </si>
+  <si>
+    <t>asuntosiivouksia, SOL office about klo 8.45-</t>
   </si>
 </sst>
 </file>
@@ -1856,6 +1986,12 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -2035,6 +2171,9 @@
     </xf>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
@@ -2231,10 +2370,10 @@
     <xf numFmtId="164" fontId="7" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2318,12 +2457,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2410,10 +2543,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -2766,27 +2896,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="141" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="142" t="s">
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="144" t="s">
         <v>109</v>
       </c>
-      <c r="F1" s="143"/>
-      <c r="G1" s="144"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="146"/>
       <c r="H1" s="120" t="s">
         <v>110</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="145" t="s">
+      <c r="J1" s="147" t="s">
         <v>112</v>
       </c>
-      <c r="K1" s="144"/>
+      <c r="K1" s="146"/>
       <c r="L1" s="1" t="s">
         <v>113</v>
       </c>
@@ -2798,39 +2928,41 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="146" t="s">
+      <c r="A2" s="148" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="148"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="N2" s="5"/>
     </row>
     <row r="3" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="128"/>
-      <c r="B3" s="129"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="131" t="s">
+      <c r="A3" s="130"/>
+      <c r="B3" s="131"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="132"/>
+      <c r="E3" s="133" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="132"/>
-      <c r="G3" s="132"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="134"/>
       <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="132" t="s">
+      <c r="I3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="132"/>
+      <c r="J3" s="134" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="134"/>
       <c r="L3" s="6" t="s">
         <v>1</v>
       </c>
@@ -2838,25 +2970,25 @@
       <c r="N3" s="7"/>
     </row>
     <row r="4" spans="1:14" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="133" t="s">
+      <c r="A4" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="134"/>
-      <c r="C4" s="134"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="135" t="s">
-        <v>131</v>
-      </c>
-      <c r="F4" s="136"/>
-      <c r="G4" s="137"/>
+      <c r="B4" s="136"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="137" t="s">
+        <v>130</v>
+      </c>
+      <c r="F4" s="138"/>
+      <c r="G4" s="139"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="138" t="s">
+      <c r="J4" s="140" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="138"/>
+      <c r="K4" s="140"/>
       <c r="L4" s="3" t="s">
         <v>32</v>
       </c>
@@ -2864,63 +2996,2648 @@
       <c r="N4" s="8"/>
     </row>
     <row r="5" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="150"/>
-      <c r="B5" s="151"/>
-      <c r="C5" s="151"/>
-      <c r="D5" s="151"/>
-      <c r="E5" s="153"/>
-      <c r="F5" s="154"/>
-      <c r="G5" s="154"/>
+      <c r="A5" s="152"/>
+      <c r="B5" s="153"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="156"/>
+      <c r="G5" s="156"/>
       <c r="H5" s="9"/>
       <c r="I5" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="156" t="s">
         <v>32</v>
       </c>
-      <c r="K5" s="154"/>
+      <c r="K5" s="156"/>
       <c r="L5" s="9" t="s">
         <v>32</v>
       </c>
       <c r="M5" s="9"/>
       <c r="N5" s="16"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="159" t="s">
+    <row r="6" spans="1:14" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="161" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="160"/>
-      <c r="C6" s="160"/>
-      <c r="D6" s="161"/>
-      <c r="E6" s="162"/>
-      <c r="F6" s="163"/>
-      <c r="G6" s="163"/>
+      <c r="B6" s="162"/>
+      <c r="C6" s="162"/>
+      <c r="D6" s="163"/>
+      <c r="E6" s="164"/>
+      <c r="F6" s="165"/>
+      <c r="G6" s="165"/>
       <c r="H6" s="13"/>
+      <c r="I6" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="J6" s="165"/>
+      <c r="K6" s="165"/>
+      <c r="L6" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="M6" s="12"/>
+      <c r="N6" s="14"/>
+    </row>
+    <row r="7" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="152"/>
+      <c r="B7" s="153"/>
+      <c r="C7" s="153"/>
+      <c r="D7" s="154"/>
+      <c r="E7" s="155" t="s">
+        <v>116</v>
+      </c>
+      <c r="F7" s="156"/>
+      <c r="G7" s="156"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="156" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="156"/>
+      <c r="L7" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="N7" s="16"/>
+    </row>
+    <row r="8" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="157" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="158"/>
+      <c r="C8" s="158"/>
+      <c r="D8" s="158"/>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="160"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="160" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="160"/>
+      <c r="L8" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="122"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="175" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="176"/>
+      <c r="C9" s="176"/>
+      <c r="D9" s="177"/>
+      <c r="E9" s="178"/>
+      <c r="F9" s="140"/>
+      <c r="G9" s="140"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="140"/>
+      <c r="K9" s="140"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="8"/>
+    </row>
+    <row r="10" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="179"/>
+      <c r="B10" s="180"/>
+      <c r="C10" s="180"/>
+      <c r="D10" s="180"/>
+      <c r="E10" s="181" t="s">
+        <v>149</v>
+      </c>
+      <c r="F10" s="182"/>
+      <c r="G10" s="182"/>
+      <c r="H10" s="126"/>
+      <c r="I10" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="J10" s="183" t="s">
+        <v>117</v>
+      </c>
+      <c r="K10" s="183"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="N10" s="39"/>
+    </row>
+    <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="166"/>
+      <c r="B11" s="167"/>
+      <c r="C11" s="167"/>
+      <c r="D11" s="168"/>
+      <c r="E11" s="169" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="170"/>
+      <c r="G11" s="170"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" s="156" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="156"/>
+      <c r="L11" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="M11" s="22"/>
+      <c r="N11" s="23"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="171" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="172"/>
+      <c r="C12" s="172"/>
+      <c r="D12" s="172"/>
+      <c r="E12" s="173"/>
+      <c r="F12" s="174"/>
+      <c r="G12" s="174"/>
+      <c r="H12" s="123"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="165"/>
+      <c r="K12" s="165"/>
+      <c r="L12" s="124"/>
+      <c r="M12" s="124"/>
+      <c r="N12" s="125"/>
+    </row>
+    <row r="13" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="191"/>
+      <c r="B13" s="192"/>
+      <c r="C13" s="192"/>
+      <c r="D13" s="193"/>
+      <c r="E13" s="194" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="156"/>
+      <c r="G13" s="156"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="156" t="s">
+        <v>13</v>
+      </c>
+      <c r="K13" s="156"/>
+      <c r="L13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="M13" s="25"/>
+      <c r="N13" s="26"/>
+    </row>
+    <row r="14" spans="1:14" ht="43.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="196"/>
+      <c r="C14" s="196"/>
+      <c r="D14" s="197"/>
+      <c r="E14" s="198" t="s">
+        <v>119</v>
+      </c>
+      <c r="F14" s="199"/>
+      <c r="G14" s="199"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="199" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="199"/>
+      <c r="L14" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="27"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="171" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="172"/>
+      <c r="C15" s="172"/>
+      <c r="D15" s="184"/>
+      <c r="E15" s="137"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="185"/>
+      <c r="K15" s="186"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="29"/>
+    </row>
+    <row r="16" spans="1:14" ht="43.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="187"/>
+      <c r="B16" s="188"/>
+      <c r="C16" s="188"/>
+      <c r="D16" s="189"/>
+      <c r="E16" s="133" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="134"/>
+      <c r="G16" s="134"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="128" t="s">
+        <v>3</v>
+      </c>
+      <c r="J16" s="190" t="s">
+        <v>3</v>
+      </c>
+      <c r="K16" s="190"/>
+      <c r="L16" s="128" t="s">
+        <v>3</v>
+      </c>
+      <c r="M16" s="128" t="s">
+        <v>3</v>
+      </c>
+      <c r="N16" s="30"/>
+    </row>
+    <row r="17" spans="1:14" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="161" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="162"/>
+      <c r="C17" s="162"/>
+      <c r="D17" s="162"/>
+      <c r="E17" s="151"/>
+      <c r="F17" s="140"/>
+      <c r="G17" s="140"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="204" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="139"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="8"/>
+    </row>
+    <row r="18" spans="1:14" ht="43.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="152"/>
+      <c r="B18" s="153"/>
+      <c r="C18" s="153"/>
+      <c r="D18" s="153"/>
+      <c r="E18" s="155" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="156"/>
+      <c r="G18" s="156"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="205" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="206"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N18" s="16"/>
+    </row>
+    <row r="19" spans="1:14" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="175" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="176"/>
+      <c r="C19" s="176"/>
+      <c r="D19" s="177"/>
+      <c r="E19" s="151" t="s">
+        <v>141</v>
+      </c>
+      <c r="F19" s="140"/>
+      <c r="G19" s="140"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="140" t="s">
+        <v>145</v>
+      </c>
+      <c r="K19" s="140"/>
+      <c r="L19" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="31"/>
+    </row>
+    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="200"/>
+      <c r="B20" s="201"/>
+      <c r="C20" s="201"/>
+      <c r="D20" s="202"/>
+      <c r="E20" s="203"/>
+      <c r="F20" s="183"/>
+      <c r="G20" s="183"/>
+      <c r="H20" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="I20" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" s="183" t="s">
+        <v>124</v>
+      </c>
+      <c r="K20" s="183"/>
+      <c r="L20" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="M20" s="32"/>
+      <c r="N20" s="33"/>
+    </row>
+    <row r="21" spans="1:14" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="200"/>
+      <c r="B21" s="201"/>
+      <c r="C21" s="201"/>
+      <c r="D21" s="202"/>
+      <c r="E21" s="203" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" s="183"/>
+      <c r="G21" s="183"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="J21" s="183"/>
+      <c r="K21" s="183"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="35"/>
+    </row>
+    <row r="22" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="210"/>
+      <c r="B22" s="211"/>
+      <c r="C22" s="211"/>
+      <c r="D22" s="212"/>
+      <c r="E22" s="155" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="156"/>
+      <c r="G22" s="156"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="J22" s="156" t="s">
+        <v>125</v>
+      </c>
+      <c r="K22" s="156"/>
+      <c r="L22" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N22" s="11"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="175" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="176"/>
+      <c r="C23" s="176"/>
+      <c r="D23" s="177"/>
+      <c r="E23" s="164" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="165"/>
+      <c r="G23" s="165"/>
+      <c r="H23" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" s="207"/>
+      <c r="L23" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="N23" s="37" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="208"/>
+      <c r="B24" s="209"/>
+      <c r="C24" s="209"/>
+      <c r="D24" s="209"/>
+      <c r="E24" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="134"/>
+      <c r="G24" s="134"/>
+      <c r="H24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" s="134" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" s="134"/>
+      <c r="L24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N24" s="38" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="175" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="176"/>
+      <c r="C25" s="176"/>
+      <c r="D25" s="177"/>
+      <c r="E25" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" s="140"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J25" s="204" t="s">
+        <v>35</v>
+      </c>
+      <c r="K25" s="139"/>
+      <c r="L25" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M25" s="3"/>
+      <c r="N25" s="8"/>
+    </row>
+    <row r="26" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="179"/>
+      <c r="B26" s="180"/>
+      <c r="C26" s="180"/>
+      <c r="D26" s="180"/>
+      <c r="E26" s="221" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="222"/>
+      <c r="G26" s="223"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="J26" s="224" t="s">
+        <v>36</v>
+      </c>
+      <c r="K26" s="223"/>
+      <c r="L26" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="M26" s="32"/>
+      <c r="N26" s="39"/>
+    </row>
+    <row r="27" spans="1:14" ht="43.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="152"/>
+      <c r="B27" s="153"/>
+      <c r="C27" s="153"/>
+      <c r="D27" s="153"/>
+      <c r="E27" s="213" t="s">
+        <v>127</v>
+      </c>
+      <c r="F27" s="214"/>
+      <c r="G27" s="206"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="J27" s="205" t="s">
+        <v>127</v>
+      </c>
+      <c r="K27" s="206"/>
+      <c r="L27" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M27" s="9"/>
+      <c r="N27" s="16"/>
+    </row>
+    <row r="28" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="215" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="216"/>
+      <c r="C28" s="216"/>
+      <c r="D28" s="216"/>
+      <c r="E28" s="217" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" s="218"/>
+      <c r="G28" s="219"/>
+      <c r="H28" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="I28" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="J28" s="220"/>
+      <c r="K28" s="219"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="40"/>
+    </row>
+    <row r="29" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="187" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="188"/>
+      <c r="C29" s="188"/>
+      <c r="D29" s="189"/>
+      <c r="E29" s="229"/>
+      <c r="F29" s="230"/>
+      <c r="G29" s="231"/>
+      <c r="H29" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="I29" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="J29" s="232" t="s">
+        <v>39</v>
+      </c>
+      <c r="K29" s="233"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="20"/>
+    </row>
+    <row r="30" spans="1:14" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="191" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="192"/>
+      <c r="C30" s="192"/>
+      <c r="D30" s="193"/>
+      <c r="E30" s="234"/>
+      <c r="F30" s="235"/>
+      <c r="G30" s="235"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="160"/>
+      <c r="K30" s="160"/>
+      <c r="L30" s="42"/>
+      <c r="M30" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="N30" s="45"/>
+    </row>
+    <row r="31" spans="1:14" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="171" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="172"/>
+      <c r="C31" s="172"/>
+      <c r="D31" s="172"/>
+      <c r="E31" s="225"/>
+      <c r="F31" s="226"/>
+      <c r="G31" s="226"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="204" t="s">
+        <v>178</v>
+      </c>
+      <c r="K31" s="139"/>
+      <c r="L31" s="47"/>
+      <c r="M31" s="48"/>
+      <c r="N31" s="49"/>
+    </row>
+    <row r="32" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="187"/>
+      <c r="B32" s="188"/>
+      <c r="C32" s="188"/>
+      <c r="D32" s="188"/>
+      <c r="E32" s="227"/>
+      <c r="F32" s="228"/>
+      <c r="G32" s="228"/>
+      <c r="H32" s="51"/>
+      <c r="I32" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="J32" s="205"/>
+      <c r="K32" s="206"/>
+      <c r="L32" s="51"/>
+      <c r="M32" s="50"/>
+      <c r="N32" s="52"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="175" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="176"/>
+      <c r="C33" s="176"/>
+      <c r="D33" s="177"/>
+      <c r="E33" s="151"/>
+      <c r="F33" s="140"/>
+      <c r="G33" s="140"/>
+      <c r="H33" s="47"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="243"/>
+      <c r="K33" s="243"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="49"/>
+    </row>
+    <row r="34" spans="1:14" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="152"/>
+      <c r="B34" s="153"/>
+      <c r="C34" s="153"/>
+      <c r="D34" s="153"/>
+      <c r="E34" s="169" t="s">
+        <v>5</v>
+      </c>
+      <c r="F34" s="170"/>
+      <c r="G34" s="170"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="170"/>
+      <c r="K34" s="244"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="N34" s="54"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="135" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="136"/>
+      <c r="C35" s="136"/>
+      <c r="D35" s="136"/>
+      <c r="E35" s="164"/>
+      <c r="F35" s="165"/>
+      <c r="G35" s="165"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="236"/>
+      <c r="K35" s="237"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="56"/>
+      <c r="N35" s="57"/>
+    </row>
+    <row r="36" spans="1:14" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="152"/>
+      <c r="B36" s="153"/>
+      <c r="C36" s="153"/>
+      <c r="D36" s="153"/>
+      <c r="E36" s="238"/>
+      <c r="F36" s="239"/>
+      <c r="G36" s="240"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J36" s="241"/>
+      <c r="K36" s="242"/>
+      <c r="L36" s="50"/>
+      <c r="M36" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="N36" s="127"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="245" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="246"/>
+      <c r="C37" s="246"/>
+      <c r="D37" s="247"/>
+      <c r="E37" s="151"/>
+      <c r="F37" s="140"/>
+      <c r="G37" s="140"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="185"/>
+      <c r="K37" s="186"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="59"/>
+    </row>
+    <row r="38" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="248"/>
+      <c r="B38" s="249"/>
+      <c r="C38" s="249"/>
+      <c r="D38" s="250"/>
+      <c r="E38" s="251" t="s">
+        <v>47</v>
+      </c>
+      <c r="F38" s="252"/>
+      <c r="G38" s="253"/>
+      <c r="H38" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="I38" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="J38" s="254" t="s">
+        <v>47</v>
+      </c>
+      <c r="K38" s="254"/>
+      <c r="L38" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="M38" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="N38" s="61" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="175" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="176"/>
+      <c r="C39" s="176"/>
+      <c r="D39" s="177"/>
+      <c r="E39" s="151"/>
+      <c r="F39" s="140"/>
+      <c r="G39" s="140"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="140"/>
+      <c r="K39" s="140"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="62"/>
+      <c r="N39" s="31"/>
+    </row>
+    <row r="40" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="130"/>
+      <c r="B40" s="131"/>
+      <c r="C40" s="131"/>
+      <c r="D40" s="132"/>
+      <c r="E40" s="155" t="s">
+        <v>129</v>
+      </c>
+      <c r="F40" s="156"/>
+      <c r="G40" s="156"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="J40" s="156" t="s">
+        <v>19</v>
+      </c>
+      <c r="K40" s="156"/>
+      <c r="L40" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="M40" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="16"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="175" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="176"/>
+      <c r="C41" s="176"/>
+      <c r="D41" s="177"/>
+      <c r="E41" s="173" t="s">
+        <v>32</v>
+      </c>
+      <c r="F41" s="165"/>
+      <c r="G41" s="165"/>
+      <c r="H41" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J41" s="165" t="s">
+        <v>32</v>
+      </c>
+      <c r="K41" s="165"/>
+      <c r="L41" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M41" s="12"/>
+      <c r="N41" s="14"/>
+    </row>
+    <row r="42" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="210"/>
+      <c r="B42" s="211"/>
+      <c r="C42" s="211"/>
+      <c r="D42" s="212"/>
+      <c r="E42" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" s="134"/>
+      <c r="G42" s="134"/>
+      <c r="H42" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J42" s="134" t="s">
+        <v>32</v>
+      </c>
+      <c r="K42" s="134"/>
+      <c r="L42" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M42" s="63"/>
+      <c r="N42" s="30"/>
+    </row>
+    <row r="43" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="175" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" s="176"/>
+      <c r="C43" s="176"/>
+      <c r="D43" s="177"/>
+      <c r="E43" s="151" t="s">
+        <v>142</v>
+      </c>
+      <c r="F43" s="140"/>
+      <c r="G43" s="140"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J43" s="140" t="s">
+        <v>117</v>
+      </c>
+      <c r="K43" s="140"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="64"/>
+    </row>
+    <row r="44" spans="1:14" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="200"/>
+      <c r="B44" s="201"/>
+      <c r="C44" s="201"/>
+      <c r="D44" s="202"/>
+      <c r="E44" s="203"/>
+      <c r="F44" s="183"/>
+      <c r="G44" s="183"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="32"/>
+      <c r="J44" s="183" t="s">
+        <v>55</v>
+      </c>
+      <c r="K44" s="183"/>
+      <c r="L44" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="M44" s="32"/>
+      <c r="N44" s="33"/>
+    </row>
+    <row r="45" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="210"/>
+      <c r="B45" s="211"/>
+      <c r="C45" s="211"/>
+      <c r="D45" s="212"/>
+      <c r="E45" s="155"/>
+      <c r="F45" s="156"/>
+      <c r="G45" s="156"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="156"/>
+      <c r="K45" s="156"/>
+      <c r="L45" s="9"/>
+      <c r="M45" s="65"/>
+      <c r="N45" s="11"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="175" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" s="176"/>
+      <c r="C46" s="176"/>
+      <c r="D46" s="261"/>
+      <c r="E46" s="164"/>
+      <c r="F46" s="165"/>
+      <c r="G46" s="165"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="J46" s="262" t="s">
+        <v>32</v>
+      </c>
+      <c r="K46" s="263"/>
+      <c r="L46" s="12"/>
+      <c r="M46" s="66"/>
+      <c r="N46" s="67"/>
+    </row>
+    <row r="47" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="248"/>
+      <c r="B47" s="249"/>
+      <c r="C47" s="249"/>
+      <c r="D47" s="250"/>
+      <c r="E47" s="255"/>
+      <c r="F47" s="256"/>
+      <c r="G47" s="257"/>
+      <c r="H47" s="68"/>
+      <c r="I47" s="68"/>
+      <c r="J47" s="258" t="s">
+        <v>32</v>
+      </c>
+      <c r="K47" s="259"/>
+      <c r="L47" s="68"/>
+      <c r="M47" s="69"/>
+      <c r="N47" s="70"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48" s="171" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="172"/>
+      <c r="C48" s="172"/>
+      <c r="D48" s="172"/>
+      <c r="E48" s="151"/>
+      <c r="F48" s="140"/>
+      <c r="G48" s="140"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="260"/>
+      <c r="K48" s="260"/>
+      <c r="L48" s="28"/>
+      <c r="M48" s="71"/>
+      <c r="N48" s="29"/>
+    </row>
+    <row r="49" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="267"/>
+      <c r="B49" s="268"/>
+      <c r="C49" s="268"/>
+      <c r="D49" s="268"/>
+      <c r="E49" s="155"/>
+      <c r="F49" s="156"/>
+      <c r="G49" s="156"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="J49" s="156" t="s">
+        <v>5</v>
+      </c>
+      <c r="K49" s="156"/>
+      <c r="L49" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="M49" s="9"/>
+      <c r="N49" s="16"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" s="135" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" s="136"/>
+      <c r="C50" s="136"/>
+      <c r="D50" s="136"/>
+      <c r="E50" s="269"/>
+      <c r="F50" s="270"/>
+      <c r="G50" s="263"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="12"/>
+      <c r="J50" s="207"/>
+      <c r="K50" s="207"/>
+      <c r="L50" s="12"/>
+      <c r="M50" s="12"/>
+      <c r="N50" s="72"/>
+    </row>
+    <row r="51" spans="1:14" ht="55.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="264"/>
+      <c r="B51" s="265"/>
+      <c r="C51" s="265"/>
+      <c r="D51" s="265"/>
+      <c r="E51" s="155" t="s">
+        <v>131</v>
+      </c>
+      <c r="F51" s="156"/>
+      <c r="G51" s="156"/>
+      <c r="H51" s="9"/>
+      <c r="I51" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="J51" s="156" t="s">
+        <v>50</v>
+      </c>
+      <c r="K51" s="156"/>
+      <c r="L51" s="9"/>
+      <c r="M51" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="N51" s="73"/>
+    </row>
+    <row r="52" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="245" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="246"/>
+      <c r="C52" s="246"/>
+      <c r="D52" s="266"/>
+      <c r="E52" s="137" t="s">
+        <v>147</v>
+      </c>
+      <c r="F52" s="138"/>
+      <c r="G52" s="139"/>
+      <c r="H52" s="74"/>
+      <c r="I52" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="J52" s="207"/>
+      <c r="K52" s="207"/>
+      <c r="L52" s="12"/>
+      <c r="M52" s="36"/>
+      <c r="N52" s="75"/>
+    </row>
+    <row r="53" spans="1:14" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="274"/>
+      <c r="B53" s="275"/>
+      <c r="C53" s="275"/>
+      <c r="D53" s="275"/>
+      <c r="E53" s="276" t="s">
+        <v>120</v>
+      </c>
+      <c r="F53" s="277"/>
+      <c r="G53" s="277"/>
+      <c r="H53" s="76"/>
+      <c r="I53" s="76"/>
+      <c r="J53" s="277" t="s">
+        <v>18</v>
+      </c>
+      <c r="K53" s="277"/>
+      <c r="L53" s="76" t="s">
+        <v>18</v>
+      </c>
+      <c r="M53" s="76" t="s">
+        <v>21</v>
+      </c>
+      <c r="N53" s="77"/>
+    </row>
+    <row r="54" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A54" s="278" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54" s="279"/>
+      <c r="C54" s="279"/>
+      <c r="D54" s="280"/>
+      <c r="E54" s="151" t="s">
+        <v>143</v>
+      </c>
+      <c r="F54" s="140"/>
+      <c r="G54" s="140"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J54" s="140" t="s">
+        <v>117</v>
+      </c>
+      <c r="K54" s="140"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="49"/>
+    </row>
+    <row r="55" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="271"/>
+      <c r="B55" s="272"/>
+      <c r="C55" s="272"/>
+      <c r="D55" s="273"/>
+      <c r="E55" s="155"/>
+      <c r="F55" s="156"/>
+      <c r="G55" s="156"/>
+      <c r="H55" s="21"/>
+      <c r="I55" s="50"/>
+      <c r="J55" s="156"/>
+      <c r="K55" s="156"/>
+      <c r="L55" s="9"/>
+      <c r="M55" s="51"/>
+      <c r="N55" s="52"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" s="245" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" s="246"/>
+      <c r="C56" s="246"/>
+      <c r="D56" s="266"/>
+      <c r="E56" s="164" t="s">
+        <v>65</v>
+      </c>
+      <c r="F56" s="165"/>
+      <c r="G56" s="165"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="J56" s="262" t="s">
+        <v>65</v>
+      </c>
+      <c r="K56" s="263"/>
+      <c r="L56" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="M56" s="12"/>
+      <c r="N56" s="78"/>
+    </row>
+    <row r="57" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="210"/>
+      <c r="B57" s="211"/>
+      <c r="C57" s="211"/>
+      <c r="D57" s="212"/>
+      <c r="E57" s="133"/>
+      <c r="F57" s="134"/>
+      <c r="G57" s="134"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="156"/>
+      <c r="K57" s="156"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="63"/>
+      <c r="N57" s="30"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58" s="175" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" s="176"/>
+      <c r="C58" s="176"/>
+      <c r="D58" s="177"/>
+      <c r="E58" s="151" t="s">
+        <v>26</v>
+      </c>
+      <c r="F58" s="140"/>
+      <c r="G58" s="140"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J58" s="140" t="s">
+        <v>26</v>
+      </c>
+      <c r="K58" s="140"/>
+      <c r="L58" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M58" s="3"/>
+      <c r="N58" s="31"/>
+    </row>
+    <row r="59" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="210"/>
+      <c r="B59" s="211"/>
+      <c r="C59" s="211"/>
+      <c r="D59" s="212"/>
+      <c r="E59" s="133"/>
+      <c r="F59" s="134"/>
+      <c r="G59" s="134"/>
+      <c r="H59" s="68"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="134"/>
+      <c r="K59" s="134"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
+      <c r="N59" s="30"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60" s="175" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="176"/>
+      <c r="C60" s="176"/>
+      <c r="D60" s="177"/>
+      <c r="E60" s="281" t="s">
+        <v>27</v>
+      </c>
+      <c r="F60" s="260"/>
+      <c r="G60" s="260"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J60" s="260" t="s">
+        <v>68</v>
+      </c>
+      <c r="K60" s="260"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="79"/>
+      <c r="N60" s="59"/>
+    </row>
+    <row r="61" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="200"/>
+      <c r="B61" s="201"/>
+      <c r="C61" s="201"/>
+      <c r="D61" s="202"/>
+      <c r="E61" s="203"/>
+      <c r="F61" s="183"/>
+      <c r="G61" s="183"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="J61" s="183"/>
+      <c r="K61" s="183"/>
+      <c r="L61" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="M61" s="32"/>
+      <c r="N61" s="33"/>
+    </row>
+    <row r="62" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="248"/>
+      <c r="B62" s="249"/>
+      <c r="C62" s="249"/>
+      <c r="D62" s="287"/>
+      <c r="E62" s="155"/>
+      <c r="F62" s="156"/>
+      <c r="G62" s="156"/>
+      <c r="H62" s="10"/>
+      <c r="I62" s="10"/>
+      <c r="J62" s="288"/>
+      <c r="K62" s="288"/>
+      <c r="L62" s="10"/>
+      <c r="M62" s="80"/>
+      <c r="N62" s="81"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="175" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="176"/>
+      <c r="C63" s="176"/>
+      <c r="D63" s="261"/>
+      <c r="E63" s="282" t="s">
+        <v>47</v>
+      </c>
+      <c r="F63" s="283"/>
+      <c r="G63" s="283"/>
+      <c r="H63" s="82" t="s">
+        <v>47</v>
+      </c>
+      <c r="I63" s="82" t="s">
+        <v>47</v>
+      </c>
+      <c r="J63" s="284" t="s">
+        <v>47</v>
+      </c>
+      <c r="K63" s="284"/>
+      <c r="L63" s="84" t="s">
+        <v>47</v>
+      </c>
+      <c r="M63" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="N63" s="85" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="210"/>
+      <c r="B64" s="211"/>
+      <c r="C64" s="211"/>
+      <c r="D64" s="285"/>
+      <c r="E64" s="133"/>
+      <c r="F64" s="134"/>
+      <c r="G64" s="134"/>
+      <c r="H64" s="86"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="286"/>
+      <c r="K64" s="286"/>
+      <c r="L64" s="87"/>
+      <c r="M64" s="87"/>
+      <c r="N64" s="70"/>
+    </row>
+    <row r="65" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A65" s="135" t="s">
+        <v>70</v>
+      </c>
+      <c r="B65" s="136"/>
+      <c r="C65" s="136"/>
+      <c r="D65" s="136"/>
+      <c r="E65" s="137"/>
+      <c r="F65" s="138"/>
+      <c r="G65" s="139"/>
+      <c r="H65" s="28"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="185"/>
+      <c r="K65" s="186"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="N65" s="88"/>
+    </row>
+    <row r="66" spans="1:14" ht="34.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="264"/>
+      <c r="B66" s="265"/>
+      <c r="C66" s="265"/>
+      <c r="D66" s="265"/>
+      <c r="E66" s="213" t="s">
+        <v>74</v>
+      </c>
+      <c r="F66" s="214"/>
+      <c r="G66" s="206"/>
+      <c r="H66" s="80"/>
+      <c r="I66" s="9"/>
+      <c r="J66" s="258"/>
+      <c r="K66" s="259"/>
+      <c r="L66" s="89"/>
+      <c r="M66" s="89"/>
+      <c r="N66" s="90"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A67" s="245" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" s="246"/>
+      <c r="C67" s="246"/>
+      <c r="D67" s="266"/>
+      <c r="E67" s="151"/>
+      <c r="F67" s="140"/>
+      <c r="G67" s="140"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="204"/>
+      <c r="K67" s="139"/>
+      <c r="L67" s="46"/>
+      <c r="M67" s="46"/>
+      <c r="N67" s="8"/>
+    </row>
+    <row r="68" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="210"/>
+      <c r="B68" s="211"/>
+      <c r="C68" s="211"/>
+      <c r="D68" s="212"/>
+      <c r="E68" s="289" t="s">
+        <v>47</v>
+      </c>
+      <c r="F68" s="290"/>
+      <c r="G68" s="290"/>
+      <c r="H68" s="91" t="s">
+        <v>47</v>
+      </c>
+      <c r="I68" s="91" t="s">
+        <v>47</v>
+      </c>
+      <c r="J68" s="291" t="s">
+        <v>47</v>
+      </c>
+      <c r="K68" s="292"/>
+      <c r="L68" s="92" t="s">
+        <v>47</v>
+      </c>
+      <c r="M68" s="92" t="s">
+        <v>47</v>
+      </c>
+      <c r="N68" s="93" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A69" s="135" t="s">
+        <v>72</v>
+      </c>
+      <c r="B69" s="136"/>
+      <c r="C69" s="136"/>
+      <c r="D69" s="136"/>
+      <c r="E69" s="151" t="s">
+        <v>23</v>
+      </c>
+      <c r="F69" s="140"/>
+      <c r="G69" s="140"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J69" s="140"/>
+      <c r="K69" s="140"/>
+      <c r="L69" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M69" s="3"/>
+      <c r="N69" s="8"/>
+    </row>
+    <row r="70" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="294"/>
+      <c r="B70" s="295"/>
+      <c r="C70" s="295"/>
+      <c r="D70" s="295"/>
+      <c r="E70" s="155" t="s">
+        <v>24</v>
+      </c>
+      <c r="F70" s="156"/>
+      <c r="G70" s="156"/>
+      <c r="H70" s="9"/>
+      <c r="I70" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J70" s="170" t="s">
+        <v>73</v>
+      </c>
+      <c r="K70" s="170"/>
+      <c r="L70" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M70" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="N70" s="16"/>
+    </row>
+    <row r="71" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A71" s="135" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71" s="136"/>
+      <c r="C71" s="136"/>
+      <c r="D71" s="136"/>
+      <c r="E71" s="293" t="s">
+        <v>76</v>
+      </c>
+      <c r="F71" s="207"/>
+      <c r="G71" s="207"/>
+      <c r="H71" s="12"/>
+      <c r="I71" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="J71" s="165" t="s">
+        <v>76</v>
+      </c>
+      <c r="K71" s="165"/>
+      <c r="L71" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="M71" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="N71" s="94"/>
+    </row>
+    <row r="72" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="294"/>
+      <c r="B72" s="295"/>
+      <c r="C72" s="295"/>
+      <c r="D72" s="295"/>
+      <c r="E72" s="133"/>
+      <c r="F72" s="134"/>
+      <c r="G72" s="134"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="134"/>
+      <c r="K72" s="134"/>
+      <c r="L72" s="6"/>
+      <c r="M72" s="6"/>
+      <c r="N72" s="38"/>
+    </row>
+    <row r="73" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="215" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73" s="216"/>
+      <c r="C73" s="216"/>
+      <c r="D73" s="296"/>
+      <c r="E73" s="297" t="s">
+        <v>39</v>
+      </c>
+      <c r="F73" s="298"/>
+      <c r="G73" s="299"/>
+      <c r="H73" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="I73" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="J73" s="300" t="s">
+        <v>39</v>
+      </c>
+      <c r="K73" s="299"/>
+      <c r="L73" s="44"/>
+      <c r="M73" s="44"/>
+      <c r="N73" s="95"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74" s="161" t="s">
+        <v>78</v>
+      </c>
+      <c r="B74" s="162"/>
+      <c r="C74" s="162"/>
+      <c r="D74" s="162"/>
+      <c r="E74" s="151" t="s">
+        <v>79</v>
+      </c>
+      <c r="F74" s="140"/>
+      <c r="G74" s="140"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J74" s="140" t="s">
+        <v>79</v>
+      </c>
+      <c r="K74" s="140"/>
+      <c r="L74" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="M74" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="N74" s="31"/>
+    </row>
+    <row r="75" spans="1:14" ht="57.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="264"/>
+      <c r="B75" s="265"/>
+      <c r="C75" s="265"/>
+      <c r="D75" s="265"/>
+      <c r="E75" s="155" t="s">
+        <v>102</v>
+      </c>
+      <c r="F75" s="156"/>
+      <c r="G75" s="156"/>
+      <c r="H75" s="9"/>
+      <c r="I75" s="9"/>
+      <c r="J75" s="156"/>
+      <c r="K75" s="156"/>
+      <c r="L75" s="9"/>
+      <c r="M75" s="9"/>
+      <c r="N75" s="11"/>
+    </row>
+    <row r="76" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A76" s="245" t="s">
+        <v>80</v>
+      </c>
+      <c r="B76" s="246"/>
+      <c r="C76" s="246"/>
+      <c r="D76" s="266"/>
+      <c r="E76" s="151" t="s">
+        <v>81</v>
+      </c>
+      <c r="F76" s="140"/>
+      <c r="G76" s="140"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J76" s="140" t="s">
+        <v>117</v>
+      </c>
+      <c r="K76" s="140"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="96"/>
+    </row>
+    <row r="77" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="248"/>
+      <c r="B77" s="249"/>
+      <c r="C77" s="249"/>
+      <c r="D77" s="287"/>
+      <c r="E77" s="155"/>
+      <c r="F77" s="156"/>
+      <c r="G77" s="156"/>
+      <c r="H77" s="9"/>
+      <c r="I77" s="97"/>
+      <c r="J77" s="156"/>
+      <c r="K77" s="156"/>
+      <c r="L77" s="9"/>
+      <c r="M77" s="9"/>
+      <c r="N77" s="98"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A78" s="135" t="s">
+        <v>82</v>
+      </c>
+      <c r="B78" s="136"/>
+      <c r="C78" s="136"/>
+      <c r="D78" s="136"/>
+      <c r="E78" s="269"/>
+      <c r="F78" s="270"/>
+      <c r="G78" s="263"/>
+      <c r="H78" s="12"/>
+      <c r="I78" s="12"/>
+      <c r="J78" s="262"/>
+      <c r="K78" s="263"/>
+      <c r="L78" s="12"/>
+      <c r="M78" s="12"/>
+      <c r="N78" s="14"/>
+    </row>
+    <row r="79" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="294"/>
+      <c r="B79" s="295"/>
+      <c r="C79" s="295"/>
+      <c r="D79" s="295"/>
+      <c r="E79" s="255"/>
+      <c r="F79" s="256"/>
+      <c r="G79" s="257"/>
+      <c r="H79" s="68"/>
+      <c r="I79" s="68"/>
+      <c r="J79" s="156"/>
+      <c r="K79" s="156"/>
+      <c r="L79" s="68"/>
+      <c r="M79" s="69"/>
+      <c r="N79" s="70"/>
+    </row>
+    <row r="80" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A80" s="175" t="s">
+        <v>83</v>
+      </c>
+      <c r="B80" s="176"/>
+      <c r="C80" s="176"/>
+      <c r="D80" s="177"/>
+      <c r="E80" s="151" t="s">
+        <v>49</v>
+      </c>
+      <c r="F80" s="140"/>
+      <c r="G80" s="140"/>
+      <c r="H80" s="99"/>
+      <c r="I80" s="99" t="s">
+        <v>49</v>
+      </c>
+      <c r="J80" s="301" t="s">
+        <v>49</v>
+      </c>
+      <c r="K80" s="301"/>
+      <c r="L80" s="99" t="s">
+        <v>49</v>
+      </c>
+      <c r="M80" s="99" t="s">
+        <v>84</v>
+      </c>
+      <c r="N80" s="64"/>
+    </row>
+    <row r="81" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="210"/>
+      <c r="B81" s="211"/>
+      <c r="C81" s="211"/>
+      <c r="D81" s="212"/>
+      <c r="E81" s="306"/>
+      <c r="F81" s="307"/>
+      <c r="G81" s="307"/>
+      <c r="H81" s="69"/>
+      <c r="I81" s="69"/>
+      <c r="J81" s="307"/>
+      <c r="K81" s="307"/>
+      <c r="L81" s="69"/>
+      <c r="M81" s="69"/>
+      <c r="N81" s="70"/>
+    </row>
+    <row r="82" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A82" s="175" t="s">
+        <v>85</v>
+      </c>
+      <c r="B82" s="176"/>
+      <c r="C82" s="176"/>
+      <c r="D82" s="177"/>
+      <c r="E82" s="151" t="s">
+        <v>86</v>
+      </c>
+      <c r="F82" s="140"/>
+      <c r="G82" s="140"/>
+      <c r="H82" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J82" s="140" t="s">
+        <v>86</v>
+      </c>
+      <c r="K82" s="140"/>
+      <c r="L82" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="M82" s="3"/>
+      <c r="N82" s="100"/>
+    </row>
+    <row r="83" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="210"/>
+      <c r="B83" s="211"/>
+      <c r="C83" s="211"/>
+      <c r="D83" s="212"/>
+      <c r="E83" s="302" t="s">
+        <v>87</v>
+      </c>
+      <c r="F83" s="286"/>
+      <c r="G83" s="286"/>
+      <c r="H83" s="68"/>
+      <c r="I83" s="68" t="s">
+        <v>87</v>
+      </c>
+      <c r="J83" s="134" t="s">
+        <v>87</v>
+      </c>
+      <c r="K83" s="134"/>
+      <c r="L83" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="M83" s="6"/>
+      <c r="N83" s="70"/>
+    </row>
+    <row r="84" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="215" t="s">
+        <v>88</v>
+      </c>
+      <c r="B84" s="216"/>
+      <c r="C84" s="216"/>
+      <c r="D84" s="296"/>
+      <c r="E84" s="303" t="s">
+        <v>39</v>
+      </c>
+      <c r="F84" s="304"/>
+      <c r="G84" s="305"/>
+      <c r="H84" s="101" t="s">
+        <v>39</v>
+      </c>
+      <c r="I84" s="101"/>
+      <c r="J84" s="220" t="s">
+        <v>135</v>
+      </c>
+      <c r="K84" s="219"/>
+      <c r="L84" s="17"/>
+      <c r="M84" s="17"/>
+      <c r="N84" s="102"/>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A85" s="245" t="s">
+        <v>90</v>
+      </c>
+      <c r="B85" s="246"/>
+      <c r="C85" s="246"/>
+      <c r="D85" s="266"/>
+      <c r="E85" s="293" t="s">
+        <v>91</v>
+      </c>
+      <c r="F85" s="207"/>
+      <c r="G85" s="207"/>
+      <c r="H85" s="13"/>
+      <c r="I85" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="J85" s="207" t="s">
+        <v>91</v>
+      </c>
+      <c r="K85" s="207"/>
+      <c r="L85" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="M85" s="103"/>
+      <c r="N85" s="104"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A86" s="200"/>
+      <c r="B86" s="201"/>
+      <c r="C86" s="201"/>
+      <c r="D86" s="202"/>
+      <c r="E86" s="203" t="s">
+        <v>92</v>
+      </c>
+      <c r="F86" s="183"/>
+      <c r="G86" s="183"/>
+      <c r="H86" s="105"/>
+      <c r="I86" s="105" t="s">
+        <v>92</v>
+      </c>
+      <c r="J86" s="183" t="s">
+        <v>95</v>
+      </c>
+      <c r="K86" s="183"/>
+      <c r="L86" s="105" t="s">
+        <v>92</v>
+      </c>
+      <c r="M86" s="6"/>
+      <c r="N86" s="106"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A87" s="200"/>
+      <c r="B87" s="201"/>
+      <c r="C87" s="201"/>
+      <c r="D87" s="202"/>
+      <c r="E87" s="308" t="s">
+        <v>93</v>
+      </c>
+      <c r="F87" s="309"/>
+      <c r="G87" s="309"/>
+      <c r="H87" s="34"/>
+      <c r="I87" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="J87" s="183"/>
+      <c r="K87" s="183"/>
+      <c r="L87" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="M87" s="107"/>
+      <c r="N87" s="108"/>
+    </row>
+    <row r="88" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="210"/>
+      <c r="B88" s="211"/>
+      <c r="C88" s="211"/>
+      <c r="D88" s="212"/>
+      <c r="E88" s="302" t="s">
+        <v>136</v>
+      </c>
+      <c r="F88" s="286"/>
+      <c r="G88" s="286"/>
+      <c r="H88" s="69"/>
+      <c r="I88" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="J88" s="134"/>
+      <c r="K88" s="134"/>
+      <c r="L88" s="87" t="s">
+        <v>94</v>
+      </c>
+      <c r="M88" s="87"/>
+      <c r="N88" s="70"/>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A89" s="135" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89" s="136"/>
+      <c r="C89" s="136"/>
+      <c r="D89" s="136"/>
+      <c r="E89" s="151"/>
+      <c r="F89" s="140"/>
+      <c r="G89" s="140"/>
+      <c r="H89" s="71"/>
+      <c r="I89" s="3"/>
+      <c r="J89" s="140"/>
+      <c r="K89" s="140"/>
+      <c r="L89" s="28"/>
+      <c r="M89" s="28"/>
+      <c r="N89" s="29"/>
+    </row>
+    <row r="90" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="264"/>
+      <c r="B90" s="265"/>
+      <c r="C90" s="265"/>
+      <c r="D90" s="265"/>
+      <c r="E90" s="155"/>
+      <c r="F90" s="156"/>
+      <c r="G90" s="156"/>
+      <c r="H90" s="25"/>
+      <c r="I90" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J90" s="156"/>
+      <c r="K90" s="156"/>
+      <c r="L90" s="21"/>
+      <c r="M90" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="N90" s="109"/>
+    </row>
+    <row r="91" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="157" t="s">
+        <v>97</v>
+      </c>
+      <c r="B91" s="158"/>
+      <c r="C91" s="158"/>
+      <c r="D91" s="158"/>
+      <c r="E91" s="310" t="s">
+        <v>39</v>
+      </c>
+      <c r="F91" s="311"/>
+      <c r="G91" s="233"/>
+      <c r="H91" s="110" t="s">
+        <v>39</v>
+      </c>
+      <c r="I91" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="J91" s="232" t="s">
+        <v>39</v>
+      </c>
+      <c r="K91" s="233"/>
+      <c r="L91" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="M91" s="19"/>
+      <c r="N91" s="111"/>
+    </row>
+    <row r="92" spans="1:14" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="135" t="s">
+        <v>98</v>
+      </c>
+      <c r="B92" s="136"/>
+      <c r="C92" s="136"/>
+      <c r="D92" s="136"/>
+      <c r="E92" s="137" t="s">
+        <v>99</v>
+      </c>
+      <c r="F92" s="138"/>
+      <c r="G92" s="139"/>
+      <c r="H92" s="62"/>
+      <c r="I92" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="J92" s="204" t="s">
+        <v>28</v>
+      </c>
+      <c r="K92" s="139"/>
+      <c r="L92" s="3"/>
+      <c r="M92" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="N92" s="112"/>
+    </row>
+    <row r="93" spans="1:14" ht="52.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="152"/>
+      <c r="B93" s="153"/>
+      <c r="C93" s="153"/>
+      <c r="D93" s="153"/>
+      <c r="E93" s="213" t="s">
+        <v>100</v>
+      </c>
+      <c r="F93" s="214"/>
+      <c r="G93" s="206"/>
+      <c r="H93" s="97"/>
+      <c r="I93" s="10"/>
+      <c r="J93" s="156"/>
+      <c r="K93" s="156"/>
+      <c r="L93" s="9"/>
+      <c r="M93" s="9"/>
+      <c r="N93" s="109"/>
+    </row>
+    <row r="94" spans="1:14" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="245" t="s">
+        <v>101</v>
+      </c>
+      <c r="B94" s="246"/>
+      <c r="C94" s="246"/>
+      <c r="D94" s="266"/>
+      <c r="E94" s="151" t="s">
+        <v>144</v>
+      </c>
+      <c r="F94" s="140"/>
+      <c r="G94" s="140"/>
+      <c r="H94" s="24"/>
+      <c r="I94" s="3"/>
+      <c r="J94" s="140"/>
+      <c r="K94" s="140"/>
+      <c r="L94" s="3"/>
+      <c r="M94" s="3"/>
+      <c r="N94" s="59"/>
+    </row>
+    <row r="95" spans="1:14" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="200"/>
+      <c r="B95" s="201"/>
+      <c r="C95" s="201"/>
+      <c r="D95" s="202"/>
+      <c r="E95" s="203" t="s">
+        <v>140</v>
+      </c>
+      <c r="F95" s="183"/>
+      <c r="G95" s="183"/>
+      <c r="H95" s="32"/>
+      <c r="I95" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="J95" s="183" t="s">
+        <v>102</v>
+      </c>
+      <c r="K95" s="183"/>
+      <c r="L95" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="M95" s="32"/>
+      <c r="N95" s="33"/>
+    </row>
+    <row r="96" spans="1:14" ht="67.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="248"/>
+      <c r="B96" s="249"/>
+      <c r="C96" s="249"/>
+      <c r="D96" s="287"/>
+      <c r="E96" s="133"/>
+      <c r="F96" s="134"/>
+      <c r="G96" s="134"/>
+      <c r="H96" s="6"/>
+      <c r="I96" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="J96" s="134" t="s">
+        <v>146</v>
+      </c>
+      <c r="K96" s="134"/>
+      <c r="L96" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="6"/>
+      <c r="N96" s="70"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A97" s="321" t="s">
+        <v>103</v>
+      </c>
+      <c r="B97" s="322"/>
+      <c r="C97" s="322"/>
+      <c r="D97" s="322"/>
+      <c r="E97" s="323"/>
+      <c r="F97" s="324"/>
+      <c r="G97" s="324"/>
+      <c r="H97" s="113"/>
+      <c r="I97" s="113"/>
+      <c r="J97" s="324"/>
+      <c r="K97" s="324"/>
+      <c r="L97" s="3"/>
+      <c r="M97" s="3"/>
+      <c r="N97" s="8"/>
+    </row>
+    <row r="98" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="325"/>
+      <c r="B98" s="326"/>
+      <c r="C98" s="326"/>
+      <c r="D98" s="326"/>
+      <c r="E98" s="327" t="s">
+        <v>3</v>
+      </c>
+      <c r="F98" s="328"/>
+      <c r="G98" s="328"/>
+      <c r="H98" s="114" t="s">
+        <v>3</v>
+      </c>
+      <c r="I98" s="114" t="s">
+        <v>3</v>
+      </c>
+      <c r="J98" s="328" t="s">
+        <v>3</v>
+      </c>
+      <c r="K98" s="328"/>
+      <c r="L98" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="M98" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="N98" s="115" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="101" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="312" t="s">
+        <v>104</v>
+      </c>
+      <c r="B101" s="313"/>
+      <c r="C101" s="313"/>
+      <c r="D101" s="313"/>
+      <c r="E101" s="314" t="s">
+        <v>105</v>
+      </c>
+      <c r="F101" s="315"/>
+      <c r="G101" s="316"/>
+      <c r="H101" s="116"/>
+      <c r="I101" s="116" t="s">
+        <v>105</v>
+      </c>
+      <c r="J101" s="314" t="s">
+        <v>105</v>
+      </c>
+      <c r="K101" s="316"/>
+      <c r="L101" s="117" t="s">
+        <v>105</v>
+      </c>
+      <c r="M101" s="117"/>
+      <c r="N101" s="118"/>
+    </row>
+    <row r="102" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="317" t="s">
+        <v>106</v>
+      </c>
+      <c r="B102" s="318"/>
+      <c r="C102" s="318"/>
+      <c r="D102" s="319"/>
+      <c r="E102" s="320" t="s">
+        <v>148</v>
+      </c>
+      <c r="F102" s="315"/>
+      <c r="G102" s="316"/>
+      <c r="H102" s="119"/>
+      <c r="I102" s="119" t="s">
+        <v>107</v>
+      </c>
+      <c r="J102" s="320" t="s">
+        <v>107</v>
+      </c>
+      <c r="K102" s="316"/>
+      <c r="L102" s="119" t="s">
+        <v>107</v>
+      </c>
+      <c r="M102" s="117"/>
+      <c r="N102" s="118"/>
+    </row>
+  </sheetData>
+  <mergeCells count="300">
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="E101:G101"/>
+    <mergeCell ref="J101:K101"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="E102:G102"/>
+    <mergeCell ref="J102:K102"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="E97:G97"/>
+    <mergeCell ref="J97:K97"/>
+    <mergeCell ref="A98:D98"/>
+    <mergeCell ref="E98:G98"/>
+    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="A95:D95"/>
+    <mergeCell ref="E95:G95"/>
+    <mergeCell ref="J95:K95"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="E96:G96"/>
+    <mergeCell ref="J96:K96"/>
+    <mergeCell ref="A93:D93"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="J93:K93"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="E94:G94"/>
+    <mergeCell ref="J94:K94"/>
+    <mergeCell ref="A91:D91"/>
+    <mergeCell ref="E91:G91"/>
+    <mergeCell ref="J91:K91"/>
+    <mergeCell ref="A92:D92"/>
+    <mergeCell ref="E92:G92"/>
+    <mergeCell ref="J92:K92"/>
+    <mergeCell ref="A89:D89"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="J89:K89"/>
+    <mergeCell ref="A90:D90"/>
+    <mergeCell ref="E90:G90"/>
+    <mergeCell ref="J90:K90"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="E87:G87"/>
+    <mergeCell ref="J87:K87"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="E88:G88"/>
+    <mergeCell ref="J88:K88"/>
+    <mergeCell ref="A85:D85"/>
+    <mergeCell ref="E85:G85"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="A86:D86"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="A83:D83"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="E84:G84"/>
+    <mergeCell ref="J84:K84"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="E81:G81"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="A82:D82"/>
+    <mergeCell ref="E82:G82"/>
+    <mergeCell ref="J82:K82"/>
+    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="E79:G79"/>
+    <mergeCell ref="J79:K79"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="E80:G80"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="E78:G78"/>
+    <mergeCell ref="J78:K78"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="E75:G75"/>
+    <mergeCell ref="J75:K75"/>
+    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="E76:G76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="J73:K73"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="E71:G71"/>
+    <mergeCell ref="J71:K71"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="E72:G72"/>
+    <mergeCell ref="J72:K72"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="J69:K69"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="E70:G70"/>
+    <mergeCell ref="J70:K70"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="E67:G67"/>
+    <mergeCell ref="J67:K67"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="E68:G68"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="E65:G65"/>
+    <mergeCell ref="J65:K65"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="E66:G66"/>
+    <mergeCell ref="J66:K66"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="J63:K63"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="J64:K64"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="J62:K62"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="E60:G60"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="J57:K57"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="E52:G52"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="J2:K2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BE88C1-8357-4935-9E7E-2751A3306D06}">
+  <dimension ref="A1:N102"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="17.44140625" customWidth="1"/>
+    <col min="8" max="8" width="23.109375" customWidth="1"/>
+    <col min="9" max="9" width="19.21875" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" customWidth="1"/>
+    <col min="13" max="13" width="20.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="141" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="144" t="s">
+        <v>153</v>
+      </c>
+      <c r="F1" s="145"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J1" s="147" t="s">
+        <v>156</v>
+      </c>
+      <c r="K1" s="146"/>
+      <c r="L1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="148" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="5"/>
+    </row>
+    <row r="3" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="130"/>
+      <c r="B3" s="131"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="132"/>
+      <c r="E3" s="133" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="134"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6"/>
+      <c r="J3" s="134" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="134"/>
+      <c r="L3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="6"/>
+      <c r="N3" s="7"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="135" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="136"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="137" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="138"/>
+      <c r="G4" s="139"/>
+      <c r="H4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="140"/>
+      <c r="L4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="3"/>
+      <c r="N4" s="8"/>
+    </row>
+    <row r="5" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="152"/>
+      <c r="B5" s="153"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="155" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="156"/>
+      <c r="G5" s="156"/>
+      <c r="H5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="156" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="156"/>
+      <c r="L5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="9"/>
+      <c r="N5" s="16"/>
+    </row>
+    <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="161" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="162"/>
+      <c r="C6" s="162"/>
+      <c r="D6" s="163"/>
+      <c r="E6" s="164"/>
+      <c r="F6" s="165"/>
+      <c r="G6" s="165"/>
+      <c r="H6" s="13" t="s">
+        <v>184</v>
+      </c>
       <c r="I6" s="13"/>
-      <c r="J6" s="163"/>
-      <c r="K6" s="163"/>
+      <c r="J6" s="165"/>
+      <c r="K6" s="165"/>
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
       <c r="N6" s="14"/>
     </row>
     <row r="7" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="150"/>
-      <c r="B7" s="151"/>
-      <c r="C7" s="151"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="153" t="s">
-        <v>116</v>
-      </c>
-      <c r="F7" s="154"/>
-      <c r="G7" s="154"/>
-      <c r="H7" s="9"/>
+      <c r="A7" s="152"/>
+      <c r="B7" s="153"/>
+      <c r="C7" s="153"/>
+      <c r="D7" s="154"/>
+      <c r="E7" s="155"/>
+      <c r="F7" s="156"/>
+      <c r="G7" s="156"/>
+      <c r="H7" s="9" t="s">
+        <v>185</v>
+      </c>
       <c r="I7" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="J7" s="154" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="154"/>
+      <c r="J7" s="156" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" s="156"/>
       <c r="L7" s="9" t="s">
         <v>6</v>
       </c>
@@ -2929,68 +5646,74 @@
       </c>
       <c r="N7" s="16"/>
     </row>
-    <row r="8" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="155" t="s">
+    <row r="8" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="157" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="156"/>
-      <c r="C8" s="156"/>
-      <c r="D8" s="156"/>
-      <c r="E8" s="157"/>
-      <c r="F8" s="158"/>
-      <c r="G8" s="158"/>
-      <c r="H8" s="121"/>
+      <c r="B8" s="158"/>
+      <c r="C8" s="158"/>
+      <c r="D8" s="158"/>
+      <c r="E8" s="159" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="160"/>
+      <c r="G8" s="160"/>
+      <c r="H8" s="44" t="s">
+        <v>8</v>
+      </c>
       <c r="I8" s="44"/>
-      <c r="J8" s="158" t="s">
+      <c r="J8" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="158"/>
+      <c r="K8" s="160"/>
       <c r="L8" s="44" t="s">
         <v>60</v>
       </c>
       <c r="M8" s="44" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N8" s="122"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="173" t="s">
+      <c r="A9" s="175" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="174"/>
-      <c r="C9" s="174"/>
-      <c r="D9" s="175"/>
-      <c r="E9" s="176"/>
-      <c r="F9" s="138"/>
-      <c r="G9" s="138"/>
+      <c r="B9" s="176"/>
+      <c r="C9" s="176"/>
+      <c r="D9" s="177"/>
+      <c r="E9" s="178"/>
+      <c r="F9" s="140"/>
+      <c r="G9" s="140"/>
       <c r="H9" s="18"/>
       <c r="I9" s="3"/>
-      <c r="J9" s="138"/>
-      <c r="K9" s="138"/>
+      <c r="J9" s="140"/>
+      <c r="K9" s="140"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="8"/>
     </row>
-    <row r="10" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="177"/>
-      <c r="B10" s="178"/>
-      <c r="C10" s="178"/>
-      <c r="D10" s="178"/>
-      <c r="E10" s="179" t="s">
-        <v>152</v>
-      </c>
-      <c r="F10" s="180"/>
-      <c r="G10" s="180"/>
-      <c r="H10" s="126"/>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="179"/>
+      <c r="B10" s="180"/>
+      <c r="C10" s="180"/>
+      <c r="D10" s="180"/>
+      <c r="E10" s="181" t="s">
+        <v>193</v>
+      </c>
+      <c r="F10" s="182"/>
+      <c r="G10" s="182"/>
+      <c r="H10" s="126" t="s">
+        <v>193</v>
+      </c>
       <c r="I10" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="J10" s="181" t="s">
-        <v>117</v>
-      </c>
-      <c r="K10" s="181"/>
+        <v>193</v>
+      </c>
+      <c r="J10" s="183" t="s">
+        <v>193</v>
+      </c>
+      <c r="K10" s="183"/>
       <c r="L10" s="32" t="s">
-        <v>117</v>
+        <v>193</v>
       </c>
       <c r="M10" s="32" t="s">
         <v>118</v>
@@ -2998,23 +5721,25 @@
       <c r="N10" s="39"/>
     </row>
     <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="164"/>
-      <c r="B11" s="165"/>
-      <c r="C11" s="165"/>
-      <c r="D11" s="166"/>
-      <c r="E11" s="167" t="s">
+      <c r="A11" s="166"/>
+      <c r="B11" s="167"/>
+      <c r="C11" s="167"/>
+      <c r="D11" s="168"/>
+      <c r="E11" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="168"/>
-      <c r="G11" s="168"/>
-      <c r="H11" s="21"/>
+      <c r="F11" s="170"/>
+      <c r="G11" s="170"/>
+      <c r="H11" s="21" t="s">
+        <v>11</v>
+      </c>
       <c r="I11" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="J11" s="154" t="s">
+      <c r="J11" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="K11" s="154"/>
+      <c r="K11" s="156"/>
       <c r="L11" s="22" t="s">
         <v>11</v>
       </c>
@@ -3022,67 +5747,69 @@
       <c r="N11" s="23"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="169" t="s">
+      <c r="A12" s="171" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="170"/>
-      <c r="C12" s="170"/>
-      <c r="D12" s="170"/>
-      <c r="E12" s="171"/>
-      <c r="F12" s="172"/>
-      <c r="G12" s="172"/>
+      <c r="B12" s="172"/>
+      <c r="C12" s="172"/>
+      <c r="D12" s="172"/>
+      <c r="E12" s="173"/>
+      <c r="F12" s="174"/>
+      <c r="G12" s="174"/>
       <c r="H12" s="123"/>
       <c r="I12" s="13"/>
-      <c r="J12" s="163"/>
-      <c r="K12" s="163"/>
+      <c r="J12" s="165"/>
+      <c r="K12" s="165"/>
       <c r="L12" s="124"/>
       <c r="M12" s="124"/>
       <c r="N12" s="125"/>
     </row>
-    <row r="13" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="188"/>
-      <c r="B13" s="189"/>
-      <c r="C13" s="189"/>
-      <c r="D13" s="190"/>
-      <c r="E13" s="191" t="s">
+    <row r="13" spans="1:14" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="191"/>
+      <c r="B13" s="192"/>
+      <c r="C13" s="192"/>
+      <c r="D13" s="193"/>
+      <c r="E13" s="194" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="154"/>
-      <c r="G13" s="154"/>
-      <c r="H13" s="9"/>
+      <c r="F13" s="156"/>
+      <c r="G13" s="156"/>
+      <c r="H13" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="I13" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J13" s="154" t="s">
+      <c r="J13" s="156" t="s">
         <v>13</v>
       </c>
-      <c r="K13" s="154"/>
+      <c r="K13" s="156"/>
       <c r="L13" s="9" t="s">
         <v>14</v>
       </c>
       <c r="M13" s="25"/>
       <c r="N13" s="26"/>
     </row>
-    <row r="14" spans="1:14" ht="43.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="192" t="s">
+    <row r="14" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="195" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="193"/>
-      <c r="C14" s="193"/>
-      <c r="D14" s="194"/>
-      <c r="E14" s="195" t="s">
-        <v>119</v>
-      </c>
-      <c r="F14" s="196"/>
-      <c r="G14" s="196"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19" t="s">
+      <c r="B14" s="196"/>
+      <c r="C14" s="196"/>
+      <c r="D14" s="197"/>
+      <c r="E14" s="198" t="s">
+        <v>160</v>
+      </c>
+      <c r="F14" s="199"/>
+      <c r="G14" s="199"/>
+      <c r="H14" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="196" t="s">
+      <c r="I14" s="19"/>
+      <c r="J14" s="199" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="196"/>
+      <c r="K14" s="199"/>
       <c r="L14" s="19" t="s">
         <v>16</v>
       </c>
@@ -3092,183 +5819,199 @@
       <c r="N14" s="27"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="169" t="s">
+      <c r="A15" s="171" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="170"/>
-      <c r="C15" s="170"/>
-      <c r="D15" s="182"/>
-      <c r="E15" s="135"/>
-      <c r="F15" s="136"/>
-      <c r="G15" s="137"/>
+      <c r="B15" s="172"/>
+      <c r="C15" s="172"/>
+      <c r="D15" s="184"/>
+      <c r="E15" s="137"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="139"/>
       <c r="H15" s="3"/>
       <c r="I15" s="4"/>
-      <c r="J15" s="183"/>
-      <c r="K15" s="184"/>
+      <c r="J15" s="185"/>
+      <c r="K15" s="186"/>
       <c r="L15" s="28"/>
       <c r="M15" s="3"/>
       <c r="N15" s="29"/>
     </row>
-    <row r="16" spans="1:14" ht="43.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="185"/>
-      <c r="B16" s="186"/>
-      <c r="C16" s="186"/>
-      <c r="D16" s="187"/>
-      <c r="E16" s="131" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="132"/>
-      <c r="G16" s="132"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="328" t="s">
+    <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="187"/>
+      <c r="B16" s="188"/>
+      <c r="C16" s="188"/>
+      <c r="D16" s="189"/>
+      <c r="E16" s="329" t="s">
         <v>3</v>
       </c>
-      <c r="J16" s="329" t="s">
+      <c r="F16" s="190"/>
+      <c r="G16" s="190"/>
+      <c r="H16" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="K16" s="329"/>
-      <c r="L16" s="328" t="s">
+      <c r="I16" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="M16" s="328" t="s">
+      <c r="J16" s="190" t="s">
         <v>3</v>
       </c>
+      <c r="K16" s="190"/>
+      <c r="L16" s="128" t="s">
+        <v>3</v>
+      </c>
+      <c r="M16" s="128" t="s">
+        <v>3</v>
+      </c>
       <c r="N16" s="30"/>
     </row>
-    <row r="17" spans="1:14" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="159" t="s">
+    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="161" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="160"/>
-      <c r="C17" s="160"/>
-      <c r="D17" s="160"/>
-      <c r="E17" s="149"/>
-      <c r="F17" s="138"/>
-      <c r="G17" s="138"/>
-      <c r="H17" s="3"/>
+      <c r="B17" s="162"/>
+      <c r="C17" s="162"/>
+      <c r="D17" s="162"/>
+      <c r="E17" s="151"/>
+      <c r="F17" s="140"/>
+      <c r="G17" s="140"/>
+      <c r="H17" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="I17" s="3"/>
-      <c r="J17" s="201" t="s">
+      <c r="J17" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="K17" s="137"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3" t="s">
+      <c r="K17" s="140"/>
+      <c r="L17" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="M17" s="3"/>
       <c r="N17" s="8"/>
     </row>
-    <row r="18" spans="1:14" ht="43.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="150"/>
-      <c r="B18" s="151"/>
-      <c r="C18" s="151"/>
-      <c r="D18" s="151"/>
-      <c r="E18" s="153" t="s">
+    <row r="18" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="152"/>
+      <c r="B18" s="153"/>
+      <c r="C18" s="153"/>
+      <c r="D18" s="153"/>
+      <c r="E18" s="155"/>
+      <c r="F18" s="156"/>
+      <c r="G18" s="156"/>
+      <c r="H18" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="156" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="156"/>
+      <c r="L18" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M18" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="154"/>
-      <c r="G18" s="154"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="202" t="s">
-        <v>24</v>
-      </c>
-      <c r="K18" s="203"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9" t="s">
-        <v>24</v>
-      </c>
       <c r="N18" s="16"/>
     </row>
-    <row r="19" spans="1:14" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="173" t="s">
+    <row r="19" spans="1:14" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="175" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="174"/>
-      <c r="C19" s="174"/>
-      <c r="D19" s="175"/>
-      <c r="E19" s="149"/>
-      <c r="F19" s="138"/>
-      <c r="G19" s="138"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="J19" s="138" t="s">
-        <v>148</v>
-      </c>
-      <c r="K19" s="138"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3" t="s">
+      <c r="B19" s="176"/>
+      <c r="C19" s="176"/>
+      <c r="D19" s="177"/>
+      <c r="E19" s="164" t="s">
+        <v>161</v>
+      </c>
+      <c r="F19" s="165"/>
+      <c r="G19" s="165"/>
+      <c r="H19" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="J19" s="165" t="s">
+        <v>166</v>
+      </c>
+      <c r="K19" s="165"/>
+      <c r="L19" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="M19" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="N19" s="31"/>
-    </row>
-    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="197"/>
-      <c r="B20" s="198"/>
-      <c r="C20" s="198"/>
-      <c r="D20" s="199"/>
-      <c r="E20" s="200"/>
-      <c r="F20" s="181"/>
-      <c r="G20" s="181"/>
+      <c r="N19" s="14"/>
+    </row>
+    <row r="20" spans="1:14" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="200"/>
+      <c r="B20" s="201"/>
+      <c r="C20" s="201"/>
+      <c r="D20" s="202"/>
+      <c r="E20" s="203" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="183"/>
+      <c r="G20" s="183"/>
       <c r="H20" s="32" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="I20" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J20" s="181" t="s">
+        <v>127</v>
+      </c>
+      <c r="J20" s="183" t="s">
         <v>124</v>
       </c>
-      <c r="K20" s="181"/>
+      <c r="K20" s="183"/>
       <c r="L20" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="M20" s="32"/>
+        <v>127</v>
+      </c>
+      <c r="M20" s="32" t="s">
+        <v>189</v>
+      </c>
       <c r="N20" s="33"/>
     </row>
-    <row r="21" spans="1:14" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="197"/>
-      <c r="B21" s="198"/>
-      <c r="C21" s="198"/>
-      <c r="D21" s="199"/>
-      <c r="E21" s="200" t="s">
-        <v>121</v>
-      </c>
-      <c r="F21" s="181"/>
-      <c r="G21" s="181"/>
-      <c r="H21" s="32"/>
+    <row r="21" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="200"/>
+      <c r="B21" s="201"/>
+      <c r="C21" s="201"/>
+      <c r="D21" s="202"/>
+      <c r="E21" s="203"/>
+      <c r="F21" s="183"/>
+      <c r="G21" s="183"/>
+      <c r="H21" s="32" t="s">
+        <v>127</v>
+      </c>
       <c r="I21" s="34"/>
-      <c r="J21" s="181" t="s">
-        <v>125</v>
-      </c>
-      <c r="K21" s="181"/>
+      <c r="J21" s="183"/>
+      <c r="K21" s="183"/>
       <c r="L21" s="32"/>
       <c r="M21" s="32"/>
       <c r="N21" s="35"/>
     </row>
-    <row r="22" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="207"/>
-      <c r="B22" s="208"/>
-      <c r="C22" s="208"/>
-      <c r="D22" s="209"/>
-      <c r="E22" s="153" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" s="154"/>
-      <c r="G22" s="154"/>
-      <c r="H22" s="9"/>
+    <row r="22" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="210"/>
+      <c r="B22" s="211"/>
+      <c r="C22" s="211"/>
+      <c r="D22" s="212"/>
+      <c r="E22" s="155" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" s="156"/>
+      <c r="G22" s="156"/>
+      <c r="H22" s="9" t="s">
+        <v>164</v>
+      </c>
       <c r="I22" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="J22" s="154" t="s">
-        <v>126</v>
-      </c>
-      <c r="K22" s="154"/>
+        <v>8</v>
+      </c>
+      <c r="J22" s="156" t="s">
+        <v>29</v>
+      </c>
+      <c r="K22" s="156"/>
       <c r="L22" s="9" t="s">
-        <v>127</v>
+        <v>167</v>
       </c>
       <c r="M22" s="9" t="s">
         <v>30</v>
@@ -3276,27 +6019,27 @@
       <c r="N22" s="11"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="173" t="s">
+      <c r="A23" s="175" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="174"/>
-      <c r="C23" s="174"/>
-      <c r="D23" s="175"/>
-      <c r="E23" s="162" t="s">
+      <c r="B23" s="176"/>
+      <c r="C23" s="176"/>
+      <c r="D23" s="177"/>
+      <c r="E23" s="164" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="163"/>
-      <c r="G23" s="163"/>
+      <c r="F23" s="165"/>
+      <c r="G23" s="165"/>
       <c r="H23" s="12" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="J23" s="204" t="s">
+      <c r="J23" s="207" t="s">
         <v>32</v>
       </c>
-      <c r="K23" s="204"/>
+      <c r="K23" s="207"/>
       <c r="L23" s="12" t="s">
         <v>32</v>
       </c>
@@ -3308,25 +6051,25 @@
       </c>
     </row>
     <row r="24" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="205"/>
-      <c r="B24" s="206"/>
-      <c r="C24" s="206"/>
-      <c r="D24" s="206"/>
-      <c r="E24" s="131" t="s">
+      <c r="A24" s="208"/>
+      <c r="B24" s="209"/>
+      <c r="C24" s="209"/>
+      <c r="D24" s="209"/>
+      <c r="E24" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="132"/>
-      <c r="G24" s="132"/>
+      <c r="F24" s="134"/>
+      <c r="G24" s="134"/>
       <c r="H24" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="J24" s="132" t="s">
+      <c r="J24" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="K24" s="132"/>
+      <c r="K24" s="134"/>
       <c r="L24" s="6" t="s">
         <v>32</v>
       </c>
@@ -3337,142 +6080,148 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="173" t="s">
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="175" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="174"/>
-      <c r="C25" s="174"/>
-      <c r="D25" s="175"/>
-      <c r="E25" s="149" t="s">
+      <c r="B25" s="176"/>
+      <c r="C25" s="176"/>
+      <c r="D25" s="177"/>
+      <c r="E25" s="151" t="s">
         <v>35</v>
       </c>
-      <c r="F25" s="138"/>
-      <c r="G25" s="138"/>
-      <c r="H25" s="3"/>
+      <c r="F25" s="140"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I25" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J25" s="201" t="s">
+      <c r="J25" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="K25" s="137"/>
+      <c r="K25" s="139"/>
       <c r="L25" s="3" t="s">
         <v>34</v>
       </c>
       <c r="M25" s="3"/>
       <c r="N25" s="8"/>
     </row>
-    <row r="26" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="177"/>
-      <c r="B26" s="178"/>
-      <c r="C26" s="178"/>
-      <c r="D26" s="178"/>
-      <c r="E26" s="218" t="s">
+    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="179"/>
+      <c r="B26" s="180"/>
+      <c r="C26" s="180"/>
+      <c r="D26" s="180"/>
+      <c r="E26" s="221" t="s">
         <v>36</v>
       </c>
-      <c r="F26" s="219"/>
-      <c r="G26" s="220"/>
-      <c r="H26" s="32"/>
+      <c r="F26" s="222"/>
+      <c r="G26" s="223"/>
+      <c r="H26" s="32" t="s">
+        <v>168</v>
+      </c>
       <c r="I26" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="J26" s="221" t="s">
+      <c r="J26" s="224" t="s">
         <v>36</v>
       </c>
-      <c r="K26" s="220"/>
+      <c r="K26" s="223"/>
       <c r="L26" s="32" t="s">
         <v>35</v>
       </c>
       <c r="M26" s="32"/>
       <c r="N26" s="39"/>
     </row>
-    <row r="27" spans="1:14" ht="43.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="150"/>
-      <c r="B27" s="151"/>
-      <c r="C27" s="151"/>
-      <c r="D27" s="151"/>
-      <c r="E27" s="210" t="s">
-        <v>128</v>
-      </c>
-      <c r="F27" s="211"/>
-      <c r="G27" s="203"/>
-      <c r="H27" s="9"/>
+    <row r="27" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="152"/>
+      <c r="B27" s="153"/>
+      <c r="C27" s="153"/>
+      <c r="D27" s="153"/>
+      <c r="E27" s="213" t="s">
+        <v>127</v>
+      </c>
+      <c r="F27" s="214"/>
+      <c r="G27" s="206"/>
+      <c r="H27" s="9" t="s">
+        <v>169</v>
+      </c>
       <c r="I27" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="J27" s="202" t="s">
-        <v>128</v>
-      </c>
-      <c r="K27" s="203"/>
+        <v>170</v>
+      </c>
+      <c r="J27" s="205" t="s">
+        <v>127</v>
+      </c>
+      <c r="K27" s="206"/>
       <c r="L27" s="9" t="s">
-        <v>37</v>
+        <v>171</v>
       </c>
       <c r="M27" s="9"/>
       <c r="N27" s="16"/>
     </row>
     <row r="28" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="212" t="s">
+      <c r="A28" s="215" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="213"/>
-      <c r="C28" s="213"/>
-      <c r="D28" s="213"/>
-      <c r="E28" s="214" t="s">
+      <c r="B28" s="216"/>
+      <c r="C28" s="216"/>
+      <c r="D28" s="216"/>
+      <c r="E28" s="217" t="s">
         <v>39</v>
       </c>
-      <c r="F28" s="215"/>
-      <c r="G28" s="216"/>
+      <c r="F28" s="218"/>
+      <c r="G28" s="219"/>
       <c r="H28" s="17" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="J28" s="217"/>
-      <c r="K28" s="216"/>
+      <c r="J28" s="220"/>
+      <c r="K28" s="219"/>
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" s="40"/>
     </row>
     <row r="29" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="185" t="s">
+      <c r="A29" s="187" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="186"/>
-      <c r="C29" s="186"/>
-      <c r="D29" s="187"/>
-      <c r="E29" s="226"/>
-      <c r="F29" s="227"/>
-      <c r="G29" s="228"/>
+      <c r="B29" s="188"/>
+      <c r="C29" s="188"/>
+      <c r="D29" s="189"/>
+      <c r="E29" s="229"/>
+      <c r="F29" s="230"/>
+      <c r="G29" s="231"/>
       <c r="H29" s="19" t="s">
         <v>39</v>
       </c>
       <c r="I29" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="J29" s="229" t="s">
+      <c r="J29" s="232" t="s">
         <v>39</v>
       </c>
-      <c r="K29" s="230"/>
+      <c r="K29" s="233"/>
       <c r="L29" s="19"/>
       <c r="M29" s="19"/>
       <c r="N29" s="20"/>
     </row>
-    <row r="30" spans="1:14" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="188" t="s">
+    <row r="30" spans="1:14" ht="28.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="191" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="189"/>
-      <c r="C30" s="189"/>
-      <c r="D30" s="190"/>
-      <c r="E30" s="231"/>
-      <c r="F30" s="232"/>
-      <c r="G30" s="232"/>
+      <c r="B30" s="192"/>
+      <c r="C30" s="192"/>
+      <c r="D30" s="193"/>
+      <c r="E30" s="234"/>
+      <c r="F30" s="235"/>
+      <c r="G30" s="235"/>
       <c r="H30" s="42"/>
       <c r="I30" s="43"/>
-      <c r="J30" s="158"/>
-      <c r="K30" s="158"/>
+      <c r="J30" s="160"/>
+      <c r="K30" s="160"/>
       <c r="L30" s="42"/>
       <c r="M30" s="41" t="s">
         <v>42</v>
@@ -3480,111 +6229,113 @@
       <c r="N30" s="45"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="169" t="s">
+      <c r="A31" s="171" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="170"/>
-      <c r="C31" s="170"/>
-      <c r="D31" s="170"/>
-      <c r="E31" s="222"/>
-      <c r="F31" s="223"/>
-      <c r="G31" s="223"/>
+      <c r="B31" s="172"/>
+      <c r="C31" s="172"/>
+      <c r="D31" s="172"/>
+      <c r="E31" s="225"/>
+      <c r="F31" s="226"/>
+      <c r="G31" s="226"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
-      <c r="J31" s="201"/>
-      <c r="K31" s="137"/>
+      <c r="J31" s="204"/>
+      <c r="K31" s="139"/>
       <c r="L31" s="47"/>
       <c r="M31" s="48"/>
       <c r="N31" s="49"/>
     </row>
-    <row r="32" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="185"/>
-      <c r="B32" s="186"/>
-      <c r="C32" s="186"/>
-      <c r="D32" s="186"/>
-      <c r="E32" s="224"/>
-      <c r="F32" s="225"/>
-      <c r="G32" s="225"/>
+    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="187"/>
+      <c r="B32" s="188"/>
+      <c r="C32" s="188"/>
+      <c r="D32" s="188"/>
+      <c r="E32" s="227"/>
+      <c r="F32" s="228"/>
+      <c r="G32" s="228"/>
       <c r="H32" s="51"/>
-      <c r="I32" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="J32" s="202"/>
-      <c r="K32" s="203"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="205"/>
+      <c r="K32" s="206"/>
       <c r="L32" s="51"/>
       <c r="M32" s="50"/>
       <c r="N32" s="52"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="173" t="s">
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="175" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="174"/>
-      <c r="C33" s="174"/>
-      <c r="D33" s="175"/>
-      <c r="E33" s="149"/>
-      <c r="F33" s="138"/>
-      <c r="G33" s="138"/>
+      <c r="B33" s="176"/>
+      <c r="C33" s="176"/>
+      <c r="D33" s="177"/>
+      <c r="E33" s="151"/>
+      <c r="F33" s="140"/>
+      <c r="G33" s="140"/>
       <c r="H33" s="47"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="240"/>
-      <c r="K33" s="240"/>
+      <c r="I33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" s="243"/>
+      <c r="K33" s="243"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
       <c r="N33" s="49"/>
     </row>
-    <row r="34" spans="1:14" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="150"/>
-      <c r="B34" s="151"/>
-      <c r="C34" s="151"/>
-      <c r="D34" s="151"/>
-      <c r="E34" s="167" t="s">
+    <row r="34" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="152"/>
+      <c r="B34" s="153"/>
+      <c r="C34" s="153"/>
+      <c r="D34" s="153"/>
+      <c r="E34" s="169" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="168"/>
-      <c r="G34" s="168"/>
+      <c r="F34" s="170"/>
+      <c r="G34" s="170"/>
       <c r="H34" s="53"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="168"/>
-      <c r="K34" s="241"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="21" t="s">
+      <c r="I34" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J34" s="170"/>
+      <c r="K34" s="244"/>
+      <c r="L34" s="9" t="s">
         <v>5</v>
       </c>
+      <c r="M34" s="21"/>
       <c r="N34" s="54"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="133" t="s">
+      <c r="A35" s="135" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="134"/>
-      <c r="C35" s="134"/>
-      <c r="D35" s="134"/>
-      <c r="E35" s="162"/>
-      <c r="F35" s="163"/>
-      <c r="G35" s="163"/>
+      <c r="B35" s="136"/>
+      <c r="C35" s="136"/>
+      <c r="D35" s="136"/>
+      <c r="E35" s="164"/>
+      <c r="F35" s="165"/>
+      <c r="G35" s="165"/>
       <c r="H35" s="55"/>
       <c r="I35" s="12"/>
-      <c r="J35" s="233"/>
-      <c r="K35" s="234"/>
+      <c r="J35" s="236"/>
+      <c r="K35" s="237"/>
       <c r="L35" s="55"/>
       <c r="M35" s="56"/>
       <c r="N35" s="57"/>
     </row>
-    <row r="36" spans="1:14" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="150"/>
-      <c r="B36" s="151"/>
-      <c r="C36" s="151"/>
-      <c r="D36" s="151"/>
-      <c r="E36" s="235"/>
-      <c r="F36" s="236"/>
-      <c r="G36" s="237"/>
+    <row r="36" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="152"/>
+      <c r="B36" s="153"/>
+      <c r="C36" s="153"/>
+      <c r="D36" s="153"/>
+      <c r="E36" s="238"/>
+      <c r="F36" s="239"/>
+      <c r="G36" s="240"/>
       <c r="H36" s="9"/>
       <c r="I36" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="J36" s="238"/>
-      <c r="K36" s="239"/>
+      <c r="J36" s="241"/>
+      <c r="K36" s="242"/>
       <c r="L36" s="50"/>
       <c r="M36" s="21" t="s">
         <v>1</v>
@@ -3592,43 +6343,43 @@
       <c r="N36" s="127"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="242" t="s">
+      <c r="A37" s="245" t="s">
         <v>46</v>
       </c>
-      <c r="B37" s="243"/>
-      <c r="C37" s="243"/>
-      <c r="D37" s="244"/>
-      <c r="E37" s="149"/>
-      <c r="F37" s="138"/>
-      <c r="G37" s="138"/>
+      <c r="B37" s="246"/>
+      <c r="C37" s="246"/>
+      <c r="D37" s="247"/>
+      <c r="E37" s="151"/>
+      <c r="F37" s="140"/>
+      <c r="G37" s="140"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
-      <c r="J37" s="183"/>
-      <c r="K37" s="184"/>
+      <c r="J37" s="185"/>
+      <c r="K37" s="186"/>
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
       <c r="N37" s="59"/>
     </row>
     <row r="38" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="245"/>
-      <c r="B38" s="246"/>
-      <c r="C38" s="246"/>
-      <c r="D38" s="247"/>
-      <c r="E38" s="248" t="s">
+      <c r="A38" s="248"/>
+      <c r="B38" s="249"/>
+      <c r="C38" s="249"/>
+      <c r="D38" s="250"/>
+      <c r="E38" s="251" t="s">
         <v>47</v>
       </c>
-      <c r="F38" s="249"/>
-      <c r="G38" s="250"/>
+      <c r="F38" s="252"/>
+      <c r="G38" s="253"/>
       <c r="H38" s="60" t="s">
         <v>47</v>
       </c>
       <c r="I38" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="J38" s="251" t="s">
+      <c r="J38" s="254" t="s">
         <v>47</v>
       </c>
-      <c r="K38" s="251"/>
+      <c r="K38" s="254"/>
       <c r="L38" s="60" t="s">
         <v>47</v>
       </c>
@@ -3640,41 +6391,41 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="173" t="s">
+      <c r="A39" s="175" t="s">
         <v>48</v>
       </c>
-      <c r="B39" s="174"/>
-      <c r="C39" s="174"/>
-      <c r="D39" s="175"/>
-      <c r="E39" s="149"/>
-      <c r="F39" s="138"/>
-      <c r="G39" s="138"/>
+      <c r="B39" s="176"/>
+      <c r="C39" s="176"/>
+      <c r="D39" s="177"/>
+      <c r="E39" s="151"/>
+      <c r="F39" s="140"/>
+      <c r="G39" s="140"/>
       <c r="H39" s="3"/>
       <c r="I39" s="4"/>
-      <c r="J39" s="138"/>
-      <c r="K39" s="138"/>
+      <c r="J39" s="140"/>
+      <c r="K39" s="140"/>
       <c r="L39" s="3"/>
       <c r="M39" s="62"/>
       <c r="N39" s="31"/>
     </row>
     <row r="40" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="128"/>
-      <c r="B40" s="129"/>
-      <c r="C40" s="129"/>
-      <c r="D40" s="130"/>
-      <c r="E40" s="153" t="s">
-        <v>130</v>
-      </c>
-      <c r="F40" s="154"/>
-      <c r="G40" s="154"/>
-      <c r="H40" s="9"/>
+      <c r="A40" s="130"/>
+      <c r="B40" s="131"/>
+      <c r="C40" s="131"/>
+      <c r="D40" s="132"/>
+      <c r="E40" s="155" t="s">
+        <v>50</v>
+      </c>
+      <c r="F40" s="156"/>
+      <c r="G40" s="156"/>
+      <c r="H40" s="9" t="s">
+        <v>50</v>
+      </c>
       <c r="I40" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="J40" s="154" t="s">
-        <v>19</v>
-      </c>
-      <c r="K40" s="154"/>
+      <c r="J40" s="156"/>
+      <c r="K40" s="156"/>
       <c r="L40" s="9" t="s">
         <v>62</v>
       </c>
@@ -3684,27 +6435,27 @@
       <c r="N40" s="16"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="173" t="s">
+      <c r="A41" s="175" t="s">
         <v>52</v>
       </c>
-      <c r="B41" s="174"/>
-      <c r="C41" s="174"/>
-      <c r="D41" s="175"/>
-      <c r="E41" s="171" t="s">
+      <c r="B41" s="176"/>
+      <c r="C41" s="176"/>
+      <c r="D41" s="177"/>
+      <c r="E41" s="173" t="s">
         <v>32</v>
       </c>
-      <c r="F41" s="163"/>
-      <c r="G41" s="163"/>
+      <c r="F41" s="165"/>
+      <c r="G41" s="165"/>
       <c r="H41" s="12" t="s">
         <v>32</v>
       </c>
       <c r="I41" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="J41" s="163" t="s">
+      <c r="J41" s="165" t="s">
         <v>32</v>
       </c>
-      <c r="K41" s="163"/>
+      <c r="K41" s="165"/>
       <c r="L41" s="3" t="s">
         <v>32</v>
       </c>
@@ -3712,315 +6463,331 @@
       <c r="N41" s="14"/>
     </row>
     <row r="42" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="207"/>
-      <c r="B42" s="208"/>
-      <c r="C42" s="208"/>
-      <c r="D42" s="209"/>
-      <c r="E42" s="131" t="s">
+      <c r="A42" s="210"/>
+      <c r="B42" s="211"/>
+      <c r="C42" s="211"/>
+      <c r="D42" s="212"/>
+      <c r="E42" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="F42" s="132"/>
-      <c r="G42" s="132"/>
+      <c r="F42" s="134"/>
+      <c r="G42" s="134"/>
       <c r="H42" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I42" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="J42" s="132" t="s">
+      <c r="J42" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="K42" s="132"/>
+      <c r="K42" s="134"/>
       <c r="L42" s="6" t="s">
         <v>32</v>
       </c>
       <c r="M42" s="63"/>
       <c r="N42" s="30"/>
     </row>
-    <row r="43" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="173" t="s">
+    <row r="43" spans="1:14" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="175" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="174"/>
-      <c r="C43" s="174"/>
-      <c r="D43" s="175"/>
-      <c r="E43" s="149" t="s">
-        <v>145</v>
-      </c>
-      <c r="F43" s="138"/>
-      <c r="G43" s="138"/>
-      <c r="H43" s="3"/>
+      <c r="B43" s="176"/>
+      <c r="C43" s="176"/>
+      <c r="D43" s="177"/>
+      <c r="E43" s="151" t="s">
+        <v>161</v>
+      </c>
+      <c r="F43" s="140"/>
+      <c r="G43" s="140"/>
+      <c r="H43" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="I43" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J43" s="138" t="s">
-        <v>117</v>
-      </c>
-      <c r="K43" s="138"/>
+        <v>172</v>
+      </c>
+      <c r="J43" s="140" t="s">
+        <v>192</v>
+      </c>
+      <c r="K43" s="140"/>
       <c r="L43" s="3" t="s">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="M43" s="3"/>
       <c r="N43" s="64"/>
     </row>
-    <row r="44" spans="1:14" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="197"/>
-      <c r="B44" s="198"/>
-      <c r="C44" s="198"/>
-      <c r="D44" s="199"/>
-      <c r="E44" s="200"/>
-      <c r="F44" s="181"/>
-      <c r="G44" s="181"/>
-      <c r="H44" s="32"/>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="200"/>
+      <c r="B44" s="201"/>
+      <c r="C44" s="201"/>
+      <c r="D44" s="202"/>
+      <c r="E44" s="203"/>
+      <c r="F44" s="183"/>
+      <c r="G44" s="183"/>
+      <c r="H44" s="32" t="s">
+        <v>55</v>
+      </c>
       <c r="I44" s="32"/>
-      <c r="J44" s="181" t="s">
+      <c r="J44" s="183"/>
+      <c r="K44" s="183"/>
+      <c r="L44" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="K44" s="181"/>
-      <c r="L44" s="32"/>
       <c r="M44" s="32"/>
       <c r="N44" s="33"/>
     </row>
     <row r="45" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="207"/>
-      <c r="B45" s="208"/>
-      <c r="C45" s="208"/>
-      <c r="D45" s="209"/>
-      <c r="E45" s="153"/>
-      <c r="F45" s="154"/>
-      <c r="G45" s="154"/>
+      <c r="A45" s="210"/>
+      <c r="B45" s="211"/>
+      <c r="C45" s="211"/>
+      <c r="D45" s="212"/>
+      <c r="E45" s="155"/>
+      <c r="F45" s="156"/>
+      <c r="G45" s="156"/>
       <c r="H45" s="9"/>
       <c r="I45" s="10"/>
-      <c r="J45" s="154"/>
-      <c r="K45" s="154"/>
+      <c r="J45" s="156"/>
+      <c r="K45" s="156"/>
       <c r="L45" s="9"/>
       <c r="M45" s="65"/>
       <c r="N45" s="11"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="173" t="s">
+      <c r="A46" s="175" t="s">
         <v>56</v>
       </c>
-      <c r="B46" s="174"/>
-      <c r="C46" s="174"/>
-      <c r="D46" s="258"/>
-      <c r="E46" s="162"/>
-      <c r="F46" s="163"/>
-      <c r="G46" s="163"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="12"/>
-      <c r="J46" s="259"/>
-      <c r="K46" s="260"/>
-      <c r="L46" s="12"/>
+      <c r="B46" s="176"/>
+      <c r="C46" s="176"/>
+      <c r="D46" s="261"/>
+      <c r="E46" s="164" t="s">
+        <v>193</v>
+      </c>
+      <c r="F46" s="165"/>
+      <c r="G46" s="165"/>
+      <c r="H46" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="I46" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="J46" s="262" t="s">
+        <v>193</v>
+      </c>
+      <c r="K46" s="263"/>
+      <c r="L46" s="12" t="s">
+        <v>193</v>
+      </c>
       <c r="M46" s="66"/>
       <c r="N46" s="67"/>
     </row>
     <row r="47" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="245"/>
-      <c r="B47" s="246"/>
-      <c r="C47" s="246"/>
-      <c r="D47" s="247"/>
-      <c r="E47" s="252"/>
-      <c r="F47" s="253"/>
-      <c r="G47" s="254"/>
+      <c r="A47" s="248"/>
+      <c r="B47" s="249"/>
+      <c r="C47" s="249"/>
+      <c r="D47" s="250"/>
+      <c r="E47" s="255"/>
+      <c r="F47" s="256"/>
+      <c r="G47" s="257"/>
       <c r="H47" s="68"/>
       <c r="I47" s="68"/>
-      <c r="J47" s="255"/>
-      <c r="K47" s="256"/>
+      <c r="J47" s="258"/>
+      <c r="K47" s="259"/>
       <c r="L47" s="68"/>
       <c r="M47" s="69"/>
       <c r="N47" s="70"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="169" t="s">
+      <c r="A48" s="171" t="s">
         <v>57</v>
       </c>
-      <c r="B48" s="170"/>
-      <c r="C48" s="170"/>
-      <c r="D48" s="170"/>
-      <c r="E48" s="149"/>
-      <c r="F48" s="138"/>
-      <c r="G48" s="138"/>
+      <c r="B48" s="172"/>
+      <c r="C48" s="172"/>
+      <c r="D48" s="172"/>
+      <c r="E48" s="151"/>
+      <c r="F48" s="140"/>
+      <c r="G48" s="140"/>
       <c r="H48" s="28"/>
       <c r="I48" s="3"/>
-      <c r="J48" s="257"/>
-      <c r="K48" s="257"/>
+      <c r="J48" s="260"/>
+      <c r="K48" s="260"/>
       <c r="L48" s="28"/>
       <c r="M48" s="71"/>
       <c r="N48" s="29"/>
     </row>
-    <row r="49" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="264"/>
-      <c r="B49" s="265"/>
-      <c r="C49" s="265"/>
-      <c r="D49" s="265"/>
-      <c r="E49" s="153"/>
-      <c r="F49" s="154"/>
-      <c r="G49" s="154"/>
-      <c r="H49" s="9"/>
+    <row r="49" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="267"/>
+      <c r="B49" s="268"/>
+      <c r="C49" s="268"/>
+      <c r="D49" s="268"/>
+      <c r="E49" s="155"/>
+      <c r="F49" s="156"/>
+      <c r="G49" s="156"/>
+      <c r="H49" s="9" t="s">
+        <v>5</v>
+      </c>
       <c r="I49" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="J49" s="154" t="s">
-        <v>5</v>
-      </c>
-      <c r="K49" s="154"/>
-      <c r="L49" s="9" t="s">
+      <c r="J49" s="156"/>
+      <c r="K49" s="156"/>
+      <c r="L49" s="9"/>
+      <c r="M49" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="M49" s="9"/>
       <c r="N49" s="16"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="133" t="s">
+    <row r="50" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="135" t="s">
         <v>59</v>
       </c>
-      <c r="B50" s="134"/>
-      <c r="C50" s="134"/>
-      <c r="D50" s="134"/>
-      <c r="E50" s="266"/>
-      <c r="F50" s="267"/>
-      <c r="G50" s="260"/>
+      <c r="B50" s="136"/>
+      <c r="C50" s="136"/>
+      <c r="D50" s="136"/>
+      <c r="E50" s="269"/>
+      <c r="F50" s="270"/>
+      <c r="G50" s="263"/>
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
-      <c r="J50" s="204"/>
-      <c r="K50" s="204"/>
+      <c r="J50" s="207"/>
+      <c r="K50" s="207"/>
       <c r="L50" s="12"/>
-      <c r="M50" s="12"/>
+      <c r="M50" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="N50" s="72"/>
     </row>
-    <row r="51" spans="1:14" ht="55.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="261"/>
-      <c r="B51" s="262"/>
-      <c r="C51" s="262"/>
-      <c r="D51" s="262"/>
-      <c r="E51" s="153" t="s">
+    <row r="51" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="264"/>
+      <c r="B51" s="265"/>
+      <c r="C51" s="265"/>
+      <c r="D51" s="265"/>
+      <c r="E51" s="155"/>
+      <c r="F51" s="156"/>
+      <c r="G51" s="156"/>
+      <c r="H51" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I51" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="F51" s="154"/>
-      <c r="G51" s="154"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="J51" s="154" t="s">
+      <c r="J51" s="156" t="s">
         <v>50</v>
       </c>
-      <c r="K51" s="154"/>
+      <c r="K51" s="156"/>
       <c r="L51" s="9"/>
-      <c r="M51" s="9" t="s">
-        <v>9</v>
-      </c>
+      <c r="M51" s="9"/>
       <c r="N51" s="73"/>
     </row>
-    <row r="52" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="242" t="s">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="245" t="s">
         <v>61</v>
       </c>
-      <c r="B52" s="243"/>
-      <c r="C52" s="243"/>
-      <c r="D52" s="263"/>
-      <c r="E52" s="135" t="s">
-        <v>150</v>
-      </c>
-      <c r="F52" s="136"/>
-      <c r="G52" s="137"/>
+      <c r="B52" s="246"/>
+      <c r="C52" s="246"/>
+      <c r="D52" s="266"/>
+      <c r="E52" s="137"/>
+      <c r="F52" s="138"/>
+      <c r="G52" s="139"/>
       <c r="H52" s="74"/>
-      <c r="I52" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="J52" s="204"/>
-      <c r="K52" s="204"/>
+      <c r="I52" s="12"/>
+      <c r="J52" s="207"/>
+      <c r="K52" s="207"/>
       <c r="L52" s="12"/>
       <c r="M52" s="36"/>
       <c r="N52" s="75"/>
     </row>
-    <row r="53" spans="1:14" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="271"/>
-      <c r="B53" s="272"/>
-      <c r="C53" s="272"/>
-      <c r="D53" s="272"/>
-      <c r="E53" s="273" t="s">
-        <v>120</v>
-      </c>
-      <c r="F53" s="274"/>
-      <c r="G53" s="274"/>
-      <c r="H53" s="76"/>
-      <c r="I53" s="76"/>
-      <c r="J53" s="274" t="s">
+    <row r="53" spans="1:14" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="274"/>
+      <c r="B53" s="275"/>
+      <c r="C53" s="275"/>
+      <c r="D53" s="275"/>
+      <c r="E53" s="276" t="s">
         <v>18</v>
       </c>
-      <c r="K53" s="274"/>
-      <c r="L53" s="76" t="s">
+      <c r="F53" s="277"/>
+      <c r="G53" s="277"/>
+      <c r="H53" s="76" t="s">
         <v>18</v>
       </c>
+      <c r="I53" s="76" t="s">
+        <v>18</v>
+      </c>
+      <c r="J53" s="277" t="s">
+        <v>19</v>
+      </c>
+      <c r="K53" s="277"/>
+      <c r="L53" s="76"/>
       <c r="M53" s="76" t="s">
         <v>21</v>
       </c>
       <c r="N53" s="77"/>
     </row>
-    <row r="54" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="275" t="s">
+    <row r="54" spans="1:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="278" t="s">
         <v>63</v>
       </c>
-      <c r="B54" s="276"/>
-      <c r="C54" s="276"/>
-      <c r="D54" s="277"/>
-      <c r="E54" s="149" t="s">
-        <v>146</v>
-      </c>
-      <c r="F54" s="138"/>
-      <c r="G54" s="138"/>
-      <c r="H54" s="3"/>
+      <c r="B54" s="279"/>
+      <c r="C54" s="279"/>
+      <c r="D54" s="280"/>
+      <c r="E54" s="151" t="s">
+        <v>195</v>
+      </c>
+      <c r="F54" s="140"/>
+      <c r="G54" s="140"/>
+      <c r="H54" s="3" t="s">
+        <v>193</v>
+      </c>
       <c r="I54" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J54" s="138" t="s">
-        <v>117</v>
-      </c>
-      <c r="K54" s="138"/>
+        <v>193</v>
+      </c>
+      <c r="J54" s="140" t="s">
+        <v>193</v>
+      </c>
+      <c r="K54" s="140"/>
       <c r="L54" s="3" t="s">
-        <v>117</v>
+        <v>193</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="49"/>
     </row>
     <row r="55" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="268"/>
-      <c r="B55" s="269"/>
-      <c r="C55" s="269"/>
-      <c r="D55" s="270"/>
-      <c r="E55" s="153"/>
-      <c r="F55" s="154"/>
-      <c r="G55" s="154"/>
+      <c r="A55" s="271"/>
+      <c r="B55" s="272"/>
+      <c r="C55" s="272"/>
+      <c r="D55" s="273"/>
+      <c r="E55" s="155"/>
+      <c r="F55" s="156"/>
+      <c r="G55" s="156"/>
       <c r="H55" s="21"/>
       <c r="I55" s="50"/>
-      <c r="J55" s="154"/>
-      <c r="K55" s="154"/>
+      <c r="J55" s="156"/>
+      <c r="K55" s="156"/>
       <c r="L55" s="9"/>
       <c r="M55" s="51"/>
       <c r="N55" s="52"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="242" t="s">
+      <c r="A56" s="245" t="s">
         <v>64</v>
       </c>
-      <c r="B56" s="243"/>
-      <c r="C56" s="243"/>
-      <c r="D56" s="263"/>
-      <c r="E56" s="162" t="s">
+      <c r="B56" s="246"/>
+      <c r="C56" s="246"/>
+      <c r="D56" s="266"/>
+      <c r="E56" s="164" t="s">
         <v>65</v>
       </c>
-      <c r="F56" s="163"/>
-      <c r="G56" s="163"/>
-      <c r="H56" s="12"/>
+      <c r="F56" s="165"/>
+      <c r="G56" s="165"/>
+      <c r="H56" s="12" t="s">
+        <v>65</v>
+      </c>
       <c r="I56" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="J56" s="259" t="s">
+      <c r="J56" s="262" t="s">
         <v>65</v>
       </c>
-      <c r="K56" s="260"/>
+      <c r="K56" s="263"/>
       <c r="L56" s="12" t="s">
         <v>65</v>
       </c>
@@ -4028,41 +6795,43 @@
       <c r="N56" s="78"/>
     </row>
     <row r="57" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="207"/>
-      <c r="B57" s="208"/>
-      <c r="C57" s="208"/>
-      <c r="D57" s="209"/>
-      <c r="E57" s="131"/>
-      <c r="F57" s="132"/>
-      <c r="G57" s="132"/>
+      <c r="A57" s="210"/>
+      <c r="B57" s="211"/>
+      <c r="C57" s="211"/>
+      <c r="D57" s="212"/>
+      <c r="E57" s="133"/>
+      <c r="F57" s="134"/>
+      <c r="G57" s="134"/>
       <c r="H57" s="6"/>
       <c r="I57" s="6"/>
-      <c r="J57" s="154"/>
-      <c r="K57" s="154"/>
+      <c r="J57" s="156"/>
+      <c r="K57" s="156"/>
       <c r="L57" s="6"/>
       <c r="M57" s="63"/>
       <c r="N57" s="30"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="173" t="s">
+    <row r="58" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="175" t="s">
         <v>66</v>
       </c>
-      <c r="B58" s="174"/>
-      <c r="C58" s="174"/>
-      <c r="D58" s="175"/>
-      <c r="E58" s="149" t="s">
+      <c r="B58" s="176"/>
+      <c r="C58" s="176"/>
+      <c r="D58" s="177"/>
+      <c r="E58" s="151" t="s">
         <v>26</v>
       </c>
-      <c r="F58" s="138"/>
-      <c r="G58" s="138"/>
-      <c r="H58" s="3"/>
+      <c r="F58" s="140"/>
+      <c r="G58" s="140"/>
+      <c r="H58" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="I58" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J58" s="138" t="s">
+      <c r="J58" s="140" t="s">
         <v>26</v>
       </c>
-      <c r="K58" s="138"/>
+      <c r="K58" s="140"/>
       <c r="L58" s="3" t="s">
         <v>26</v>
       </c>
@@ -4070,107 +6839,105 @@
       <c r="N58" s="31"/>
     </row>
     <row r="59" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="207"/>
-      <c r="B59" s="208"/>
-      <c r="C59" s="208"/>
-      <c r="D59" s="209"/>
-      <c r="E59" s="131"/>
-      <c r="F59" s="132"/>
-      <c r="G59" s="132"/>
+      <c r="A59" s="210"/>
+      <c r="B59" s="211"/>
+      <c r="C59" s="211"/>
+      <c r="D59" s="212"/>
+      <c r="E59" s="133"/>
+      <c r="F59" s="134"/>
+      <c r="G59" s="134"/>
       <c r="H59" s="68"/>
       <c r="I59" s="6"/>
-      <c r="J59" s="132"/>
-      <c r="K59" s="132"/>
+      <c r="J59" s="134"/>
+      <c r="K59" s="134"/>
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
       <c r="N59" s="30"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="173" t="s">
+    <row r="60" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="175" t="s">
         <v>67</v>
       </c>
-      <c r="B60" s="174"/>
-      <c r="C60" s="174"/>
-      <c r="D60" s="175"/>
-      <c r="E60" s="278" t="s">
+      <c r="B60" s="176"/>
+      <c r="C60" s="176"/>
+      <c r="D60" s="177"/>
+      <c r="E60" s="281" t="s">
         <v>27</v>
       </c>
-      <c r="F60" s="257"/>
-      <c r="G60" s="257"/>
-      <c r="H60" s="4"/>
+      <c r="F60" s="260"/>
+      <c r="G60" s="260"/>
+      <c r="H60" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="I60" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="J60" s="257" t="s">
+      <c r="J60" s="260" t="s">
         <v>68</v>
       </c>
-      <c r="K60" s="257"/>
+      <c r="K60" s="260"/>
       <c r="L60" s="4" t="s">
-        <v>135</v>
+        <v>27</v>
       </c>
       <c r="M60" s="79"/>
       <c r="N60" s="59"/>
     </row>
-    <row r="61" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A61" s="197"/>
-      <c r="B61" s="198"/>
-      <c r="C61" s="198"/>
-      <c r="D61" s="199"/>
-      <c r="E61" s="200"/>
-      <c r="F61" s="181"/>
-      <c r="G61" s="181"/>
-      <c r="H61" s="32"/>
-      <c r="I61" s="32" t="s">
-        <v>142</v>
-      </c>
-      <c r="J61" s="181"/>
-      <c r="K61" s="181"/>
-      <c r="L61" s="32" t="s">
-        <v>54</v>
-      </c>
+    <row r="61" spans="1:14" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="200"/>
+      <c r="B61" s="201"/>
+      <c r="C61" s="201"/>
+      <c r="D61" s="202"/>
+      <c r="E61" s="203"/>
+      <c r="F61" s="183"/>
+      <c r="G61" s="183"/>
+      <c r="H61" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="I61" s="32"/>
+      <c r="J61" s="183"/>
+      <c r="K61" s="183"/>
+      <c r="L61" s="32"/>
       <c r="M61" s="32"/>
       <c r="N61" s="33"/>
     </row>
-    <row r="62" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="245"/>
-      <c r="B62" s="246"/>
-      <c r="C62" s="246"/>
-      <c r="D62" s="284"/>
-      <c r="E62" s="153"/>
-      <c r="F62" s="154"/>
-      <c r="G62" s="154"/>
+    <row r="62" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="248"/>
+      <c r="B62" s="249"/>
+      <c r="C62" s="249"/>
+      <c r="D62" s="287"/>
+      <c r="E62" s="155"/>
+      <c r="F62" s="156"/>
+      <c r="G62" s="156"/>
       <c r="H62" s="10"/>
       <c r="I62" s="10"/>
-      <c r="J62" s="285"/>
-      <c r="K62" s="285"/>
-      <c r="L62" s="10" t="s">
-        <v>136</v>
-      </c>
+      <c r="J62" s="288"/>
+      <c r="K62" s="288"/>
+      <c r="L62" s="10"/>
       <c r="M62" s="80"/>
       <c r="N62" s="81"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="173" t="s">
+      <c r="A63" s="175" t="s">
         <v>69</v>
       </c>
-      <c r="B63" s="174"/>
-      <c r="C63" s="174"/>
-      <c r="D63" s="258"/>
-      <c r="E63" s="279" t="s">
+      <c r="B63" s="176"/>
+      <c r="C63" s="176"/>
+      <c r="D63" s="261"/>
+      <c r="E63" s="282" t="s">
         <v>47</v>
       </c>
-      <c r="F63" s="280"/>
-      <c r="G63" s="280"/>
+      <c r="F63" s="283"/>
+      <c r="G63" s="283"/>
       <c r="H63" s="82" t="s">
         <v>47</v>
       </c>
       <c r="I63" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="J63" s="281" t="s">
+      <c r="J63" s="284" t="s">
         <v>47</v>
       </c>
-      <c r="K63" s="281"/>
+      <c r="K63" s="284"/>
       <c r="L63" s="84" t="s">
         <v>47</v>
       </c>
@@ -4182,97 +6949,95 @@
       </c>
     </row>
     <row r="64" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="207"/>
-      <c r="B64" s="208"/>
-      <c r="C64" s="208"/>
-      <c r="D64" s="282"/>
-      <c r="E64" s="131"/>
-      <c r="F64" s="132"/>
-      <c r="G64" s="132"/>
+      <c r="A64" s="210"/>
+      <c r="B64" s="211"/>
+      <c r="C64" s="211"/>
+      <c r="D64" s="285"/>
+      <c r="E64" s="133"/>
+      <c r="F64" s="134"/>
+      <c r="G64" s="134"/>
       <c r="H64" s="86"/>
       <c r="I64" s="6"/>
-      <c r="J64" s="283"/>
-      <c r="K64" s="283"/>
+      <c r="J64" s="286"/>
+      <c r="K64" s="286"/>
       <c r="L64" s="87"/>
       <c r="M64" s="87"/>
       <c r="N64" s="70"/>
     </row>
     <row r="65" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A65" s="133" t="s">
+      <c r="A65" s="135" t="s">
         <v>70</v>
       </c>
-      <c r="B65" s="134"/>
-      <c r="C65" s="134"/>
-      <c r="D65" s="134"/>
-      <c r="E65" s="135"/>
-      <c r="F65" s="136"/>
-      <c r="G65" s="137"/>
+      <c r="B65" s="136"/>
+      <c r="C65" s="136"/>
+      <c r="D65" s="136"/>
+      <c r="E65" s="137"/>
+      <c r="F65" s="138"/>
+      <c r="G65" s="139"/>
       <c r="H65" s="28"/>
       <c r="I65" s="3"/>
-      <c r="J65" s="183"/>
-      <c r="K65" s="184"/>
+      <c r="J65" s="185"/>
+      <c r="K65" s="186"/>
       <c r="L65" s="3"/>
       <c r="M65" s="28" t="s">
         <v>26</v>
       </c>
       <c r="N65" s="88"/>
     </row>
-    <row r="66" spans="1:14" ht="34.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="261"/>
-      <c r="B66" s="262"/>
-      <c r="C66" s="262"/>
-      <c r="D66" s="262"/>
-      <c r="E66" s="210" t="s">
-        <v>74</v>
-      </c>
-      <c r="F66" s="211"/>
-      <c r="G66" s="203"/>
+    <row r="66" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="264"/>
+      <c r="B66" s="265"/>
+      <c r="C66" s="265"/>
+      <c r="D66" s="265"/>
+      <c r="E66" s="213"/>
+      <c r="F66" s="214"/>
+      <c r="G66" s="206"/>
       <c r="H66" s="80"/>
       <c r="I66" s="9"/>
-      <c r="J66" s="290"/>
-      <c r="K66" s="291"/>
+      <c r="J66" s="258"/>
+      <c r="K66" s="259"/>
       <c r="L66" s="89"/>
       <c r="M66" s="89"/>
       <c r="N66" s="90"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="242" t="s">
+      <c r="A67" s="245" t="s">
         <v>71</v>
       </c>
-      <c r="B67" s="243"/>
-      <c r="C67" s="243"/>
-      <c r="D67" s="263"/>
-      <c r="E67" s="149"/>
-      <c r="F67" s="138"/>
-      <c r="G67" s="138"/>
+      <c r="B67" s="246"/>
+      <c r="C67" s="246"/>
+      <c r="D67" s="266"/>
+      <c r="E67" s="151"/>
+      <c r="F67" s="140"/>
+      <c r="G67" s="140"/>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
-      <c r="J67" s="201"/>
-      <c r="K67" s="137"/>
+      <c r="J67" s="204"/>
+      <c r="K67" s="139"/>
       <c r="L67" s="46"/>
       <c r="M67" s="46"/>
       <c r="N67" s="8"/>
     </row>
     <row r="68" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="207"/>
-      <c r="B68" s="208"/>
-      <c r="C68" s="208"/>
-      <c r="D68" s="209"/>
-      <c r="E68" s="286" t="s">
+      <c r="A68" s="210"/>
+      <c r="B68" s="211"/>
+      <c r="C68" s="211"/>
+      <c r="D68" s="212"/>
+      <c r="E68" s="289" t="s">
         <v>47</v>
       </c>
-      <c r="F68" s="287"/>
-      <c r="G68" s="287"/>
+      <c r="F68" s="290"/>
+      <c r="G68" s="290"/>
       <c r="H68" s="91" t="s">
         <v>47</v>
       </c>
       <c r="I68" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="J68" s="288" t="s">
+      <c r="J68" s="291" t="s">
         <v>47</v>
       </c>
-      <c r="K68" s="289"/>
+      <c r="K68" s="292"/>
       <c r="L68" s="92" t="s">
         <v>47</v>
       </c>
@@ -4283,50 +7048,48 @@
         <v>47</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A69" s="133" t="s">
+    <row r="69" spans="1:14" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="135" t="s">
         <v>72</v>
       </c>
-      <c r="B69" s="134"/>
-      <c r="C69" s="134"/>
-      <c r="D69" s="134"/>
-      <c r="E69" s="149" t="s">
+      <c r="B69" s="136"/>
+      <c r="C69" s="136"/>
+      <c r="D69" s="136"/>
+      <c r="E69" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="F69" s="138"/>
-      <c r="G69" s="138"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J69" s="138"/>
-      <c r="K69" s="138"/>
-      <c r="L69" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="F69" s="140"/>
+      <c r="G69" s="140"/>
+      <c r="H69" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I69" s="3"/>
+      <c r="J69" s="140"/>
+      <c r="K69" s="140"/>
+      <c r="L69" s="3"/>
       <c r="M69" s="3"/>
       <c r="N69" s="8"/>
     </row>
     <row r="70" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="293"/>
-      <c r="B70" s="294"/>
-      <c r="C70" s="294"/>
-      <c r="D70" s="294"/>
-      <c r="E70" s="153" t="s">
+      <c r="A70" s="294"/>
+      <c r="B70" s="295"/>
+      <c r="C70" s="295"/>
+      <c r="D70" s="295"/>
+      <c r="E70" s="155" t="s">
         <v>24</v>
       </c>
-      <c r="F70" s="154"/>
-      <c r="G70" s="154"/>
-      <c r="H70" s="9"/>
-      <c r="I70" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="J70" s="168" t="s">
+      <c r="F70" s="156"/>
+      <c r="G70" s="156"/>
+      <c r="H70" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="I70" s="9"/>
+      <c r="J70" s="170" t="s">
+        <v>175</v>
+      </c>
+      <c r="K70" s="170"/>
+      <c r="L70" s="9" t="s">
         <v>73</v>
-      </c>
-      <c r="K70" s="168"/>
-      <c r="L70" s="9" t="s">
-        <v>24</v>
       </c>
       <c r="M70" s="9" t="s">
         <v>74</v>
@@ -4334,25 +7097,27 @@
       <c r="N70" s="16"/>
     </row>
     <row r="71" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A71" s="133" t="s">
+      <c r="A71" s="135" t="s">
         <v>75</v>
       </c>
-      <c r="B71" s="134"/>
-      <c r="C71" s="134"/>
-      <c r="D71" s="134"/>
-      <c r="E71" s="292" t="s">
+      <c r="B71" s="136"/>
+      <c r="C71" s="136"/>
+      <c r="D71" s="136"/>
+      <c r="E71" s="293" t="s">
         <v>76</v>
       </c>
-      <c r="F71" s="204"/>
-      <c r="G71" s="204"/>
-      <c r="H71" s="12"/>
+      <c r="F71" s="207"/>
+      <c r="G71" s="207"/>
+      <c r="H71" s="12" t="s">
+        <v>76</v>
+      </c>
       <c r="I71" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="J71" s="163" t="s">
+      <c r="J71" s="165" t="s">
         <v>76</v>
       </c>
-      <c r="K71" s="163"/>
+      <c r="K71" s="165"/>
       <c r="L71" s="12" t="s">
         <v>76</v>
       </c>
@@ -4362,67 +7127,71 @@
       <c r="N71" s="94"/>
     </row>
     <row r="72" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="293"/>
-      <c r="B72" s="294"/>
-      <c r="C72" s="294"/>
-      <c r="D72" s="294"/>
-      <c r="E72" s="131"/>
-      <c r="F72" s="132"/>
-      <c r="G72" s="132"/>
+      <c r="A72" s="294"/>
+      <c r="B72" s="295"/>
+      <c r="C72" s="295"/>
+      <c r="D72" s="295"/>
+      <c r="E72" s="133"/>
+      <c r="F72" s="134"/>
+      <c r="G72" s="134"/>
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
-      <c r="J72" s="132"/>
-      <c r="K72" s="132"/>
+      <c r="J72" s="134"/>
+      <c r="K72" s="134"/>
       <c r="L72" s="6"/>
       <c r="M72" s="6"/>
       <c r="N72" s="38"/>
     </row>
     <row r="73" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="212" t="s">
+      <c r="A73" s="215" t="s">
         <v>77</v>
       </c>
-      <c r="B73" s="213"/>
-      <c r="C73" s="213"/>
-      <c r="D73" s="295"/>
-      <c r="E73" s="296" t="s">
+      <c r="B73" s="216"/>
+      <c r="C73" s="216"/>
+      <c r="D73" s="296"/>
+      <c r="E73" s="297" t="s">
         <v>39</v>
       </c>
-      <c r="F73" s="297"/>
-      <c r="G73" s="298"/>
+      <c r="F73" s="298"/>
+      <c r="G73" s="299"/>
       <c r="H73" s="44" t="s">
         <v>39</v>
       </c>
       <c r="I73" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="J73" s="299" t="s">
+      <c r="J73" s="300" t="s">
         <v>39</v>
       </c>
-      <c r="K73" s="298"/>
-      <c r="L73" s="44"/>
+      <c r="K73" s="299"/>
+      <c r="L73" s="44" t="s">
+        <v>39</v>
+      </c>
       <c r="M73" s="44"/>
       <c r="N73" s="95"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="159" t="s">
+    <row r="74" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="161" t="s">
         <v>78</v>
       </c>
-      <c r="B74" s="160"/>
-      <c r="C74" s="160"/>
-      <c r="D74" s="160"/>
-      <c r="E74" s="149" t="s">
+      <c r="B74" s="162"/>
+      <c r="C74" s="162"/>
+      <c r="D74" s="162"/>
+      <c r="E74" s="151" t="s">
         <v>79</v>
       </c>
-      <c r="F74" s="138"/>
-      <c r="G74" s="138"/>
-      <c r="H74" s="3"/>
+      <c r="F74" s="140"/>
+      <c r="G74" s="140"/>
+      <c r="H74" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="I74" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J74" s="138" t="s">
+      <c r="J74" s="140" t="s">
         <v>79</v>
       </c>
-      <c r="K74" s="138"/>
+      <c r="K74" s="140"/>
       <c r="L74" s="3" t="s">
         <v>79</v>
       </c>
@@ -4431,120 +7200,126 @@
       </c>
       <c r="N74" s="31"/>
     </row>
-    <row r="75" spans="1:14" ht="57.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="261"/>
-      <c r="B75" s="262"/>
-      <c r="C75" s="262"/>
-      <c r="D75" s="262"/>
-      <c r="E75" s="153" t="s">
-        <v>102</v>
-      </c>
-      <c r="F75" s="154"/>
-      <c r="G75" s="154"/>
+    <row r="75" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="264"/>
+      <c r="B75" s="265"/>
+      <c r="C75" s="265"/>
+      <c r="D75" s="265"/>
+      <c r="E75" s="155"/>
+      <c r="F75" s="156"/>
+      <c r="G75" s="156"/>
       <c r="H75" s="9"/>
-      <c r="I75" s="9"/>
-      <c r="J75" s="154"/>
-      <c r="K75" s="154"/>
+      <c r="I75" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J75" s="156" t="s">
+        <v>28</v>
+      </c>
+      <c r="K75" s="156"/>
       <c r="L75" s="9"/>
       <c r="M75" s="9"/>
       <c r="N75" s="11"/>
     </row>
-    <row r="76" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A76" s="242" t="s">
+    <row r="76" spans="1:14" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="245" t="s">
         <v>80</v>
       </c>
-      <c r="B76" s="243"/>
-      <c r="C76" s="243"/>
-      <c r="D76" s="263"/>
-      <c r="E76" s="149" t="s">
-        <v>81</v>
-      </c>
-      <c r="F76" s="138"/>
-      <c r="G76" s="138"/>
-      <c r="H76" s="3"/>
+      <c r="B76" s="246"/>
+      <c r="C76" s="246"/>
+      <c r="D76" s="266"/>
+      <c r="E76" s="151" t="s">
+        <v>191</v>
+      </c>
+      <c r="F76" s="140"/>
+      <c r="G76" s="140"/>
+      <c r="H76" s="3" t="s">
+        <v>193</v>
+      </c>
       <c r="I76" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J76" s="138" t="s">
-        <v>117</v>
-      </c>
-      <c r="K76" s="138"/>
+        <v>193</v>
+      </c>
+      <c r="J76" s="140" t="s">
+        <v>193</v>
+      </c>
+      <c r="K76" s="140"/>
       <c r="L76" s="3" t="s">
-        <v>117</v>
+        <v>193</v>
       </c>
       <c r="M76" s="3"/>
       <c r="N76" s="96"/>
     </row>
     <row r="77" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="245"/>
-      <c r="B77" s="246"/>
-      <c r="C77" s="246"/>
-      <c r="D77" s="284"/>
-      <c r="E77" s="153"/>
-      <c r="F77" s="154"/>
-      <c r="G77" s="154"/>
+      <c r="A77" s="248"/>
+      <c r="B77" s="249"/>
+      <c r="C77" s="249"/>
+      <c r="D77" s="287"/>
+      <c r="E77" s="155"/>
+      <c r="F77" s="156"/>
+      <c r="G77" s="156"/>
       <c r="H77" s="9"/>
       <c r="I77" s="97"/>
-      <c r="J77" s="154"/>
-      <c r="K77" s="154"/>
+      <c r="J77" s="156"/>
+      <c r="K77" s="156"/>
       <c r="L77" s="9"/>
       <c r="M77" s="9"/>
       <c r="N77" s="98"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="133" t="s">
+      <c r="A78" s="135" t="s">
         <v>82</v>
       </c>
-      <c r="B78" s="134"/>
-      <c r="C78" s="134"/>
-      <c r="D78" s="134"/>
-      <c r="E78" s="266"/>
-      <c r="F78" s="267"/>
-      <c r="G78" s="260"/>
+      <c r="B78" s="136"/>
+      <c r="C78" s="136"/>
+      <c r="D78" s="136"/>
+      <c r="E78" s="269"/>
+      <c r="F78" s="270"/>
+      <c r="G78" s="263"/>
       <c r="H78" s="12"/>
       <c r="I78" s="12"/>
-      <c r="J78" s="259"/>
-      <c r="K78" s="260"/>
+      <c r="J78" s="262"/>
+      <c r="K78" s="263"/>
       <c r="L78" s="12"/>
       <c r="M78" s="12"/>
       <c r="N78" s="14"/>
     </row>
     <row r="79" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="293"/>
-      <c r="B79" s="294"/>
-      <c r="C79" s="294"/>
-      <c r="D79" s="294"/>
-      <c r="E79" s="252"/>
-      <c r="F79" s="253"/>
-      <c r="G79" s="254"/>
+      <c r="A79" s="294"/>
+      <c r="B79" s="295"/>
+      <c r="C79" s="295"/>
+      <c r="D79" s="295"/>
+      <c r="E79" s="255"/>
+      <c r="F79" s="256"/>
+      <c r="G79" s="257"/>
       <c r="H79" s="68"/>
       <c r="I79" s="68"/>
-      <c r="J79" s="154"/>
-      <c r="K79" s="154"/>
+      <c r="J79" s="156"/>
+      <c r="K79" s="156"/>
       <c r="L79" s="68"/>
       <c r="M79" s="69"/>
       <c r="N79" s="70"/>
     </row>
-    <row r="80" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A80" s="173" t="s">
+    <row r="80" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A80" s="175" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="174"/>
-      <c r="C80" s="174"/>
-      <c r="D80" s="175"/>
-      <c r="E80" s="149" t="s">
+      <c r="B80" s="176"/>
+      <c r="C80" s="176"/>
+      <c r="D80" s="177"/>
+      <c r="E80" s="151" t="s">
         <v>49</v>
       </c>
-      <c r="F80" s="138"/>
-      <c r="G80" s="138"/>
-      <c r="H80" s="99"/>
+      <c r="F80" s="140"/>
+      <c r="G80" s="140"/>
+      <c r="H80" s="99" t="s">
+        <v>49</v>
+      </c>
       <c r="I80" s="99" t="s">
         <v>49</v>
       </c>
-      <c r="J80" s="300" t="s">
+      <c r="J80" s="301" t="s">
         <v>49</v>
       </c>
-      <c r="K80" s="300"/>
+      <c r="K80" s="301"/>
       <c r="L80" s="99" t="s">
         <v>49</v>
       </c>
@@ -4554,41 +7329,43 @@
       <c r="N80" s="64"/>
     </row>
     <row r="81" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="207"/>
-      <c r="B81" s="208"/>
-      <c r="C81" s="208"/>
-      <c r="D81" s="209"/>
-      <c r="E81" s="305"/>
-      <c r="F81" s="306"/>
-      <c r="G81" s="306"/>
+      <c r="A81" s="210"/>
+      <c r="B81" s="211"/>
+      <c r="C81" s="211"/>
+      <c r="D81" s="212"/>
+      <c r="E81" s="306"/>
+      <c r="F81" s="307"/>
+      <c r="G81" s="307"/>
       <c r="H81" s="69"/>
       <c r="I81" s="69"/>
-      <c r="J81" s="306"/>
-      <c r="K81" s="306"/>
+      <c r="J81" s="307"/>
+      <c r="K81" s="307"/>
       <c r="L81" s="69"/>
       <c r="M81" s="69"/>
       <c r="N81" s="70"/>
     </row>
     <row r="82" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A82" s="173" t="s">
+      <c r="A82" s="175" t="s">
         <v>85</v>
       </c>
-      <c r="B82" s="174"/>
-      <c r="C82" s="174"/>
-      <c r="D82" s="175"/>
-      <c r="E82" s="149" t="s">
+      <c r="B82" s="176"/>
+      <c r="C82" s="176"/>
+      <c r="D82" s="177"/>
+      <c r="E82" s="151" t="s">
         <v>86</v>
       </c>
-      <c r="F82" s="138"/>
-      <c r="G82" s="138"/>
-      <c r="H82" s="3"/>
+      <c r="F82" s="140"/>
+      <c r="G82" s="140"/>
+      <c r="H82" s="3" t="s">
+        <v>86</v>
+      </c>
       <c r="I82" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="J82" s="138" t="s">
+      <c r="J82" s="140" t="s">
         <v>86</v>
       </c>
-      <c r="K82" s="138"/>
+      <c r="K82" s="140"/>
       <c r="L82" s="3" t="s">
         <v>87</v>
       </c>
@@ -4596,73 +7373,77 @@
       <c r="N82" s="100"/>
     </row>
     <row r="83" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="207"/>
-      <c r="B83" s="208"/>
-      <c r="C83" s="208"/>
-      <c r="D83" s="209"/>
-      <c r="E83" s="301" t="s">
+      <c r="A83" s="210"/>
+      <c r="B83" s="211"/>
+      <c r="C83" s="211"/>
+      <c r="D83" s="212"/>
+      <c r="E83" s="302" t="s">
         <v>87</v>
       </c>
-      <c r="F83" s="283"/>
-      <c r="G83" s="283"/>
-      <c r="H83" s="68"/>
+      <c r="F83" s="286"/>
+      <c r="G83" s="286"/>
+      <c r="H83" s="68" t="s">
+        <v>87</v>
+      </c>
       <c r="I83" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="J83" s="132" t="s">
+      <c r="J83" s="134" t="s">
         <v>87</v>
       </c>
-      <c r="K83" s="132"/>
+      <c r="K83" s="134"/>
       <c r="L83" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="M83" s="6"/>
       <c r="N83" s="70"/>
     </row>
     <row r="84" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="212" t="s">
+      <c r="A84" s="215" t="s">
         <v>88</v>
       </c>
-      <c r="B84" s="213"/>
-      <c r="C84" s="213"/>
-      <c r="D84" s="295"/>
-      <c r="E84" s="302" t="s">
+      <c r="B84" s="216"/>
+      <c r="C84" s="216"/>
+      <c r="D84" s="296"/>
+      <c r="E84" s="303" t="s">
         <v>39</v>
       </c>
-      <c r="F84" s="303"/>
-      <c r="G84" s="304"/>
+      <c r="F84" s="304"/>
+      <c r="G84" s="305"/>
       <c r="H84" s="101" t="s">
         <v>39</v>
       </c>
       <c r="I84" s="101"/>
-      <c r="J84" s="217" t="s">
-        <v>138</v>
-      </c>
-      <c r="K84" s="216"/>
+      <c r="J84" s="220" t="s">
+        <v>135</v>
+      </c>
+      <c r="K84" s="219"/>
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
       <c r="N84" s="102"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A85" s="242" t="s">
+      <c r="A85" s="245" t="s">
         <v>90</v>
       </c>
-      <c r="B85" s="243"/>
-      <c r="C85" s="243"/>
-      <c r="D85" s="263"/>
-      <c r="E85" s="292" t="s">
+      <c r="B85" s="246"/>
+      <c r="C85" s="246"/>
+      <c r="D85" s="266"/>
+      <c r="E85" s="293" t="s">
         <v>91</v>
       </c>
-      <c r="F85" s="204"/>
-      <c r="G85" s="204"/>
-      <c r="H85" s="13"/>
+      <c r="F85" s="207"/>
+      <c r="G85" s="207"/>
+      <c r="H85" s="13" t="s">
+        <v>91</v>
+      </c>
       <c r="I85" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="J85" s="204" t="s">
+      <c r="J85" s="207" t="s">
         <v>91</v>
       </c>
-      <c r="K85" s="204"/>
+      <c r="K85" s="207"/>
       <c r="L85" s="13" t="s">
         <v>91</v>
       </c>
@@ -4670,45 +7451,49 @@
       <c r="N85" s="104"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A86" s="197"/>
-      <c r="B86" s="198"/>
-      <c r="C86" s="198"/>
-      <c r="D86" s="199"/>
-      <c r="E86" s="200" t="s">
+      <c r="A86" s="200"/>
+      <c r="B86" s="201"/>
+      <c r="C86" s="201"/>
+      <c r="D86" s="202"/>
+      <c r="E86" s="203" t="s">
         <v>92</v>
       </c>
-      <c r="F86" s="181"/>
-      <c r="G86" s="181"/>
-      <c r="H86" s="105"/>
+      <c r="F86" s="183"/>
+      <c r="G86" s="183"/>
+      <c r="H86" s="105" t="s">
+        <v>136</v>
+      </c>
       <c r="I86" s="105" t="s">
         <v>92</v>
       </c>
-      <c r="J86" s="181" t="s">
+      <c r="J86" s="183" t="s">
         <v>95</v>
       </c>
-      <c r="K86" s="181"/>
+      <c r="K86" s="183"/>
       <c r="L86" s="105" t="s">
         <v>92</v>
       </c>
       <c r="M86" s="6"/>
       <c r="N86" s="106"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A87" s="197"/>
-      <c r="B87" s="198"/>
-      <c r="C87" s="198"/>
-      <c r="D87" s="199"/>
-      <c r="E87" s="307" t="s">
+    <row r="87" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A87" s="200"/>
+      <c r="B87" s="201"/>
+      <c r="C87" s="201"/>
+      <c r="D87" s="202"/>
+      <c r="E87" s="308" t="s">
         <v>93</v>
       </c>
-      <c r="F87" s="308"/>
-      <c r="G87" s="308"/>
-      <c r="H87" s="34"/>
+      <c r="F87" s="309"/>
+      <c r="G87" s="309"/>
+      <c r="H87" s="34" t="s">
+        <v>94</v>
+      </c>
       <c r="I87" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="J87" s="181"/>
-      <c r="K87" s="181"/>
+      <c r="J87" s="183"/>
+      <c r="K87" s="183"/>
       <c r="L87" s="34" t="s">
         <v>93</v>
       </c>
@@ -4716,21 +7501,17 @@
       <c r="N87" s="108"/>
     </row>
     <row r="88" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="207"/>
-      <c r="B88" s="208"/>
-      <c r="C88" s="208"/>
-      <c r="D88" s="209"/>
-      <c r="E88" s="301" t="s">
-        <v>139</v>
-      </c>
-      <c r="F88" s="283"/>
-      <c r="G88" s="283"/>
+      <c r="A88" s="210"/>
+      <c r="B88" s="211"/>
+      <c r="C88" s="211"/>
+      <c r="D88" s="212"/>
+      <c r="E88" s="302"/>
+      <c r="F88" s="286"/>
+      <c r="G88" s="286"/>
       <c r="H88" s="69"/>
-      <c r="I88" s="68" t="s">
-        <v>94</v>
-      </c>
-      <c r="J88" s="132"/>
-      <c r="K88" s="132"/>
+      <c r="I88" s="68"/>
+      <c r="J88" s="134"/>
+      <c r="K88" s="134"/>
       <c r="L88" s="87" t="s">
         <v>94</v>
       </c>
@@ -4738,250 +7519,262 @@
       <c r="N88" s="70"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A89" s="133" t="s">
+      <c r="A89" s="135" t="s">
         <v>96</v>
       </c>
-      <c r="B89" s="134"/>
-      <c r="C89" s="134"/>
-      <c r="D89" s="134"/>
-      <c r="E89" s="149"/>
-      <c r="F89" s="138"/>
-      <c r="G89" s="138"/>
+      <c r="B89" s="136"/>
+      <c r="C89" s="136"/>
+      <c r="D89" s="136"/>
+      <c r="E89" s="151"/>
+      <c r="F89" s="140"/>
+      <c r="G89" s="140"/>
       <c r="H89" s="71"/>
       <c r="I89" s="3"/>
-      <c r="J89" s="138"/>
-      <c r="K89" s="138"/>
+      <c r="J89" s="140"/>
+      <c r="K89" s="140"/>
       <c r="L89" s="28"/>
       <c r="M89" s="28"/>
       <c r="N89" s="29"/>
     </row>
-    <row r="90" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="261"/>
-      <c r="B90" s="262"/>
-      <c r="C90" s="262"/>
-      <c r="D90" s="262"/>
-      <c r="E90" s="153"/>
-      <c r="F90" s="154"/>
-      <c r="G90" s="154"/>
+    <row r="90" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="264"/>
+      <c r="B90" s="265"/>
+      <c r="C90" s="265"/>
+      <c r="D90" s="265"/>
+      <c r="E90" s="155" t="s">
+        <v>120</v>
+      </c>
+      <c r="F90" s="156"/>
+      <c r="G90" s="156"/>
       <c r="H90" s="25"/>
-      <c r="I90" s="9" t="s">
+      <c r="I90" s="9"/>
+      <c r="J90" s="156" t="s">
         <v>18</v>
       </c>
-      <c r="J90" s="154"/>
-      <c r="K90" s="154"/>
-      <c r="L90" s="21"/>
+      <c r="K90" s="156"/>
+      <c r="L90" s="21" t="s">
+        <v>18</v>
+      </c>
       <c r="M90" s="9" t="s">
         <v>20</v>
       </c>
       <c r="N90" s="109"/>
     </row>
     <row r="91" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="155" t="s">
+      <c r="A91" s="157" t="s">
         <v>97</v>
       </c>
-      <c r="B91" s="156"/>
-      <c r="C91" s="156"/>
-      <c r="D91" s="156"/>
-      <c r="E91" s="309" t="s">
+      <c r="B91" s="158"/>
+      <c r="C91" s="158"/>
+      <c r="D91" s="158"/>
+      <c r="E91" s="310" t="s">
         <v>39</v>
       </c>
-      <c r="F91" s="310"/>
-      <c r="G91" s="230"/>
+      <c r="F91" s="311"/>
+      <c r="G91" s="233"/>
       <c r="H91" s="110" t="s">
         <v>39</v>
       </c>
       <c r="I91" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="J91" s="229" t="s">
+      <c r="J91" s="232" t="s">
         <v>39</v>
       </c>
-      <c r="K91" s="230"/>
+      <c r="K91" s="233"/>
       <c r="L91" s="19" t="s">
         <v>89</v>
       </c>
       <c r="M91" s="19"/>
       <c r="N91" s="111"/>
     </row>
-    <row r="92" spans="1:14" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="133" t="s">
+    <row r="92" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A92" s="135" t="s">
         <v>98</v>
       </c>
-      <c r="B92" s="134"/>
-      <c r="C92" s="134"/>
-      <c r="D92" s="134"/>
-      <c r="E92" s="135" t="s">
+      <c r="B92" s="136"/>
+      <c r="C92" s="136"/>
+      <c r="D92" s="136"/>
+      <c r="E92" s="137" t="s">
         <v>99</v>
       </c>
-      <c r="F92" s="136"/>
-      <c r="G92" s="137"/>
-      <c r="H92" s="62"/>
+      <c r="F92" s="138"/>
+      <c r="G92" s="139"/>
+      <c r="H92" s="62" t="s">
+        <v>186</v>
+      </c>
       <c r="I92" s="62" t="s">
-        <v>99</v>
-      </c>
-      <c r="J92" s="201" t="s">
-        <v>28</v>
-      </c>
-      <c r="K92" s="137"/>
+        <v>176</v>
+      </c>
+      <c r="J92" s="204" t="s">
+        <v>176</v>
+      </c>
+      <c r="K92" s="139"/>
       <c r="L92" s="3"/>
       <c r="M92" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="N92" s="112"/>
     </row>
-    <row r="93" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="150"/>
-      <c r="B93" s="151"/>
-      <c r="C93" s="151"/>
-      <c r="D93" s="151"/>
-      <c r="E93" s="210" t="s">
-        <v>100</v>
-      </c>
-      <c r="F93" s="211"/>
-      <c r="G93" s="203"/>
-      <c r="H93" s="97"/>
+    <row r="93" spans="1:14" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="152"/>
+      <c r="B93" s="153"/>
+      <c r="C93" s="153"/>
+      <c r="D93" s="153"/>
+      <c r="E93" s="213"/>
+      <c r="F93" s="214"/>
+      <c r="G93" s="206"/>
+      <c r="H93" s="97" t="s">
+        <v>28</v>
+      </c>
       <c r="I93" s="10"/>
-      <c r="J93" s="154"/>
-      <c r="K93" s="154"/>
+      <c r="J93" s="156"/>
+      <c r="K93" s="156"/>
       <c r="L93" s="9"/>
       <c r="M93" s="9"/>
       <c r="N93" s="109"/>
     </row>
-    <row r="94" spans="1:14" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="242" t="s">
+    <row r="94" spans="1:14" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="245" t="s">
         <v>101</v>
       </c>
-      <c r="B94" s="243"/>
-      <c r="C94" s="243"/>
-      <c r="D94" s="263"/>
-      <c r="E94" s="149" t="s">
-        <v>147</v>
-      </c>
-      <c r="F94" s="138"/>
-      <c r="G94" s="138"/>
+      <c r="B94" s="246"/>
+      <c r="C94" s="246"/>
+      <c r="D94" s="266"/>
+      <c r="E94" s="151" t="s">
+        <v>190</v>
+      </c>
+      <c r="F94" s="140"/>
+      <c r="G94" s="140"/>
       <c r="H94" s="24"/>
       <c r="I94" s="3"/>
-      <c r="J94" s="138"/>
-      <c r="K94" s="138"/>
+      <c r="J94" s="140"/>
+      <c r="K94" s="140"/>
       <c r="L94" s="3"/>
       <c r="M94" s="3"/>
       <c r="N94" s="59"/>
     </row>
-    <row r="95" spans="1:14" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="197"/>
-      <c r="B95" s="198"/>
-      <c r="C95" s="198"/>
-      <c r="D95" s="199"/>
-      <c r="E95" s="200" t="s">
-        <v>143</v>
-      </c>
-      <c r="F95" s="181"/>
-      <c r="G95" s="181"/>
-      <c r="H95" s="32"/>
+    <row r="95" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A95" s="200"/>
+      <c r="B95" s="201"/>
+      <c r="C95" s="201"/>
+      <c r="D95" s="202"/>
+      <c r="E95" s="203" t="s">
+        <v>102</v>
+      </c>
+      <c r="F95" s="183"/>
+      <c r="G95" s="183"/>
+      <c r="H95" s="32" t="s">
+        <v>102</v>
+      </c>
       <c r="I95" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="J95" s="181" t="s">
+      <c r="J95" s="183" t="s">
         <v>102</v>
       </c>
-      <c r="K95" s="181"/>
+      <c r="K95" s="183"/>
       <c r="L95" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="M95" s="32"/>
+      <c r="M95" s="32" t="s">
+        <v>188</v>
+      </c>
       <c r="N95" s="33"/>
     </row>
-    <row r="96" spans="1:14" ht="67.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="245"/>
-      <c r="B96" s="246"/>
-      <c r="C96" s="246"/>
-      <c r="D96" s="284"/>
-      <c r="E96" s="131"/>
-      <c r="F96" s="132"/>
-      <c r="G96" s="132"/>
-      <c r="H96" s="6"/>
+    <row r="96" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="248"/>
+      <c r="B96" s="249"/>
+      <c r="C96" s="249"/>
+      <c r="D96" s="287"/>
+      <c r="E96" s="133"/>
+      <c r="F96" s="134"/>
+      <c r="G96" s="134"/>
+      <c r="H96" s="6" t="s">
+        <v>177</v>
+      </c>
       <c r="I96" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="J96" s="132" t="s">
-        <v>149</v>
-      </c>
-      <c r="K96" s="132"/>
+        <v>187</v>
+      </c>
+      <c r="J96" s="134"/>
+      <c r="K96" s="134"/>
       <c r="L96" s="6" t="s">
         <v>8</v>
       </c>
       <c r="M96" s="6"/>
       <c r="N96" s="70"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A97" s="320" t="s">
+    <row r="97" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A97" s="321" t="s">
         <v>103</v>
       </c>
-      <c r="B97" s="321"/>
-      <c r="C97" s="321"/>
-      <c r="D97" s="321"/>
-      <c r="E97" s="322"/>
-      <c r="F97" s="323"/>
-      <c r="G97" s="323"/>
+      <c r="B97" s="322"/>
+      <c r="C97" s="322"/>
+      <c r="D97" s="322"/>
+      <c r="E97" s="323"/>
+      <c r="F97" s="324"/>
+      <c r="G97" s="324"/>
       <c r="H97" s="113"/>
       <c r="I97" s="113"/>
-      <c r="J97" s="323"/>
-      <c r="K97" s="323"/>
+      <c r="J97" s="324"/>
+      <c r="K97" s="324"/>
       <c r="L97" s="3"/>
-      <c r="M97" s="3"/>
+      <c r="M97" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="N97" s="8"/>
     </row>
-    <row r="98" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="324"/>
-      <c r="B98" s="325"/>
-      <c r="C98" s="325"/>
-      <c r="D98" s="325"/>
-      <c r="E98" s="326" t="s">
+    <row r="98" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="325"/>
+      <c r="B98" s="326"/>
+      <c r="C98" s="326"/>
+      <c r="D98" s="326"/>
+      <c r="E98" s="327" t="s">
         <v>3</v>
       </c>
-      <c r="F98" s="327"/>
-      <c r="G98" s="327"/>
+      <c r="F98" s="328"/>
+      <c r="G98" s="328"/>
       <c r="H98" s="114" t="s">
         <v>3</v>
       </c>
       <c r="I98" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="J98" s="327" t="s">
+      <c r="J98" s="328" t="s">
         <v>3</v>
       </c>
-      <c r="K98" s="327"/>
+      <c r="K98" s="328"/>
       <c r="L98" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="M98" s="58" t="s">
-        <v>3</v>
-      </c>
-      <c r="N98" s="115" t="s">
-        <v>3</v>
-      </c>
+      <c r="M98" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N98" s="129"/>
     </row>
     <row r="100" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="101" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="311" t="s">
+      <c r="A101" s="312" t="s">
         <v>104</v>
       </c>
-      <c r="B101" s="312"/>
-      <c r="C101" s="312"/>
-      <c r="D101" s="312"/>
-      <c r="E101" s="313" t="s">
+      <c r="B101" s="313"/>
+      <c r="C101" s="313"/>
+      <c r="D101" s="313"/>
+      <c r="E101" s="314" t="s">
         <v>105</v>
       </c>
-      <c r="F101" s="314"/>
-      <c r="G101" s="315"/>
-      <c r="H101" s="116"/>
+      <c r="F101" s="315"/>
+      <c r="G101" s="316"/>
+      <c r="H101" s="116" t="s">
+        <v>105</v>
+      </c>
       <c r="I101" s="116" t="s">
         <v>105</v>
       </c>
-      <c r="J101" s="313" t="s">
+      <c r="J101" s="314" t="s">
         <v>105</v>
       </c>
-      <c r="K101" s="315"/>
+      <c r="K101" s="316"/>
       <c r="L101" s="117" t="s">
         <v>105</v>
       </c>
@@ -4989,25 +7782,25 @@
       <c r="N101" s="118"/>
     </row>
     <row r="102" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="316" t="s">
+      <c r="A102" s="317" t="s">
         <v>106</v>
       </c>
-      <c r="B102" s="317"/>
-      <c r="C102" s="317"/>
-      <c r="D102" s="318"/>
-      <c r="E102" s="319" t="s">
-        <v>151</v>
-      </c>
-      <c r="F102" s="314"/>
-      <c r="G102" s="315"/>
-      <c r="H102" s="119"/>
+      <c r="B102" s="318"/>
+      <c r="C102" s="318"/>
+      <c r="D102" s="319"/>
+      <c r="E102" s="320" t="s">
+        <v>194</v>
+      </c>
+      <c r="F102" s="315"/>
+      <c r="G102" s="316"/>
+      <c r="H102" s="119" t="s">
+        <v>107</v>
+      </c>
       <c r="I102" s="119" t="s">
         <v>107</v>
       </c>
-      <c r="J102" s="319" t="s">
-        <v>107</v>
-      </c>
-      <c r="K102" s="315"/>
+      <c r="J102" s="320"/>
+      <c r="K102" s="316"/>
       <c r="L102" s="119" t="s">
         <v>107</v>
       </c>

--- a/data/tyovuorot_2026.xlsx
+++ b/data/tyovuorot_2026.xlsx
@@ -972,7 +972,7 @@
     <t>KE 11.2</t>
   </si>
   <si>
-    <t>T0 12.2</t>
+    <t>TO 12.2</t>
   </si>
   <si>
     <t>PE 13.2</t>
@@ -1076,7 +1076,7 @@
     <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="59" formatCode="&quot;Id&quot;yyyy&quot;ntifi&quot;yyyy&quot;r - LastNam&quot;yyyy&quot; , FirstNam&quot;yyyy"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1111,12 +1111,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Arial"/>
@@ -1133,23 +1127,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="11"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-      <color indexed="12"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b val="1"/>
       <sz val="11"/>
       <color indexed="11"/>
       <name val="Arial"/>
@@ -2014,32 +1991,494 @@
     <xf numFmtId="49" fontId="5" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="27" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="28" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="30" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="31" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="34" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="35" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="36" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="4" fillId="2" borderId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="34" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="38" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="6" fillId="2" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="6" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="6" fillId="2" borderId="27" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="27" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="6" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="6" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="6" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="40" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="41" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="38" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="44" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="45" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="46" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="47" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="46" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="6" fillId="2" borderId="35" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="6" fillId="2" borderId="36" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="6" fillId="2" borderId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="6" fillId="2" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="6" fillId="2" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="6" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="44" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="45" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -2047,22 +2486,157 @@
     <xf numFmtId="1" fontId="7" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="38" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="27" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="50" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="51" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="52" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="54" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="58" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="56" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="57" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="1" fontId="8" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="2" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -2071,215 +2645,59 @@
     <xf numFmtId="1" fontId="7" fillId="2" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="34" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="38" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="27" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="27" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="28" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="30" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="31" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="32" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="34" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="35" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="36" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="2" borderId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="34" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="38" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="7" fillId="2" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="7" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="7" fillId="2" borderId="27" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="27" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="7" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="7" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="7" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -2290,451 +2708,10 @@
     <xf numFmtId="1" fontId="7" fillId="2" borderId="40" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="41" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="38" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="42" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="43" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="44" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="45" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="46" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="47" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" borderId="46" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="7" fillId="2" borderId="35" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="7" fillId="2" borderId="36" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="7" fillId="2" borderId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="7" fillId="2" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="7" fillId="2" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="7" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="44" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="45" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="48" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="38" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="2" borderId="27" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" borderId="49" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" borderId="50" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" borderId="51" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="52" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="53" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="54" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="50" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="55" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="56" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="57" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" borderId="58" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" borderId="56" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" borderId="57" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="2" borderId="34" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="2" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="38" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="2" borderId="39" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="27" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="2" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="40" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2957,17 +2934,17 @@
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="19050" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -2994,10 +2971,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Aptos Narrow"/>
-            <a:ea typeface="Aptos Narrow"/>
-            <a:cs typeface="Aptos Narrow"/>
-            <a:sym typeface="Aptos Narrow"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -3236,12 +3213,12 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="19050" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -3518,7 +3495,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -3545,10 +3522,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Aptos Narrow"/>
-            <a:ea typeface="Aptos Narrow"/>
-            <a:cs typeface="Aptos Narrow"/>
-            <a:sym typeface="Aptos Narrow"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">

--- a/data/tyovuorot_2026.xlsx
+++ b/data/tyovuorot_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solemofi-my.sharepoint.com/personal/pirjo_kleemola_sol_fi/Documents/Vuorolistat/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4975" documentId="8_{F7973BC1-41AE-4E6A-B0A3-B34DE794A113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8A86CD3-39F9-411A-B358-9502669148E0}"/>
+  <xr:revisionPtr revIDLastSave="5408" documentId="8_{F7973BC1-41AE-4E6A-B0A3-B34DE794A113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95227877-78E8-420D-AB7F-01404BEF1ABB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="6" activeTab="16" xr2:uid="{72DDB042-8082-4351-9446-F508A0968C0B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="7" activeTab="17" xr2:uid="{72DDB042-8082-4351-9446-F508A0968C0B}"/>
   </bookViews>
   <sheets>
     <sheet name="vko 2" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,7 @@
     <sheet name="vko 16" sheetId="15" r:id="rId15"/>
     <sheet name="vko 17" sheetId="16" r:id="rId16"/>
     <sheet name="vko 18" sheetId="17" r:id="rId17"/>
+    <sheet name="vko 19" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5917" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6298" uniqueCount="741">
   <si>
     <t>Ashim Acharya</t>
   </si>
@@ -2101,9 +2102,6 @@
     <t>Muut ryhmä tiimipalaveri Gamlas Hem klo 11-13</t>
   </si>
   <si>
-    <t>CM Kaakkuri myymälä ja desinfiointi (liha)</t>
-  </si>
-  <si>
     <t>Esperi Teppola huoneita</t>
   </si>
   <si>
@@ -2147,6 +2145,138 @@
   </si>
   <si>
     <t>CM Rusko klo 5 asiakaskahvio nurkat, reunat, pöytien aluset kuivahöyrylaite</t>
+  </si>
+  <si>
+    <t>CM Rusko hevin kivenhoito klo 5-</t>
+  </si>
+  <si>
+    <t>Velimark käynti</t>
+  </si>
+  <si>
+    <t>vko 18</t>
+  </si>
+  <si>
+    <t>vko 19</t>
+  </si>
+  <si>
+    <t>MA 4.5</t>
+  </si>
+  <si>
+    <t>TI 5.5</t>
+  </si>
+  <si>
+    <t>KE 6.5</t>
+  </si>
+  <si>
+    <t>TO 7.5</t>
+  </si>
+  <si>
+    <t>PE 8.5</t>
+  </si>
+  <si>
+    <t>LA 9.5</t>
+  </si>
+  <si>
+    <t>SU 10.5</t>
+  </si>
+  <si>
+    <t>Milla Rytkönen</t>
+  </si>
+  <si>
+    <t>Inga Puurunen</t>
+  </si>
+  <si>
+    <t>Sanna Leinonen</t>
+  </si>
+  <si>
+    <t>CM Rusko klo 17- uusien alueiden katsominen</t>
+  </si>
+  <si>
+    <t>klo 8-15.30</t>
+  </si>
+  <si>
+    <t>Bauhaus välilasien pesut, ulkoa puhdistus ikkunat ja lattia leikkimökit ja huvimaja</t>
+  </si>
+  <si>
+    <t>Bauhaus ulkoikkunoiden ja tuulikkaappien ikkunoiden pesut Raimon kanssa</t>
+  </si>
+  <si>
+    <t>CM Kaakkuri tuulikaappi ja niiden ikkunat klo 5- Raimon kanssa</t>
+  </si>
+  <si>
+    <t>HalpaHalli Haukipudas Millan kanssa</t>
+  </si>
+  <si>
+    <t>Wetteri Äimäkuja 3 Skoda ja Mersu matot</t>
+  </si>
+  <si>
+    <t>klo 9 näyttö</t>
+  </si>
+  <si>
+    <t>CM Raksila lihakylmiö lattia ja asiakaskahvio lattia Raimon kanssa</t>
+  </si>
+  <si>
+    <t>CM Raksila eineskylmiö, eineskeittiö ja tiskikäytävä</t>
+  </si>
+  <si>
+    <t>CM Rusko klo 17 uusien alueiden läpikäynti</t>
+  </si>
+  <si>
+    <t>CM Rusko tuulikaappi pp ja ikkunoiden pesuja Mirjan kanssa koko päivä klo 5-</t>
+  </si>
+  <si>
+    <t>CM Rusko tuulikaappi pp ja ikkunoiden pesuja Pihlan kanssa koko päivä klo 5-</t>
+  </si>
+  <si>
+    <t>CM Rusko klo 17 uusien alueiden katsominen</t>
+  </si>
+  <si>
+    <t>työsopimus klo 10.30-</t>
+  </si>
+  <si>
+    <t>SOL In koulutus klo 14-16</t>
+  </si>
+  <si>
+    <t>klo 10 työsopimus</t>
+  </si>
+  <si>
+    <t>TerraPatris opettelu</t>
+  </si>
+  <si>
+    <t>CM Rusko aamuvuoro, myös Sushi</t>
+  </si>
+  <si>
+    <t>CM Rusko aamuvuora</t>
+  </si>
+  <si>
+    <t>HalpaHalli Haukipudas opettelu</t>
+  </si>
+  <si>
+    <t>CM Kaakkuri tuulikaappi ja ikkunat tuulikaapin klo 5 Fuadin kanssa</t>
+  </si>
+  <si>
+    <t>CM Kaakkuri tuulikaappi ja sen ikkunat klo 5- Fuadin kanssa</t>
+  </si>
+  <si>
+    <t>Velimarkilta Kaakkuriin konetiskiainetta 3*20l</t>
+  </si>
+  <si>
+    <t>CM Raksila lihakylmiö lattia ja asiakaskahvio lattia Nadjan kanssa</t>
+  </si>
+  <si>
+    <t>Bauhaus ulkoikkunat ja tuulikaappien ikkunat myös sisältä molemmat Joelin kanssa</t>
+  </si>
+  <si>
+    <t>CM Rusko hevi/terminaalikylmiö, ja mehukoneen ja kurkkupurkkien taukset</t>
+  </si>
+  <si>
+    <t>CM Rusko aamuvuoro loppuun, myös maitokylmiö etureuna kunnolla</t>
+  </si>
+  <si>
+    <t>CM Rusko Fazer leipomo ja myymälä klo 17.40- myös verkkokaupan kylmiö lattia</t>
+  </si>
+  <si>
+    <t>CM Rusko leipäalue lattianpesua</t>
   </si>
 </sst>
 </file>
@@ -2296,7 +2426,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="69">
+  <borders count="72">
     <border>
       <left/>
       <right/>
@@ -3140,11 +3270,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="488">
+  <cellXfs count="505">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -4531,6 +4696,12 @@
     <xf numFmtId="164" fontId="6" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4549,11 +4720,56 @@
     <xf numFmtId="164" fontId="8" fillId="3" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -23366,8 +23582,8 @@
       <c r="C12" s="319"/>
       <c r="D12" s="319"/>
       <c r="E12" s="378"/>
-      <c r="F12" s="480"/>
-      <c r="G12" s="480"/>
+      <c r="F12" s="482"/>
+      <c r="G12" s="482"/>
       <c r="H12" s="190"/>
       <c r="I12" s="4"/>
       <c r="J12" s="232"/>
@@ -23376,7 +23592,7 @@
       <c r="M12" s="24"/>
       <c r="N12" s="191"/>
     </row>
-    <row r="13" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="350"/>
       <c r="B13" s="351"/>
       <c r="C13" s="351"/>
@@ -23491,7 +23707,7 @@
       </c>
       <c r="I17" s="12"/>
       <c r="J17" s="286" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="K17" s="286"/>
       <c r="L17" s="12"/>
@@ -23791,11 +24007,11 @@
       <c r="B29" s="240"/>
       <c r="C29" s="240"/>
       <c r="D29" s="240"/>
-      <c r="E29" s="486" t="s">
+      <c r="E29" s="480" t="s">
         <v>641</v>
       </c>
-      <c r="F29" s="487"/>
-      <c r="G29" s="487"/>
+      <c r="F29" s="481"/>
+      <c r="G29" s="481"/>
       <c r="H29" s="48" t="s">
         <v>655</v>
       </c>
@@ -24397,7 +24613,7 @@
       </c>
       <c r="K56" s="286"/>
       <c r="L56" s="3" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="M56" s="3"/>
       <c r="N56" s="49"/>
@@ -24586,7 +24802,7 @@
       </c>
       <c r="N65" s="78"/>
     </row>
-    <row r="66" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="250"/>
       <c r="B66" s="251"/>
       <c r="C66" s="251"/>
@@ -25707,7 +25923,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="384" t="s">
-        <v>643</v>
+        <v>699</v>
       </c>
       <c r="B1" s="385"/>
       <c r="C1" s="385"/>
@@ -25865,7 +26081,7 @@
         <v>32</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="N6" s="31"/>
     </row>
@@ -25906,9 +26122,7 @@
       <c r="H8" s="44" t="s">
         <v>679</v>
       </c>
-      <c r="I8" s="44" t="s">
-        <v>8</v>
-      </c>
+      <c r="I8" s="44"/>
       <c r="J8" s="355" t="s">
         <v>680</v>
       </c>
@@ -25999,8 +26213,8 @@
       <c r="C12" s="319"/>
       <c r="D12" s="319"/>
       <c r="E12" s="378"/>
-      <c r="F12" s="480"/>
-      <c r="G12" s="480"/>
+      <c r="F12" s="482"/>
+      <c r="G12" s="482"/>
       <c r="H12" s="190"/>
       <c r="I12" s="4"/>
       <c r="J12" s="232"/>
@@ -26059,7 +26273,7 @@
       </c>
       <c r="N14" s="27"/>
     </row>
-    <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="284" t="s">
         <v>22</v>
       </c>
@@ -26069,7 +26283,9 @@
       <c r="E15" s="231"/>
       <c r="F15" s="232"/>
       <c r="G15" s="232"/>
-      <c r="H15" s="3"/>
+      <c r="H15" s="3" t="s">
+        <v>197</v>
+      </c>
       <c r="I15" s="3"/>
       <c r="J15" s="232"/>
       <c r="K15" s="232"/>
@@ -26090,7 +26306,9 @@
       <c r="H16" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="I16" s="9"/>
+      <c r="I16" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="J16" s="227" t="s">
         <v>8</v>
       </c>
@@ -26114,10 +26332,10 @@
       <c r="F17" s="286"/>
       <c r="G17" s="286"/>
       <c r="H17" s="12" t="s">
+        <v>695</v>
+      </c>
+      <c r="I17" s="12" t="s">
         <v>696</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>697</v>
       </c>
       <c r="J17" s="286"/>
       <c r="K17" s="286"/>
@@ -26165,7 +26383,7 @@
         <v>395</v>
       </c>
       <c r="I19" s="105" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="J19" s="216" t="s">
         <v>219</v>
@@ -26186,7 +26404,7 @@
       <c r="F20" s="227"/>
       <c r="G20" s="227"/>
       <c r="H20" s="9" t="s">
-        <v>682</v>
+        <v>386</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="227" t="s">
@@ -26293,7 +26511,7 @@
       <c r="C24" s="359"/>
       <c r="D24" s="359"/>
       <c r="E24" s="360" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="F24" s="361"/>
       <c r="G24" s="362"/>
@@ -26304,7 +26522,7 @@
         <v>168</v>
       </c>
       <c r="J24" s="363" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="K24" s="362"/>
       <c r="L24" s="32"/>
@@ -26328,7 +26546,7 @@
         <v>127</v>
       </c>
       <c r="J25" s="345" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="K25" s="226"/>
       <c r="L25" s="9"/>
@@ -26368,14 +26586,10 @@
       <c r="B27" s="342"/>
       <c r="C27" s="342"/>
       <c r="D27" s="346"/>
-      <c r="E27" s="235" t="s">
-        <v>39</v>
-      </c>
+      <c r="E27" s="235"/>
       <c r="F27" s="236"/>
       <c r="G27" s="237"/>
-      <c r="H27" s="19" t="s">
-        <v>39</v>
-      </c>
+      <c r="H27" s="19"/>
       <c r="I27" s="19" t="s">
         <v>39</v>
       </c>
@@ -26419,15 +26633,9 @@
       </c>
       <c r="F29" s="460"/>
       <c r="G29" s="461"/>
-      <c r="H29" s="48" t="s">
-        <v>189</v>
-      </c>
-      <c r="I29" s="62" t="s">
-        <v>189</v>
-      </c>
-      <c r="J29" s="244" t="s">
-        <v>189</v>
-      </c>
+      <c r="H29" s="48"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="244"/>
       <c r="K29" s="243"/>
       <c r="L29" s="48"/>
       <c r="M29" s="48"/>
@@ -26737,14 +26945,12 @@
       </c>
       <c r="F43" s="242"/>
       <c r="G43" s="243"/>
-      <c r="H43" s="3" t="s">
-        <v>189</v>
-      </c>
+      <c r="H43" s="3"/>
       <c r="I43" s="3" t="s">
         <v>327</v>
       </c>
       <c r="J43" s="244" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="K43" s="243"/>
       <c r="L43" s="3"/>
@@ -26756,15 +26962,11 @@
       <c r="B44" s="246"/>
       <c r="C44" s="246"/>
       <c r="D44" s="246"/>
-      <c r="E44" s="224" t="s">
-        <v>189</v>
-      </c>
+      <c r="E44" s="224"/>
       <c r="F44" s="225"/>
       <c r="G44" s="226"/>
       <c r="H44" s="9"/>
-      <c r="I44" s="9" t="s">
-        <v>189</v>
-      </c>
+      <c r="I44" s="9"/>
       <c r="J44" s="345"/>
       <c r="K44" s="226"/>
       <c r="L44" s="9"/>
@@ -26779,16 +26981,18 @@
       <c r="C45" s="229"/>
       <c r="D45" s="230"/>
       <c r="E45" s="307" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="F45" s="286"/>
       <c r="G45" s="286"/>
       <c r="H45" s="12" t="s">
-        <v>696</v>
-      </c>
-      <c r="I45" s="12"/>
+        <v>695</v>
+      </c>
+      <c r="I45" s="12" t="s">
+        <v>697</v>
+      </c>
       <c r="J45" s="286" t="s">
-        <v>54</v>
+        <v>697</v>
       </c>
       <c r="K45" s="286"/>
       <c r="L45" s="12"/>
@@ -26801,13 +27005,13 @@
       <c r="C46" s="213"/>
       <c r="D46" s="214"/>
       <c r="E46" s="215" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F46" s="216"/>
       <c r="G46" s="216"/>
       <c r="H46" s="32"/>
       <c r="I46" s="32" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="J46" s="216" t="s">
         <v>55</v>
@@ -26940,7 +27144,7 @@
       <c r="F53" s="227"/>
       <c r="G53" s="227"/>
       <c r="H53" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="I53" s="9" t="s">
         <v>559</v>
@@ -27007,18 +27211,18 @@
       <c r="C56" s="313"/>
       <c r="D56" s="314"/>
       <c r="E56" s="241" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F56" s="242"/>
       <c r="G56" s="243"/>
       <c r="H56" s="24" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="J56" s="286" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="K56" s="286"/>
       <c r="L56" s="3"/>
@@ -27031,7 +27235,7 @@
       <c r="C57" s="305"/>
       <c r="D57" s="306"/>
       <c r="E57" s="247" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="F57" s="227"/>
       <c r="G57" s="227"/>
@@ -27075,7 +27279,7 @@
       <c r="C59" s="251"/>
       <c r="D59" s="252"/>
       <c r="E59" s="220" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F59" s="221"/>
       <c r="G59" s="221"/>
@@ -27161,7 +27365,7 @@
       <c r="C63" s="213"/>
       <c r="D63" s="214"/>
       <c r="E63" s="215" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F63" s="216"/>
       <c r="G63" s="216"/>
@@ -27303,9 +27507,7 @@
       <c r="I70" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J70" s="287" t="s">
-        <v>74</v>
-      </c>
+      <c r="J70" s="287"/>
       <c r="K70" s="287"/>
       <c r="L70" s="9"/>
       <c r="M70" s="21" t="s">
@@ -27347,7 +27549,7 @@
       <c r="C72" s="271"/>
       <c r="D72" s="271"/>
       <c r="E72" s="220" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F72" s="221"/>
       <c r="G72" s="221"/>
@@ -27427,7 +27629,7 @@
       <c r="M75" s="9"/>
       <c r="N75" s="11"/>
     </row>
-    <row r="76" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="228" t="s">
         <v>80</v>
       </c>
@@ -27440,8 +27642,12 @@
       <c r="H76" s="124" t="s">
         <v>54</v>
       </c>
-      <c r="I76" s="124"/>
-      <c r="J76" s="286"/>
+      <c r="I76" s="12" t="s">
+        <v>697</v>
+      </c>
+      <c r="J76" s="286" t="s">
+        <v>697</v>
+      </c>
       <c r="K76" s="286"/>
       <c r="L76" s="12"/>
       <c r="M76" s="12" t="s">
@@ -27449,7 +27655,7 @@
       </c>
       <c r="N76" s="78"/>
     </row>
-    <row r="77" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:14" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="217"/>
       <c r="B77" s="218"/>
       <c r="C77" s="218"/>
@@ -27461,7 +27667,9 @@
         <v>55</v>
       </c>
       <c r="I77" s="97"/>
-      <c r="J77" s="227"/>
+      <c r="J77" s="227" t="s">
+        <v>55</v>
+      </c>
       <c r="K77" s="227"/>
       <c r="L77" s="9"/>
       <c r="M77" s="9"/>
@@ -27577,7 +27785,7 @@
       <c r="C83" s="251"/>
       <c r="D83" s="252"/>
       <c r="E83" s="253" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F83" s="254"/>
       <c r="G83" s="254"/>
@@ -27602,21 +27810,21 @@
       <c r="B84" s="258"/>
       <c r="C84" s="258"/>
       <c r="D84" s="259"/>
-      <c r="E84" s="481" t="s">
+      <c r="E84" s="483" t="s">
         <v>47</v>
       </c>
-      <c r="F84" s="482"/>
-      <c r="G84" s="483"/>
+      <c r="F84" s="484"/>
+      <c r="G84" s="485"/>
       <c r="H84" s="193" t="s">
         <v>47</v>
       </c>
       <c r="I84" s="193" t="s">
         <v>47</v>
       </c>
-      <c r="J84" s="484" t="s">
+      <c r="J84" s="486" t="s">
         <v>47</v>
       </c>
-      <c r="K84" s="485"/>
+      <c r="K84" s="487"/>
       <c r="L84" s="192"/>
       <c r="M84" s="192"/>
       <c r="N84" s="102"/>
@@ -27679,7 +27887,7 @@
       <c r="C87" s="213"/>
       <c r="D87" s="214"/>
       <c r="E87" s="248" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F87" s="249"/>
       <c r="G87" s="249"/>
@@ -27837,7 +28045,9 @@
       </c>
       <c r="F94" s="232"/>
       <c r="G94" s="232"/>
-      <c r="H94" s="48"/>
+      <c r="H94" s="48" t="s">
+        <v>698</v>
+      </c>
       <c r="I94" s="3"/>
       <c r="J94" s="232"/>
       <c r="K94" s="232"/>
@@ -27845,7 +28055,7 @@
       <c r="M94" s="3"/>
       <c r="N94" s="59"/>
     </row>
-    <row r="95" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A95" s="212"/>
       <c r="B95" s="213"/>
       <c r="C95" s="213"/>
@@ -27869,7 +28079,7 @@
       <c r="M95" s="32"/>
       <c r="N95" s="33"/>
     </row>
-    <row r="96" spans="1:14" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:14" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="217"/>
       <c r="B96" s="218"/>
       <c r="C96" s="218"/>
@@ -27881,7 +28091,9 @@
       <c r="G96" s="227"/>
       <c r="H96" s="9"/>
       <c r="I96" s="9"/>
-      <c r="J96" s="227"/>
+      <c r="J96" s="227" t="s">
+        <v>74</v>
+      </c>
       <c r="K96" s="227"/>
       <c r="L96" s="9"/>
       <c r="M96" s="9"/>
@@ -27961,11 +28173,13 @@
       <c r="B102" s="201"/>
       <c r="C102" s="201"/>
       <c r="D102" s="202"/>
-      <c r="E102" s="203"/>
+      <c r="E102" s="203" t="s">
+        <v>107</v>
+      </c>
       <c r="F102" s="198"/>
       <c r="G102" s="199"/>
       <c r="H102" s="119" t="s">
-        <v>107</v>
+        <v>199</v>
       </c>
       <c r="I102" s="119" t="s">
         <v>107</v>
@@ -28283,6 +28497,2805 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38FAB627-CE51-4918-9597-13F010F9BDCD}">
+  <dimension ref="A1:N108"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="20.77734375" customWidth="1"/>
+    <col min="9" max="9" width="23" customWidth="1"/>
+    <col min="11" max="11" width="20.21875" customWidth="1"/>
+    <col min="12" max="12" width="22.88671875" customWidth="1"/>
+    <col min="13" max="13" width="17" customWidth="1"/>
+    <col min="14" max="14" width="15.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="384" t="s">
+        <v>700</v>
+      </c>
+      <c r="B1" s="385"/>
+      <c r="C1" s="385"/>
+      <c r="D1" s="386"/>
+      <c r="E1" s="387" t="s">
+        <v>701</v>
+      </c>
+      <c r="F1" s="388"/>
+      <c r="G1" s="389"/>
+      <c r="H1" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="J1" s="390" t="s">
+        <v>704</v>
+      </c>
+      <c r="K1" s="389"/>
+      <c r="L1" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="391" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="392"/>
+      <c r="C2" s="392"/>
+      <c r="D2" s="393"/>
+      <c r="E2" s="231"/>
+      <c r="F2" s="232"/>
+      <c r="G2" s="232"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="5"/>
+    </row>
+    <row r="3" spans="1:14" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="321"/>
+      <c r="B3" s="322"/>
+      <c r="C3" s="322"/>
+      <c r="D3" s="323"/>
+      <c r="E3" s="247" t="s">
+        <v>450</v>
+      </c>
+      <c r="F3" s="227"/>
+      <c r="G3" s="227"/>
+      <c r="H3" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="422" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" s="422"/>
+      <c r="L3" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="M3" s="9"/>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="239" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="240"/>
+      <c r="C4" s="240"/>
+      <c r="D4" s="240"/>
+      <c r="E4" s="241" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="242"/>
+      <c r="G4" s="243"/>
+      <c r="H4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="232" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="232"/>
+      <c r="L4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="3"/>
+      <c r="N4" s="8"/>
+    </row>
+    <row r="5" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="223"/>
+      <c r="D5" s="223"/>
+      <c r="E5" s="247" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="227"/>
+      <c r="G5" s="227"/>
+      <c r="H5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="227" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="227"/>
+      <c r="L5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="9"/>
+      <c r="N5" s="16"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="284" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="285"/>
+      <c r="C6" s="285"/>
+      <c r="D6" s="383"/>
+      <c r="E6" s="231"/>
+      <c r="F6" s="232"/>
+      <c r="G6" s="232"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="232"/>
+      <c r="K6" s="232"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="31"/>
+    </row>
+    <row r="7" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="222"/>
+      <c r="B7" s="223"/>
+      <c r="C7" s="223"/>
+      <c r="D7" s="381"/>
+      <c r="E7" s="247" t="s">
+        <v>313</v>
+      </c>
+      <c r="F7" s="227"/>
+      <c r="G7" s="227"/>
+      <c r="H7" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="I7" s="9"/>
+      <c r="J7" s="227" t="s">
+        <v>711</v>
+      </c>
+      <c r="K7" s="227"/>
+      <c r="L7" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="N7" s="16"/>
+    </row>
+    <row r="8" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="233" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="234"/>
+      <c r="C8" s="234"/>
+      <c r="D8" s="234"/>
+      <c r="E8" s="382" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="355"/>
+      <c r="G8" s="355"/>
+      <c r="H8" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="355"/>
+      <c r="K8" s="355"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" s="122"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="267" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="268"/>
+      <c r="C9" s="268"/>
+      <c r="D9" s="269"/>
+      <c r="E9" s="378"/>
+      <c r="F9" s="232"/>
+      <c r="G9" s="232"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="232"/>
+      <c r="K9" s="232"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="8"/>
+    </row>
+    <row r="10" spans="1:14" ht="69" x14ac:dyDescent="0.3">
+      <c r="A10" s="358"/>
+      <c r="B10" s="359"/>
+      <c r="C10" s="359"/>
+      <c r="D10" s="359"/>
+      <c r="E10" s="379"/>
+      <c r="F10" s="380"/>
+      <c r="G10" s="380"/>
+      <c r="H10" s="126" t="s">
+        <v>713</v>
+      </c>
+      <c r="I10" s="32"/>
+      <c r="J10" s="216" t="s">
+        <v>714</v>
+      </c>
+      <c r="K10" s="216"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32" t="s">
+        <v>391</v>
+      </c>
+      <c r="N10" s="39"/>
+    </row>
+    <row r="11" spans="1:14" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="374"/>
+      <c r="B11" s="375"/>
+      <c r="C11" s="375"/>
+      <c r="D11" s="376"/>
+      <c r="E11" s="310" t="s">
+        <v>712</v>
+      </c>
+      <c r="F11" s="311"/>
+      <c r="G11" s="311"/>
+      <c r="H11" s="76" t="s">
+        <v>712</v>
+      </c>
+      <c r="I11" s="76" t="s">
+        <v>712</v>
+      </c>
+      <c r="J11" s="489" t="s">
+        <v>712</v>
+      </c>
+      <c r="K11" s="490"/>
+      <c r="L11" s="76" t="s">
+        <v>712</v>
+      </c>
+      <c r="M11" s="188"/>
+      <c r="N11" s="189"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="318" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="319"/>
+      <c r="C12" s="319"/>
+      <c r="D12" s="319"/>
+      <c r="E12" s="378"/>
+      <c r="F12" s="482"/>
+      <c r="G12" s="482"/>
+      <c r="H12" s="190"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="232"/>
+      <c r="K12" s="232"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="191"/>
+    </row>
+    <row r="13" spans="1:14" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="350"/>
+      <c r="B13" s="351"/>
+      <c r="C13" s="351"/>
+      <c r="D13" s="352"/>
+      <c r="E13" s="368" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="227"/>
+      <c r="G13" s="227"/>
+      <c r="H13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="227" t="s">
+        <v>13</v>
+      </c>
+      <c r="K13" s="227"/>
+      <c r="L13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="M13" s="9"/>
+      <c r="N13" s="26"/>
+    </row>
+    <row r="14" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="402" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="403"/>
+      <c r="C14" s="403"/>
+      <c r="D14" s="404"/>
+      <c r="E14" s="372" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="373"/>
+      <c r="G14" s="373"/>
+      <c r="H14" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="373"/>
+      <c r="K14" s="373"/>
+      <c r="L14" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="27"/>
+    </row>
+    <row r="15" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="284" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="285"/>
+      <c r="C15" s="285"/>
+      <c r="D15" s="285"/>
+      <c r="E15" s="231" t="s">
+        <v>715</v>
+      </c>
+      <c r="F15" s="232"/>
+      <c r="G15" s="232"/>
+      <c r="H15" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="J15" s="232" t="s">
+        <v>711</v>
+      </c>
+      <c r="K15" s="232"/>
+      <c r="L15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" s="3"/>
+      <c r="N15" s="8"/>
+    </row>
+    <row r="16" spans="1:14" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="222"/>
+      <c r="B16" s="223"/>
+      <c r="C16" s="223"/>
+      <c r="D16" s="223"/>
+      <c r="E16" s="247"/>
+      <c r="F16" s="227"/>
+      <c r="G16" s="227"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="227" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="227"/>
+      <c r="L16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" s="9"/>
+      <c r="N16" s="16"/>
+    </row>
+    <row r="17" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="267" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="268"/>
+      <c r="C17" s="268"/>
+      <c r="D17" s="269"/>
+      <c r="E17" s="307" t="s">
+        <v>716</v>
+      </c>
+      <c r="F17" s="286"/>
+      <c r="G17" s="286"/>
+      <c r="H17" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="I17" s="12"/>
+      <c r="J17" s="286" t="s">
+        <v>76</v>
+      </c>
+      <c r="K17" s="286"/>
+      <c r="L17" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="M17" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="N17" s="14"/>
+    </row>
+    <row r="18" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="212"/>
+      <c r="B18" s="213"/>
+      <c r="C18" s="213"/>
+      <c r="D18" s="214"/>
+      <c r="E18" s="215"/>
+      <c r="F18" s="216"/>
+      <c r="G18" s="216"/>
+      <c r="H18" s="32" t="s">
+        <v>717</v>
+      </c>
+      <c r="I18" s="32" t="s">
+        <v>718</v>
+      </c>
+      <c r="J18" s="216"/>
+      <c r="K18" s="216"/>
+      <c r="L18" s="32"/>
+      <c r="M18" s="32"/>
+      <c r="N18" s="33" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="212"/>
+      <c r="B19" s="213"/>
+      <c r="C19" s="213"/>
+      <c r="D19" s="214"/>
+      <c r="E19" s="215"/>
+      <c r="F19" s="216"/>
+      <c r="G19" s="216"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="216"/>
+      <c r="K19" s="216"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
+      <c r="N19" s="35"/>
+    </row>
+    <row r="20" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="250"/>
+      <c r="B20" s="251"/>
+      <c r="C20" s="251"/>
+      <c r="D20" s="252"/>
+      <c r="E20" s="247"/>
+      <c r="F20" s="227"/>
+      <c r="G20" s="227"/>
+      <c r="H20" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="J20" s="227" t="s">
+        <v>720</v>
+      </c>
+      <c r="K20" s="227"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="11"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="267" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="268"/>
+      <c r="C21" s="268"/>
+      <c r="D21" s="269"/>
+      <c r="E21" s="307" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="286"/>
+      <c r="G21" s="286"/>
+      <c r="H21" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J21" s="256" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" s="256"/>
+      <c r="L21" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M21" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="N21" s="37" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="364"/>
+      <c r="B22" s="365"/>
+      <c r="C22" s="365"/>
+      <c r="D22" s="365"/>
+      <c r="E22" s="220" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" s="221"/>
+      <c r="G22" s="221"/>
+      <c r="H22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" s="221" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" s="221"/>
+      <c r="L22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22" s="38" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="267" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="268"/>
+      <c r="C23" s="268"/>
+      <c r="D23" s="269"/>
+      <c r="E23" s="231" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="232"/>
+      <c r="G23" s="232"/>
+      <c r="H23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J23" s="232" t="s">
+        <v>493</v>
+      </c>
+      <c r="K23" s="232"/>
+      <c r="L23" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="M23" s="3"/>
+      <c r="N23" s="8"/>
+    </row>
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="358"/>
+      <c r="B24" s="359"/>
+      <c r="C24" s="359"/>
+      <c r="D24" s="359"/>
+      <c r="E24" s="215" t="s">
+        <v>168</v>
+      </c>
+      <c r="F24" s="216"/>
+      <c r="G24" s="216"/>
+      <c r="H24" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="I24" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J24" s="216" t="s">
+        <v>36</v>
+      </c>
+      <c r="K24" s="216"/>
+      <c r="L24" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="M24" s="32"/>
+      <c r="N24" s="39"/>
+    </row>
+    <row r="25" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="222"/>
+      <c r="B25" s="223"/>
+      <c r="C25" s="223"/>
+      <c r="D25" s="223"/>
+      <c r="E25" s="247" t="s">
+        <v>127</v>
+      </c>
+      <c r="F25" s="227"/>
+      <c r="G25" s="227"/>
+      <c r="H25" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="J25" s="227" t="s">
+        <v>127</v>
+      </c>
+      <c r="K25" s="227"/>
+      <c r="L25" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="M25" s="9"/>
+      <c r="N25" s="16"/>
+    </row>
+    <row r="26" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="257" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="258"/>
+      <c r="C26" s="258"/>
+      <c r="D26" s="258"/>
+      <c r="E26" s="491" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" s="492"/>
+      <c r="G26" s="493"/>
+      <c r="H26" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="J26" s="494" t="s">
+        <v>135</v>
+      </c>
+      <c r="K26" s="493"/>
+      <c r="L26" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="M26" s="15"/>
+      <c r="N26" s="495"/>
+    </row>
+    <row r="27" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="341" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="342"/>
+      <c r="C27" s="342"/>
+      <c r="D27" s="346"/>
+      <c r="E27" s="235" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" s="236"/>
+      <c r="G27" s="237"/>
+      <c r="H27" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="I27" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="J27" s="238" t="s">
+        <v>135</v>
+      </c>
+      <c r="K27" s="237"/>
+      <c r="L27" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M27" s="19"/>
+      <c r="N27" s="20"/>
+    </row>
+    <row r="28" spans="1:14" ht="56.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="350" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="351"/>
+      <c r="C28" s="351"/>
+      <c r="D28" s="352"/>
+      <c r="E28" s="477"/>
+      <c r="F28" s="478"/>
+      <c r="G28" s="478"/>
+      <c r="H28" s="186"/>
+      <c r="I28" s="101"/>
+      <c r="J28" s="479"/>
+      <c r="K28" s="479"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="185" t="s">
+        <v>585</v>
+      </c>
+      <c r="N28" s="187"/>
+    </row>
+    <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="239" t="s">
+        <v>524</v>
+      </c>
+      <c r="B29" s="240"/>
+      <c r="C29" s="240"/>
+      <c r="D29" s="240"/>
+      <c r="E29" s="459" t="s">
+        <v>99</v>
+      </c>
+      <c r="F29" s="460"/>
+      <c r="G29" s="461"/>
+      <c r="H29" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="I29" s="62" t="s">
+        <v>175</v>
+      </c>
+      <c r="J29" s="244" t="s">
+        <v>189</v>
+      </c>
+      <c r="K29" s="243"/>
+      <c r="L29" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="M29" s="48"/>
+      <c r="N29" s="49"/>
+    </row>
+    <row r="30" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="222"/>
+      <c r="B30" s="223"/>
+      <c r="C30" s="223"/>
+      <c r="D30" s="223"/>
+      <c r="E30" s="331" t="s">
+        <v>189</v>
+      </c>
+      <c r="F30" s="332"/>
+      <c r="G30" s="333"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="97"/>
+      <c r="J30" s="345"/>
+      <c r="K30" s="226"/>
+      <c r="L30" s="51"/>
+      <c r="M30" s="50"/>
+      <c r="N30" s="52"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="233" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="234"/>
+      <c r="C31" s="234"/>
+      <c r="D31" s="234"/>
+      <c r="E31" s="462"/>
+      <c r="F31" s="463"/>
+      <c r="G31" s="463"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="279"/>
+      <c r="K31" s="278"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="56"/>
+      <c r="N31" s="57"/>
+    </row>
+    <row r="32" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="341"/>
+      <c r="B32" s="342"/>
+      <c r="C32" s="342"/>
+      <c r="D32" s="342"/>
+      <c r="E32" s="417"/>
+      <c r="F32" s="418"/>
+      <c r="G32" s="418"/>
+      <c r="H32" s="159" t="s">
+        <v>450</v>
+      </c>
+      <c r="I32" s="159" t="s">
+        <v>450</v>
+      </c>
+      <c r="J32" s="419" t="s">
+        <v>450</v>
+      </c>
+      <c r="K32" s="420"/>
+      <c r="L32" s="135"/>
+      <c r="M32" s="159" t="s">
+        <v>450</v>
+      </c>
+      <c r="N32" s="136"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="267" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="268"/>
+      <c r="C33" s="268"/>
+      <c r="D33" s="269"/>
+      <c r="E33" s="231"/>
+      <c r="F33" s="232"/>
+      <c r="G33" s="232"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="232"/>
+      <c r="K33" s="232"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="49"/>
+    </row>
+    <row r="34" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="222"/>
+      <c r="B34" s="223"/>
+      <c r="C34" s="223"/>
+      <c r="D34" s="223"/>
+      <c r="E34" s="337"/>
+      <c r="F34" s="287"/>
+      <c r="G34" s="287"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="227" t="s">
+        <v>721</v>
+      </c>
+      <c r="K34" s="227"/>
+      <c r="L34" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="N34" s="54"/>
+    </row>
+    <row r="35" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="239" t="s">
+        <v>255</v>
+      </c>
+      <c r="B35" s="240"/>
+      <c r="C35" s="240"/>
+      <c r="D35" s="416"/>
+      <c r="E35" s="241" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35" s="242"/>
+      <c r="G35" s="243"/>
+      <c r="H35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="244" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" s="243"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="104"/>
+    </row>
+    <row r="36" spans="1:14" ht="43.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="217"/>
+      <c r="B36" s="218"/>
+      <c r="C36" s="218"/>
+      <c r="D36" s="317"/>
+      <c r="E36" s="224" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" s="225"/>
+      <c r="G36" s="226"/>
+      <c r="H36" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J36" s="345" t="s">
+        <v>24</v>
+      </c>
+      <c r="K36" s="226"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="38"/>
+    </row>
+    <row r="37" spans="1:14" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="228" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="229"/>
+      <c r="C37" s="229"/>
+      <c r="D37" s="230"/>
+      <c r="E37" s="302"/>
+      <c r="F37" s="303"/>
+      <c r="G37" s="303"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="232" t="s">
+        <v>721</v>
+      </c>
+      <c r="K37" s="232"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="138"/>
+    </row>
+    <row r="38" spans="1:14" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="245"/>
+      <c r="B38" s="246"/>
+      <c r="C38" s="246"/>
+      <c r="D38" s="246"/>
+      <c r="E38" s="247" t="s">
+        <v>5</v>
+      </c>
+      <c r="F38" s="227"/>
+      <c r="G38" s="227"/>
+      <c r="H38" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="J38" s="227" t="s">
+        <v>5</v>
+      </c>
+      <c r="K38" s="227"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="N38" s="16"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="228" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="229"/>
+      <c r="C39" s="229"/>
+      <c r="D39" s="230"/>
+      <c r="E39" s="307"/>
+      <c r="F39" s="286"/>
+      <c r="G39" s="286"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="137"/>
+      <c r="J39" s="286"/>
+      <c r="K39" s="286"/>
+      <c r="L39" s="12"/>
+      <c r="M39" s="137"/>
+      <c r="N39" s="94"/>
+    </row>
+    <row r="40" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="321"/>
+      <c r="B40" s="322"/>
+      <c r="C40" s="322"/>
+      <c r="D40" s="323"/>
+      <c r="E40" s="247" t="s">
+        <v>50</v>
+      </c>
+      <c r="F40" s="227"/>
+      <c r="G40" s="227"/>
+      <c r="H40" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="J40" s="227" t="s">
+        <v>50</v>
+      </c>
+      <c r="K40" s="227"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="16"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="267" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="268"/>
+      <c r="C41" s="268"/>
+      <c r="D41" s="269"/>
+      <c r="E41" s="320" t="s">
+        <v>32</v>
+      </c>
+      <c r="F41" s="286"/>
+      <c r="G41" s="286"/>
+      <c r="H41" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J41" s="286" t="s">
+        <v>32</v>
+      </c>
+      <c r="K41" s="286"/>
+      <c r="L41" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M41" s="12"/>
+      <c r="N41" s="14"/>
+    </row>
+    <row r="42" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="250"/>
+      <c r="B42" s="251"/>
+      <c r="C42" s="251"/>
+      <c r="D42" s="252"/>
+      <c r="E42" s="220" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" s="221"/>
+      <c r="G42" s="221"/>
+      <c r="H42" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J42" s="221" t="s">
+        <v>32</v>
+      </c>
+      <c r="K42" s="221"/>
+      <c r="L42" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M42" s="63"/>
+      <c r="N42" s="30"/>
+    </row>
+    <row r="43" spans="1:14" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="239" t="s">
+        <v>523</v>
+      </c>
+      <c r="B43" s="240"/>
+      <c r="C43" s="240"/>
+      <c r="D43" s="240"/>
+      <c r="E43" s="241" t="s">
+        <v>722</v>
+      </c>
+      <c r="F43" s="242"/>
+      <c r="G43" s="243"/>
+      <c r="H43" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J43" s="244" t="s">
+        <v>722</v>
+      </c>
+      <c r="K43" s="243"/>
+      <c r="L43" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M43" s="3"/>
+      <c r="N43" s="31"/>
+    </row>
+    <row r="44" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="245"/>
+      <c r="B44" s="246"/>
+      <c r="C44" s="246"/>
+      <c r="D44" s="246"/>
+      <c r="E44" s="224"/>
+      <c r="F44" s="225"/>
+      <c r="G44" s="226"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="345"/>
+      <c r="K44" s="226"/>
+      <c r="L44" s="9"/>
+      <c r="M44" s="65"/>
+      <c r="N44" s="11"/>
+    </row>
+    <row r="45" spans="1:14" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="228" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="229"/>
+      <c r="C45" s="229"/>
+      <c r="D45" s="230"/>
+      <c r="E45" s="307" t="s">
+        <v>723</v>
+      </c>
+      <c r="F45" s="286"/>
+      <c r="G45" s="286"/>
+      <c r="H45" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="I45" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="J45" s="244" t="s">
+        <v>723</v>
+      </c>
+      <c r="K45" s="243"/>
+      <c r="L45" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="M45" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="N45" s="172"/>
+    </row>
+    <row r="46" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="212"/>
+      <c r="B46" s="213"/>
+      <c r="C46" s="213"/>
+      <c r="D46" s="214"/>
+      <c r="E46" s="215"/>
+      <c r="F46" s="216"/>
+      <c r="G46" s="216"/>
+      <c r="H46" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="I46" s="32"/>
+      <c r="J46" s="216" t="s">
+        <v>55</v>
+      </c>
+      <c r="K46" s="216"/>
+      <c r="L46" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="M46" s="32"/>
+      <c r="N46" s="33"/>
+    </row>
+    <row r="47" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="250"/>
+      <c r="B47" s="251"/>
+      <c r="C47" s="251"/>
+      <c r="D47" s="252"/>
+      <c r="E47" s="247"/>
+      <c r="F47" s="227"/>
+      <c r="G47" s="227"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="227"/>
+      <c r="K47" s="227"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="65"/>
+      <c r="N47" s="11"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48" s="267" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="268"/>
+      <c r="C48" s="268"/>
+      <c r="D48" s="296"/>
+      <c r="E48" s="307"/>
+      <c r="F48" s="286"/>
+      <c r="G48" s="286"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="279"/>
+      <c r="K48" s="278"/>
+      <c r="L48" s="12"/>
+      <c r="M48" s="66"/>
+      <c r="N48" s="67"/>
+    </row>
+    <row r="49" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="217"/>
+      <c r="B49" s="218"/>
+      <c r="C49" s="218"/>
+      <c r="D49" s="317"/>
+      <c r="E49" s="272"/>
+      <c r="F49" s="273"/>
+      <c r="G49" s="274"/>
+      <c r="H49" s="68"/>
+      <c r="I49" s="68"/>
+      <c r="J49" s="425"/>
+      <c r="K49" s="426"/>
+      <c r="L49" s="68"/>
+      <c r="M49" s="69"/>
+      <c r="N49" s="70"/>
+    </row>
+    <row r="50" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="318" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="319"/>
+      <c r="C50" s="319"/>
+      <c r="D50" s="319"/>
+      <c r="E50" s="231" t="s">
+        <v>49</v>
+      </c>
+      <c r="F50" s="232"/>
+      <c r="G50" s="232"/>
+      <c r="H50" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="J50" s="232" t="s">
+        <v>589</v>
+      </c>
+      <c r="K50" s="232"/>
+      <c r="L50" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="M50" s="4"/>
+      <c r="N50" s="29"/>
+    </row>
+    <row r="51" spans="1:14" ht="37.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="315"/>
+      <c r="B51" s="316"/>
+      <c r="C51" s="316"/>
+      <c r="D51" s="316"/>
+      <c r="E51" s="220"/>
+      <c r="F51" s="221"/>
+      <c r="G51" s="221"/>
+      <c r="H51" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I51" s="6"/>
+      <c r="J51" s="221" t="s">
+        <v>724</v>
+      </c>
+      <c r="K51" s="221"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="6"/>
+      <c r="N51" s="38"/>
+    </row>
+    <row r="52" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="239" t="s">
+        <v>710</v>
+      </c>
+      <c r="B52" s="240"/>
+      <c r="C52" s="240"/>
+      <c r="D52" s="240"/>
+      <c r="E52" s="241" t="s">
+        <v>32</v>
+      </c>
+      <c r="F52" s="242"/>
+      <c r="G52" s="243"/>
+      <c r="H52" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="J52" s="244"/>
+      <c r="K52" s="243"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="245"/>
+      <c r="B53" s="246"/>
+      <c r="C53" s="246"/>
+      <c r="D53" s="246"/>
+      <c r="E53" s="224" t="s">
+        <v>32</v>
+      </c>
+      <c r="F53" s="225"/>
+      <c r="G53" s="226"/>
+      <c r="H53" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I53" s="9"/>
+      <c r="J53" s="345"/>
+      <c r="K53" s="226"/>
+      <c r="L53" s="9"/>
+      <c r="M53" s="9"/>
+      <c r="N53" s="16"/>
+    </row>
+    <row r="54" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="284" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" s="285"/>
+      <c r="C54" s="285"/>
+      <c r="D54" s="285"/>
+      <c r="E54" s="276"/>
+      <c r="F54" s="277"/>
+      <c r="G54" s="278"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="286"/>
+      <c r="K54" s="286"/>
+      <c r="L54" s="12"/>
+      <c r="M54" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="N54" s="72"/>
+    </row>
+    <row r="55" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="245"/>
+      <c r="B55" s="246"/>
+      <c r="C55" s="246"/>
+      <c r="D55" s="246"/>
+      <c r="E55" s="247" t="s">
+        <v>120</v>
+      </c>
+      <c r="F55" s="227"/>
+      <c r="G55" s="227"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="J55" s="227" t="s">
+        <v>19</v>
+      </c>
+      <c r="K55" s="227"/>
+      <c r="L55" s="9"/>
+      <c r="M55" s="9"/>
+      <c r="N55" s="73"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" s="228" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="229"/>
+      <c r="C56" s="229"/>
+      <c r="D56" s="230"/>
+      <c r="E56" s="231"/>
+      <c r="F56" s="232"/>
+      <c r="G56" s="232"/>
+      <c r="H56" s="181"/>
+      <c r="I56" s="181"/>
+      <c r="J56" s="232"/>
+      <c r="K56" s="232"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="28"/>
+      <c r="N56" s="182"/>
+    </row>
+    <row r="57" spans="1:14" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="308"/>
+      <c r="B57" s="309"/>
+      <c r="C57" s="309"/>
+      <c r="D57" s="309"/>
+      <c r="E57" s="337" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57" s="287"/>
+      <c r="G57" s="287"/>
+      <c r="H57" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I57" s="21"/>
+      <c r="J57" s="287" t="s">
+        <v>18</v>
+      </c>
+      <c r="K57" s="287"/>
+      <c r="L57" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="M57" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N57" s="183"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58" s="312" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58" s="313"/>
+      <c r="C58" s="313"/>
+      <c r="D58" s="314"/>
+      <c r="E58" s="241" t="s">
+        <v>197</v>
+      </c>
+      <c r="F58" s="242"/>
+      <c r="G58" s="243"/>
+      <c r="H58" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J58" s="286" t="s">
+        <v>189</v>
+      </c>
+      <c r="K58" s="286"/>
+      <c r="L58" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M58" s="3"/>
+      <c r="N58" s="49"/>
+    </row>
+    <row r="59" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="304"/>
+      <c r="B59" s="305"/>
+      <c r="C59" s="305"/>
+      <c r="D59" s="306"/>
+      <c r="E59" s="247"/>
+      <c r="F59" s="227"/>
+      <c r="G59" s="227"/>
+      <c r="H59" s="21"/>
+      <c r="I59" s="21"/>
+      <c r="J59" s="227"/>
+      <c r="K59" s="227"/>
+      <c r="L59" s="9"/>
+      <c r="M59" s="51"/>
+      <c r="N59" s="52"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60" s="228" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" s="229"/>
+      <c r="C60" s="229"/>
+      <c r="D60" s="230"/>
+      <c r="E60" s="307" t="s">
+        <v>65</v>
+      </c>
+      <c r="F60" s="286"/>
+      <c r="G60" s="286"/>
+      <c r="H60" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="I60" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="J60" s="279" t="s">
+        <v>65</v>
+      </c>
+      <c r="K60" s="278"/>
+      <c r="L60" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="M60" s="12"/>
+      <c r="N60" s="78"/>
+    </row>
+    <row r="61" spans="1:14" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="250"/>
+      <c r="B61" s="251"/>
+      <c r="C61" s="251"/>
+      <c r="D61" s="252"/>
+      <c r="E61" s="220"/>
+      <c r="F61" s="221"/>
+      <c r="G61" s="221"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="227" t="s">
+        <v>726</v>
+      </c>
+      <c r="K61" s="227"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="63"/>
+      <c r="N61" s="30"/>
+    </row>
+    <row r="62" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="267" t="s">
+        <v>66</v>
+      </c>
+      <c r="B62" s="268"/>
+      <c r="C62" s="268"/>
+      <c r="D62" s="269"/>
+      <c r="E62" s="231" t="s">
+        <v>26</v>
+      </c>
+      <c r="F62" s="232"/>
+      <c r="G62" s="232"/>
+      <c r="H62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J62" s="232" t="s">
+        <v>26</v>
+      </c>
+      <c r="K62" s="232"/>
+      <c r="L62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M62" s="3"/>
+      <c r="N62" s="31"/>
+    </row>
+    <row r="63" spans="1:14" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="250"/>
+      <c r="B63" s="251"/>
+      <c r="C63" s="251"/>
+      <c r="D63" s="252"/>
+      <c r="E63" s="220"/>
+      <c r="F63" s="221"/>
+      <c r="G63" s="221"/>
+      <c r="H63" s="68"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="221" t="s">
+        <v>726</v>
+      </c>
+      <c r="K63" s="221"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="6"/>
+      <c r="N63" s="30"/>
+    </row>
+    <row r="64" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="239" t="s">
+        <v>709</v>
+      </c>
+      <c r="B64" s="240"/>
+      <c r="C64" s="240"/>
+      <c r="D64" s="240"/>
+      <c r="E64" s="241" t="s">
+        <v>727</v>
+      </c>
+      <c r="F64" s="242"/>
+      <c r="G64" s="243"/>
+      <c r="H64" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="J64" s="244" t="s">
+        <v>728</v>
+      </c>
+      <c r="K64" s="243"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="31"/>
+    </row>
+    <row r="65" spans="1:14" ht="30.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="245"/>
+      <c r="B65" s="246"/>
+      <c r="C65" s="246"/>
+      <c r="D65" s="246"/>
+      <c r="E65" s="224" t="s">
+        <v>692</v>
+      </c>
+      <c r="F65" s="225"/>
+      <c r="G65" s="226"/>
+      <c r="H65" s="10"/>
+      <c r="I65" s="9"/>
+      <c r="J65" s="345"/>
+      <c r="K65" s="226"/>
+      <c r="L65" s="9"/>
+      <c r="M65" s="9"/>
+      <c r="N65" s="11"/>
+    </row>
+    <row r="66" spans="1:14" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="228" t="s">
+        <v>67</v>
+      </c>
+      <c r="B66" s="229"/>
+      <c r="C66" s="229"/>
+      <c r="D66" s="230"/>
+      <c r="E66" s="255" t="s">
+        <v>729</v>
+      </c>
+      <c r="F66" s="256"/>
+      <c r="G66" s="256"/>
+      <c r="H66" s="13" t="s">
+        <v>730</v>
+      </c>
+      <c r="I66" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J66" s="488" t="s">
+        <v>27</v>
+      </c>
+      <c r="K66" s="488"/>
+      <c r="L66" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="M66" s="13"/>
+      <c r="N66" s="104"/>
+    </row>
+    <row r="67" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="212"/>
+      <c r="B67" s="213"/>
+      <c r="C67" s="213"/>
+      <c r="D67" s="214"/>
+      <c r="E67" s="215" t="s">
+        <v>740</v>
+      </c>
+      <c r="F67" s="216"/>
+      <c r="G67" s="216"/>
+      <c r="H67" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="I67" s="32" t="s">
+        <v>737</v>
+      </c>
+      <c r="J67" s="216"/>
+      <c r="K67" s="216"/>
+      <c r="L67" s="32"/>
+      <c r="M67" s="32"/>
+      <c r="N67" s="33"/>
+    </row>
+    <row r="68" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="217"/>
+      <c r="B68" s="218"/>
+      <c r="C68" s="218"/>
+      <c r="D68" s="219"/>
+      <c r="E68" s="247"/>
+      <c r="F68" s="227"/>
+      <c r="G68" s="227"/>
+      <c r="H68" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="I68" s="10"/>
+      <c r="J68" s="475"/>
+      <c r="K68" s="475"/>
+      <c r="L68" s="10"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="81"/>
+    </row>
+    <row r="69" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A69" s="267" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69" s="268"/>
+      <c r="C69" s="268"/>
+      <c r="D69" s="296"/>
+      <c r="E69" s="307"/>
+      <c r="F69" s="286"/>
+      <c r="G69" s="286"/>
+      <c r="H69" s="12"/>
+      <c r="I69" s="137"/>
+      <c r="J69" s="286" t="s">
+        <v>721</v>
+      </c>
+      <c r="K69" s="286"/>
+      <c r="L69" s="56"/>
+      <c r="M69" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="N69" s="78"/>
+    </row>
+    <row r="70" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="250"/>
+      <c r="B70" s="251"/>
+      <c r="C70" s="251"/>
+      <c r="D70" s="300"/>
+      <c r="E70" s="220"/>
+      <c r="F70" s="221"/>
+      <c r="G70" s="221"/>
+      <c r="H70" s="86"/>
+      <c r="I70" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="J70" s="254" t="s">
+        <v>313</v>
+      </c>
+      <c r="K70" s="254"/>
+      <c r="L70" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="M70" s="87" t="s">
+        <v>30</v>
+      </c>
+      <c r="N70" s="70"/>
+    </row>
+    <row r="71" spans="1:14" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="239" t="s">
+        <v>708</v>
+      </c>
+      <c r="B71" s="240"/>
+      <c r="C71" s="240"/>
+      <c r="D71" s="240"/>
+      <c r="E71" s="241" t="s">
+        <v>731</v>
+      </c>
+      <c r="F71" s="242"/>
+      <c r="G71" s="243"/>
+      <c r="H71" s="142" t="s">
+        <v>3</v>
+      </c>
+      <c r="I71" s="142" t="s">
+        <v>3</v>
+      </c>
+      <c r="J71" s="433" t="s">
+        <v>3</v>
+      </c>
+      <c r="K71" s="432"/>
+      <c r="L71" s="142" t="s">
+        <v>3</v>
+      </c>
+      <c r="M71" s="142" t="s">
+        <v>3</v>
+      </c>
+      <c r="N71" s="88"/>
+    </row>
+    <row r="72" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="245"/>
+      <c r="B72" s="246"/>
+      <c r="C72" s="246"/>
+      <c r="D72" s="246"/>
+      <c r="E72" s="224"/>
+      <c r="F72" s="225"/>
+      <c r="G72" s="226"/>
+      <c r="H72" s="80"/>
+      <c r="I72" s="9"/>
+      <c r="J72" s="294"/>
+      <c r="K72" s="295"/>
+      <c r="L72" s="9"/>
+      <c r="M72" s="89"/>
+      <c r="N72" s="90"/>
+    </row>
+    <row r="73" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A73" s="284" t="s">
+        <v>70</v>
+      </c>
+      <c r="B73" s="285"/>
+      <c r="C73" s="285"/>
+      <c r="D73" s="285"/>
+      <c r="E73" s="276"/>
+      <c r="F73" s="277"/>
+      <c r="G73" s="278"/>
+      <c r="H73" s="56"/>
+      <c r="I73" s="12"/>
+      <c r="J73" s="279"/>
+      <c r="K73" s="278"/>
+      <c r="L73" s="12"/>
+      <c r="M73" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="N73" s="67"/>
+    </row>
+    <row r="74" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="245"/>
+      <c r="B74" s="246"/>
+      <c r="C74" s="246"/>
+      <c r="D74" s="246"/>
+      <c r="E74" s="448"/>
+      <c r="F74" s="449"/>
+      <c r="G74" s="420"/>
+      <c r="H74" s="86"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="425"/>
+      <c r="K74" s="426"/>
+      <c r="L74" s="87"/>
+      <c r="M74" s="87"/>
+      <c r="N74" s="70"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A75" s="239" t="s">
+        <v>72</v>
+      </c>
+      <c r="B75" s="240"/>
+      <c r="C75" s="240"/>
+      <c r="D75" s="240"/>
+      <c r="E75" s="231"/>
+      <c r="F75" s="232"/>
+      <c r="G75" s="232"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="232"/>
+      <c r="K75" s="232"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
+      <c r="N75" s="8"/>
+    </row>
+    <row r="76" spans="1:14" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="270"/>
+      <c r="B76" s="271"/>
+      <c r="C76" s="271"/>
+      <c r="D76" s="271"/>
+      <c r="E76" s="247"/>
+      <c r="F76" s="227"/>
+      <c r="G76" s="227"/>
+      <c r="H76" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="J76" s="287"/>
+      <c r="K76" s="287"/>
+      <c r="L76" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="M76" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="N76" s="16"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" s="239" t="s">
+        <v>75</v>
+      </c>
+      <c r="B77" s="240"/>
+      <c r="C77" s="240"/>
+      <c r="D77" s="240"/>
+      <c r="E77" s="445" t="s">
+        <v>47</v>
+      </c>
+      <c r="F77" s="299"/>
+      <c r="G77" s="299"/>
+      <c r="H77" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="I77" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="J77" s="299" t="s">
+        <v>47</v>
+      </c>
+      <c r="K77" s="299"/>
+      <c r="L77" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="M77" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="N77" s="176" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="270"/>
+      <c r="B78" s="271"/>
+      <c r="C78" s="271"/>
+      <c r="D78" s="271"/>
+      <c r="E78" s="220"/>
+      <c r="F78" s="221"/>
+      <c r="G78" s="221"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6"/>
+      <c r="J78" s="221"/>
+      <c r="K78" s="221"/>
+      <c r="L78" s="6"/>
+      <c r="M78" s="6"/>
+      <c r="N78" s="38"/>
+    </row>
+    <row r="79" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="257" t="s">
+        <v>77</v>
+      </c>
+      <c r="B79" s="258"/>
+      <c r="C79" s="258"/>
+      <c r="D79" s="259"/>
+      <c r="E79" s="280" t="s">
+        <v>39</v>
+      </c>
+      <c r="F79" s="281"/>
+      <c r="G79" s="282"/>
+      <c r="H79" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="I79" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="J79" s="283" t="s">
+        <v>135</v>
+      </c>
+      <c r="K79" s="282"/>
+      <c r="L79" s="44"/>
+      <c r="M79" s="44"/>
+      <c r="N79" s="95"/>
+    </row>
+    <row r="80" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A80" s="284" t="s">
+        <v>78</v>
+      </c>
+      <c r="B80" s="285"/>
+      <c r="C80" s="285"/>
+      <c r="D80" s="285"/>
+      <c r="E80" s="231" t="s">
+        <v>79</v>
+      </c>
+      <c r="F80" s="232"/>
+      <c r="G80" s="232"/>
+      <c r="H80" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J80" s="232" t="s">
+        <v>79</v>
+      </c>
+      <c r="K80" s="232"/>
+      <c r="L80" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="M80" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="N80" s="31"/>
+    </row>
+    <row r="81" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="245"/>
+      <c r="B81" s="246"/>
+      <c r="C81" s="246"/>
+      <c r="D81" s="246"/>
+      <c r="E81" s="247"/>
+      <c r="F81" s="227"/>
+      <c r="G81" s="227"/>
+      <c r="H81" s="51"/>
+      <c r="I81" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="J81" s="227"/>
+      <c r="K81" s="227"/>
+      <c r="L81" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M81" s="9"/>
+      <c r="N81" s="11"/>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A82" s="228" t="s">
+        <v>80</v>
+      </c>
+      <c r="B82" s="229"/>
+      <c r="C82" s="229"/>
+      <c r="D82" s="230"/>
+      <c r="E82" s="445" t="s">
+        <v>47</v>
+      </c>
+      <c r="F82" s="299"/>
+      <c r="G82" s="299"/>
+      <c r="H82" s="496" t="s">
+        <v>47</v>
+      </c>
+      <c r="I82" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="J82" s="299" t="s">
+        <v>47</v>
+      </c>
+      <c r="K82" s="299"/>
+      <c r="L82" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="M82" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="N82" s="85" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="217"/>
+      <c r="B83" s="218"/>
+      <c r="C83" s="218"/>
+      <c r="D83" s="219"/>
+      <c r="E83" s="247"/>
+      <c r="F83" s="227"/>
+      <c r="G83" s="227"/>
+      <c r="H83" s="9"/>
+      <c r="I83" s="97"/>
+      <c r="J83" s="227"/>
+      <c r="K83" s="227"/>
+      <c r="L83" s="9"/>
+      <c r="M83" s="9"/>
+      <c r="N83" s="98"/>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A84" s="239" t="s">
+        <v>82</v>
+      </c>
+      <c r="B84" s="240"/>
+      <c r="C84" s="240"/>
+      <c r="D84" s="240"/>
+      <c r="E84" s="276"/>
+      <c r="F84" s="277"/>
+      <c r="G84" s="278"/>
+      <c r="H84" s="12"/>
+      <c r="I84" s="12"/>
+      <c r="J84" s="279"/>
+      <c r="K84" s="278"/>
+      <c r="L84" s="12"/>
+      <c r="M84" s="12"/>
+      <c r="N84" s="14"/>
+    </row>
+    <row r="85" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="270"/>
+      <c r="B85" s="271"/>
+      <c r="C85" s="271"/>
+      <c r="D85" s="271"/>
+      <c r="E85" s="272"/>
+      <c r="F85" s="273"/>
+      <c r="G85" s="274"/>
+      <c r="H85" s="68"/>
+      <c r="I85" s="68"/>
+      <c r="J85" s="221"/>
+      <c r="K85" s="221"/>
+      <c r="L85" s="68"/>
+      <c r="M85" s="69"/>
+      <c r="N85" s="70"/>
+    </row>
+    <row r="86" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A86" s="267" t="s">
+        <v>83</v>
+      </c>
+      <c r="B86" s="268"/>
+      <c r="C86" s="268"/>
+      <c r="D86" s="269"/>
+      <c r="E86" s="231" t="s">
+        <v>250</v>
+      </c>
+      <c r="F86" s="232"/>
+      <c r="G86" s="232"/>
+      <c r="H86" s="99" t="s">
+        <v>250</v>
+      </c>
+      <c r="I86" s="99" t="s">
+        <v>250</v>
+      </c>
+      <c r="J86" s="275" t="s">
+        <v>250</v>
+      </c>
+      <c r="K86" s="275"/>
+      <c r="L86" s="99" t="s">
+        <v>250</v>
+      </c>
+      <c r="M86" s="99"/>
+      <c r="N86" s="64"/>
+    </row>
+    <row r="87" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="250"/>
+      <c r="B87" s="251"/>
+      <c r="C87" s="251"/>
+      <c r="D87" s="252"/>
+      <c r="E87" s="247"/>
+      <c r="F87" s="227"/>
+      <c r="G87" s="227"/>
+      <c r="H87" s="146"/>
+      <c r="I87" s="146"/>
+      <c r="J87" s="301"/>
+      <c r="K87" s="301"/>
+      <c r="L87" s="146"/>
+      <c r="M87" s="146"/>
+      <c r="N87" s="90"/>
+    </row>
+    <row r="88" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A88" s="267" t="s">
+        <v>85</v>
+      </c>
+      <c r="B88" s="268"/>
+      <c r="C88" s="268"/>
+      <c r="D88" s="269"/>
+      <c r="E88" s="307" t="s">
+        <v>86</v>
+      </c>
+      <c r="F88" s="286"/>
+      <c r="G88" s="286"/>
+      <c r="H88" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="I88" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="J88" s="286" t="s">
+        <v>86</v>
+      </c>
+      <c r="K88" s="286"/>
+      <c r="L88" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="M88" s="12"/>
+      <c r="N88" s="145"/>
+    </row>
+    <row r="89" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="250"/>
+      <c r="B89" s="251"/>
+      <c r="C89" s="251"/>
+      <c r="D89" s="252"/>
+      <c r="E89" s="253" t="s">
+        <v>87</v>
+      </c>
+      <c r="F89" s="254"/>
+      <c r="G89" s="254"/>
+      <c r="H89" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J89" s="221" t="s">
+        <v>87</v>
+      </c>
+      <c r="K89" s="221"/>
+      <c r="L89" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="M89" s="6"/>
+      <c r="N89" s="70"/>
+    </row>
+    <row r="90" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="257" t="s">
+        <v>88</v>
+      </c>
+      <c r="B90" s="258"/>
+      <c r="C90" s="258"/>
+      <c r="D90" s="259"/>
+      <c r="E90" s="260" t="s">
+        <v>39</v>
+      </c>
+      <c r="F90" s="261"/>
+      <c r="G90" s="262"/>
+      <c r="H90" s="101" t="s">
+        <v>39</v>
+      </c>
+      <c r="I90" s="101" t="s">
+        <v>39</v>
+      </c>
+      <c r="J90" s="263" t="s">
+        <v>39</v>
+      </c>
+      <c r="K90" s="264"/>
+      <c r="L90" s="192"/>
+      <c r="M90" s="192"/>
+      <c r="N90" s="102"/>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A91" s="228" t="s">
+        <v>90</v>
+      </c>
+      <c r="B91" s="229"/>
+      <c r="C91" s="229"/>
+      <c r="D91" s="230"/>
+      <c r="E91" s="255" t="s">
+        <v>91</v>
+      </c>
+      <c r="F91" s="256"/>
+      <c r="G91" s="256"/>
+      <c r="H91" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="I91" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="J91" s="256" t="s">
+        <v>91</v>
+      </c>
+      <c r="K91" s="256"/>
+      <c r="L91" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="M91" s="12"/>
+      <c r="N91" s="104"/>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A92" s="212"/>
+      <c r="B92" s="213"/>
+      <c r="C92" s="213"/>
+      <c r="D92" s="214"/>
+      <c r="E92" s="215" t="s">
+        <v>92</v>
+      </c>
+      <c r="F92" s="216"/>
+      <c r="G92" s="216"/>
+      <c r="H92" s="105" t="s">
+        <v>94</v>
+      </c>
+      <c r="I92" s="105" t="s">
+        <v>92</v>
+      </c>
+      <c r="J92" s="216" t="s">
+        <v>418</v>
+      </c>
+      <c r="K92" s="216"/>
+      <c r="L92" s="105" t="s">
+        <v>92</v>
+      </c>
+      <c r="M92" s="6"/>
+      <c r="N92" s="35"/>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A93" s="212"/>
+      <c r="B93" s="213"/>
+      <c r="C93" s="213"/>
+      <c r="D93" s="214"/>
+      <c r="E93" s="248" t="s">
+        <v>93</v>
+      </c>
+      <c r="F93" s="249"/>
+      <c r="G93" s="249"/>
+      <c r="H93" s="34"/>
+      <c r="I93" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="J93" s="216"/>
+      <c r="K93" s="216"/>
+      <c r="L93" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="M93" s="107"/>
+      <c r="N93" s="108"/>
+    </row>
+    <row r="94" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="250"/>
+      <c r="B94" s="251"/>
+      <c r="C94" s="251"/>
+      <c r="D94" s="252"/>
+      <c r="E94" s="253"/>
+      <c r="F94" s="254"/>
+      <c r="G94" s="254"/>
+      <c r="H94" s="69"/>
+      <c r="I94" s="68"/>
+      <c r="J94" s="221"/>
+      <c r="K94" s="221"/>
+      <c r="L94" s="87" t="s">
+        <v>94</v>
+      </c>
+      <c r="M94" s="87"/>
+      <c r="N94" s="70"/>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A95" s="239" t="s">
+        <v>96</v>
+      </c>
+      <c r="B95" s="240"/>
+      <c r="C95" s="240"/>
+      <c r="D95" s="240"/>
+      <c r="E95" s="231"/>
+      <c r="F95" s="232"/>
+      <c r="G95" s="232"/>
+      <c r="H95" s="71"/>
+      <c r="I95" s="3"/>
+      <c r="J95" s="232"/>
+      <c r="K95" s="232"/>
+      <c r="L95" s="28"/>
+      <c r="M95" s="28"/>
+      <c r="N95" s="29"/>
+    </row>
+    <row r="96" spans="1:14" ht="46.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="245"/>
+      <c r="B96" s="246"/>
+      <c r="C96" s="246"/>
+      <c r="D96" s="246"/>
+      <c r="E96" s="247"/>
+      <c r="F96" s="227"/>
+      <c r="G96" s="227"/>
+      <c r="H96" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I96" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J96" s="227"/>
+      <c r="K96" s="227"/>
+      <c r="L96" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="M96" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="N96" s="109"/>
+    </row>
+    <row r="97" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="233" t="s">
+        <v>97</v>
+      </c>
+      <c r="B97" s="234"/>
+      <c r="C97" s="234"/>
+      <c r="D97" s="234"/>
+      <c r="E97" s="497" t="s">
+        <v>47</v>
+      </c>
+      <c r="F97" s="498"/>
+      <c r="G97" s="499"/>
+      <c r="H97" s="500" t="s">
+        <v>47</v>
+      </c>
+      <c r="I97" s="148" t="s">
+        <v>47</v>
+      </c>
+      <c r="J97" s="501" t="s">
+        <v>47</v>
+      </c>
+      <c r="K97" s="499"/>
+      <c r="L97" s="148" t="s">
+        <v>47</v>
+      </c>
+      <c r="M97" s="148" t="s">
+        <v>47</v>
+      </c>
+      <c r="N97" s="111"/>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A98" s="239" t="s">
+        <v>98</v>
+      </c>
+      <c r="B98" s="240"/>
+      <c r="C98" s="240"/>
+      <c r="D98" s="240"/>
+      <c r="E98" s="407" t="s">
+        <v>47</v>
+      </c>
+      <c r="F98" s="408"/>
+      <c r="G98" s="409"/>
+      <c r="H98" s="502" t="s">
+        <v>47</v>
+      </c>
+      <c r="I98" s="502" t="s">
+        <v>47</v>
+      </c>
+      <c r="J98" s="503" t="s">
+        <v>47</v>
+      </c>
+      <c r="K98" s="504"/>
+      <c r="L98" s="502" t="s">
+        <v>47</v>
+      </c>
+      <c r="M98" s="133" t="s">
+        <v>47</v>
+      </c>
+      <c r="N98" s="112"/>
+    </row>
+    <row r="99" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="222"/>
+      <c r="B99" s="223"/>
+      <c r="C99" s="223"/>
+      <c r="D99" s="223"/>
+      <c r="E99" s="448"/>
+      <c r="F99" s="449"/>
+      <c r="G99" s="420"/>
+      <c r="H99" s="159"/>
+      <c r="I99" s="68"/>
+      <c r="J99" s="467"/>
+      <c r="K99" s="468"/>
+      <c r="L99" s="68"/>
+      <c r="M99" s="6"/>
+      <c r="N99" s="166"/>
+    </row>
+    <row r="100" spans="1:14" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="228" t="s">
+        <v>101</v>
+      </c>
+      <c r="B100" s="229"/>
+      <c r="C100" s="229"/>
+      <c r="D100" s="230"/>
+      <c r="E100" s="231" t="s">
+        <v>732</v>
+      </c>
+      <c r="F100" s="232"/>
+      <c r="G100" s="232"/>
+      <c r="H100" s="48" t="s">
+        <v>733</v>
+      </c>
+      <c r="I100" s="48" t="s">
+        <v>733</v>
+      </c>
+      <c r="J100" s="232"/>
+      <c r="K100" s="232"/>
+      <c r="L100" s="3"/>
+      <c r="M100" s="3"/>
+      <c r="N100" s="59"/>
+    </row>
+    <row r="101" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A101" s="212"/>
+      <c r="B101" s="213"/>
+      <c r="C101" s="213"/>
+      <c r="D101" s="214"/>
+      <c r="E101" s="215" t="s">
+        <v>734</v>
+      </c>
+      <c r="F101" s="216"/>
+      <c r="G101" s="216"/>
+      <c r="H101" s="32" t="s">
+        <v>663</v>
+      </c>
+      <c r="I101" s="32"/>
+      <c r="J101" s="216" t="s">
+        <v>736</v>
+      </c>
+      <c r="K101" s="216"/>
+      <c r="L101" s="32" t="s">
+        <v>663</v>
+      </c>
+      <c r="M101" s="32"/>
+      <c r="N101" s="33"/>
+    </row>
+    <row r="102" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="217"/>
+      <c r="B102" s="218"/>
+      <c r="C102" s="218"/>
+      <c r="D102" s="219"/>
+      <c r="E102" s="220"/>
+      <c r="F102" s="221"/>
+      <c r="G102" s="221"/>
+      <c r="H102" s="6"/>
+      <c r="I102" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="J102" s="221"/>
+      <c r="K102" s="221"/>
+      <c r="L102" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M102" s="6"/>
+      <c r="N102" s="70"/>
+    </row>
+    <row r="103" spans="1:14" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="204" t="s">
+        <v>103</v>
+      </c>
+      <c r="B103" s="205"/>
+      <c r="C103" s="205"/>
+      <c r="D103" s="205"/>
+      <c r="E103" s="206"/>
+      <c r="F103" s="207"/>
+      <c r="G103" s="207"/>
+      <c r="H103" s="47"/>
+      <c r="I103" s="113"/>
+      <c r="J103" s="232"/>
+      <c r="K103" s="232"/>
+      <c r="L103" s="3"/>
+      <c r="M103" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N103" s="8"/>
+    </row>
+    <row r="104" spans="1:14" ht="42.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="208"/>
+      <c r="B104" s="209"/>
+      <c r="C104" s="209"/>
+      <c r="D104" s="209"/>
+      <c r="E104" s="395"/>
+      <c r="F104" s="396"/>
+      <c r="G104" s="396"/>
+      <c r="H104" s="50"/>
+      <c r="I104" s="132"/>
+      <c r="J104" s="227" t="s">
+        <v>16</v>
+      </c>
+      <c r="K104" s="227"/>
+      <c r="L104" s="9"/>
+      <c r="M104" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N104" s="16"/>
+    </row>
+    <row r="106" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="107" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="195" t="s">
+        <v>104</v>
+      </c>
+      <c r="B107" s="196"/>
+      <c r="C107" s="196"/>
+      <c r="D107" s="196"/>
+      <c r="E107" s="197" t="s">
+        <v>105</v>
+      </c>
+      <c r="F107" s="198"/>
+      <c r="G107" s="199"/>
+      <c r="H107" s="116" t="s">
+        <v>105</v>
+      </c>
+      <c r="I107" s="116" t="s">
+        <v>105</v>
+      </c>
+      <c r="J107" s="197" t="s">
+        <v>105</v>
+      </c>
+      <c r="K107" s="199"/>
+      <c r="L107" s="116" t="s">
+        <v>105</v>
+      </c>
+      <c r="M107" s="117"/>
+      <c r="N107" s="118"/>
+    </row>
+    <row r="108" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="200" t="s">
+        <v>106</v>
+      </c>
+      <c r="B108" s="201"/>
+      <c r="C108" s="201"/>
+      <c r="D108" s="202"/>
+      <c r="E108" s="203" t="s">
+        <v>107</v>
+      </c>
+      <c r="F108" s="198"/>
+      <c r="G108" s="199"/>
+      <c r="H108" s="119" t="s">
+        <v>107</v>
+      </c>
+      <c r="I108" s="119"/>
+      <c r="J108" s="203" t="s">
+        <v>107</v>
+      </c>
+      <c r="K108" s="199"/>
+      <c r="L108" s="119" t="s">
+        <v>107</v>
+      </c>
+      <c r="M108" s="117"/>
+      <c r="N108" s="118"/>
+    </row>
+  </sheetData>
+  <mergeCells count="318">
+    <mergeCell ref="J71:K71"/>
+    <mergeCell ref="J72:K72"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="E71:G71"/>
+    <mergeCell ref="E72:G72"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="E65:G65"/>
+    <mergeCell ref="A107:D107"/>
+    <mergeCell ref="E107:G107"/>
+    <mergeCell ref="J107:K107"/>
+    <mergeCell ref="A108:D108"/>
+    <mergeCell ref="E108:G108"/>
+    <mergeCell ref="J108:K108"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="E103:G103"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="A104:D104"/>
+    <mergeCell ref="E104:G104"/>
+    <mergeCell ref="J104:K104"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="E101:G101"/>
+    <mergeCell ref="J101:K101"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="E102:G102"/>
+    <mergeCell ref="J102:K102"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="E99:G99"/>
+    <mergeCell ref="J99:K99"/>
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="E100:G100"/>
+    <mergeCell ref="J100:K100"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="E97:G97"/>
+    <mergeCell ref="J97:K97"/>
+    <mergeCell ref="A98:D98"/>
+    <mergeCell ref="E98:G98"/>
+    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="A95:D95"/>
+    <mergeCell ref="E95:G95"/>
+    <mergeCell ref="J95:K95"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="E96:G96"/>
+    <mergeCell ref="J96:K96"/>
+    <mergeCell ref="A93:D93"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="J93:K93"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="E94:G94"/>
+    <mergeCell ref="J94:K94"/>
+    <mergeCell ref="A91:D91"/>
+    <mergeCell ref="E91:G91"/>
+    <mergeCell ref="J91:K91"/>
+    <mergeCell ref="A92:D92"/>
+    <mergeCell ref="E92:G92"/>
+    <mergeCell ref="J92:K92"/>
+    <mergeCell ref="A89:D89"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="J89:K89"/>
+    <mergeCell ref="A90:D90"/>
+    <mergeCell ref="E90:G90"/>
+    <mergeCell ref="J90:K90"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="E87:G87"/>
+    <mergeCell ref="J87:K87"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="E88:G88"/>
+    <mergeCell ref="J88:K88"/>
+    <mergeCell ref="A85:D85"/>
+    <mergeCell ref="E85:G85"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="A86:D86"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="A83:D83"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="E84:G84"/>
+    <mergeCell ref="J84:K84"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="E81:G81"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="A82:D82"/>
+    <mergeCell ref="E82:G82"/>
+    <mergeCell ref="J82:K82"/>
+    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="E79:G79"/>
+    <mergeCell ref="J79:K79"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="E80:G80"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="E78:G78"/>
+    <mergeCell ref="J78:K78"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="E75:G75"/>
+    <mergeCell ref="J75:K75"/>
+    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="E76:G76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="J73:K73"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="J69:K69"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="E70:G70"/>
+    <mergeCell ref="J70:K70"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="E67:G67"/>
+    <mergeCell ref="J67:K67"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="E68:G68"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="J63:K63"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="E66:G66"/>
+    <mergeCell ref="J66:K66"/>
+    <mergeCell ref="J64:K64"/>
+    <mergeCell ref="J65:K65"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="J62:K62"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="E60:G60"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="J57:K57"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="E52:G52"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="J2:K2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/data/tyovuorot_2026.xlsx
+++ b/data/tyovuorot_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solemofi-my.sharepoint.com/personal/pirjo_kleemola_sol_fi/Documents/Vuorolistat/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5777" documentId="8_{F7973BC1-41AE-4E6A-B0A3-B34DE794A113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFF270BE-987C-40D6-BDDE-D82DEDB79797}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="13_ncr:1_{94D15033-6EA2-40BA-8B61-AC7D4FEFD9F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64F7BFFD-880F-48B4-92C9-4C92866A47A4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="8" activeTab="18" xr2:uid="{72DDB042-8082-4351-9446-F508A0968C0B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="9" activeTab="19" xr2:uid="{72DDB042-8082-4351-9446-F508A0968C0B}"/>
   </bookViews>
   <sheets>
     <sheet name="vko 2" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,7 @@
     <sheet name="vko 18" sheetId="17" r:id="rId17"/>
     <sheet name="vko 19" sheetId="18" r:id="rId18"/>
     <sheet name="vko 20" sheetId="19" r:id="rId19"/>
+    <sheet name="vko 21" sheetId="20" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6680" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7080" uniqueCount="833">
   <si>
     <t>Ashim Acharya</t>
   </si>
@@ -2373,15 +2374,9 @@
     <t>CM Rusko kassa-alue perussiivousta klo 5-8, CM Kaakkuri kauppakäytävä ikkunoiden pesut klo 8-</t>
   </si>
   <si>
-    <t>CM Rusko kassa-alue perussiivousta klo 5-8</t>
-  </si>
-  <si>
     <t>Esperi Ihmemaantie, myös torstai huoneet</t>
   </si>
   <si>
-    <t>CM Kaakkuri ikkunoiden pesuja Mirjan kanssa klo 8-</t>
-  </si>
-  <si>
     <t>CM Kaakkuri liha-alue ja keittiö klo 18.50-</t>
   </si>
   <si>
@@ -2437,6 +2432,129 @@
   </si>
   <si>
     <t>CM Rusko kassa-alue perussiivousta klo 5-8, CM Kaakkuri kauppakäytävä ikkunoiden pesut klo 8- Sanna L kanssa</t>
+  </si>
+  <si>
+    <t>Esperi Virkku Veeran kanssa</t>
+  </si>
+  <si>
+    <t>Esperi Virkku Nadjan kanssa</t>
+  </si>
+  <si>
+    <t>SOL Pesula ikkunat</t>
+  </si>
+  <si>
+    <t>vko 21</t>
+  </si>
+  <si>
+    <t>MA 18.5</t>
+  </si>
+  <si>
+    <t>TI 19.5</t>
+  </si>
+  <si>
+    <t>KE 20.5</t>
+  </si>
+  <si>
+    <t>TO 21.5</t>
+  </si>
+  <si>
+    <t>PE 22.5</t>
+  </si>
+  <si>
+    <t>LA 23.5</t>
+  </si>
+  <si>
+    <t>SU 24.5</t>
+  </si>
+  <si>
+    <t>Lotta Rasi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">klo 17.45- CM Rusko liha/myymälä </t>
+  </si>
+  <si>
+    <t>CM Kaakkuri ostoskärryjen pesut Raimon kanssa klo 20-</t>
+  </si>
+  <si>
+    <t>CM Rusko tiski/myymälä klo 17.30-</t>
+  </si>
+  <si>
+    <t>CM Rusko liha/myymälä klo 17.45-</t>
+  </si>
+  <si>
+    <t>CM Rusko pukuhuoneet perussiivoukset 1.krs Arjan kanssa klo 11-</t>
+  </si>
+  <si>
+    <t>CM Kaakkuri klo 21 palvelutiski takapöytien alusten pesu kuivahöyrylaitteella</t>
+  </si>
+  <si>
+    <t>CM Raksila hevi alueen muutos pesua klo 5-</t>
+  </si>
+  <si>
+    <t>CM Rusko kassa-alue perussiivousta klo 5-8 Sannan kanssa</t>
+  </si>
+  <si>
+    <t>CM Kaakkuri klo 4/5 elintarvike läiskien kivenhoito Sannan kanssa</t>
+  </si>
+  <si>
+    <t>CM Rusko kassa-alueen pesuja klo 5 Mirjan kanssa</t>
+  </si>
+  <si>
+    <t>CM Kaakkuri klo 4/5 elintarvike läiskien kivenhoito Mirjan kanssa</t>
+  </si>
+  <si>
+    <t>CM Rusko 1.krs pukuhuoneet perussiivous Nadjan kanssa</t>
+  </si>
+  <si>
+    <t>CM Rusko tiski/myymälä klo 17.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUKA Gneissikuja </t>
+  </si>
+  <si>
+    <t>TerraPatris la vuoro ja vahauksia Joelin kanssa</t>
+  </si>
+  <si>
+    <t>CM Raksila ulkoikkunoiden pesut ja kärryalueen ikkunoiden pesut 8-</t>
+  </si>
+  <si>
+    <t>CM Kaakkuri ostoskärryjen pesut klo 20 Emtiuksen kanssa</t>
+  </si>
+  <si>
+    <t>CM Kaakkuri ostoskärryjen pesut klo 20-</t>
+  </si>
+  <si>
+    <t>Bauhaus plakaatit ja levyleikkaamo yläpölylaitteella</t>
+  </si>
+  <si>
+    <t>CM Kaakkuri Eijan kanssa Eijan alue klo 4-</t>
+  </si>
+  <si>
+    <t>CM Kaakkuri Eijan alue Eijan kanssa klo 4</t>
+  </si>
+  <si>
+    <t>CM Raksila klo 19 2.krs taukotila lattia, vihreä lattia ja 2,krs käytävä Nadjan kanssa</t>
+  </si>
+  <si>
+    <t>CM Raksila klo 19 2.krs taukotila lattia, vihreä lattia ja 2,krs käytävä Raimon kanssa</t>
+  </si>
+  <si>
+    <t>Terrapatris opettelu</t>
+  </si>
+  <si>
+    <t>TerraPatris opettelu</t>
+  </si>
+  <si>
+    <t>Bauhaus klo 8- kohteen kertausta</t>
+  </si>
+  <si>
+    <t>työsopimus ja perehdytys Lotta Rasi klo 8, Esperi Virkku asty klo 10</t>
+  </si>
+  <si>
+    <t>Wetteri Äimäkuja 3, 2,5h</t>
+  </si>
+  <si>
+    <t>CM Rusko pienen Hakon katsominen</t>
   </si>
 </sst>
 </file>
@@ -2586,7 +2704,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="75">
+  <borders count="76">
     <border>
       <left/>
       <right/>
@@ -3504,11 +3622,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="564">
+  <cellXfs count="571">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -4973,9 +5102,6 @@
     <xf numFmtId="164" fontId="7" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="165" fontId="7" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -4985,17 +5111,8 @@
     <xf numFmtId="165" fontId="7" fillId="2" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -5006,16 +5123,22 @@
     <xf numFmtId="164" fontId="7" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5024,21 +5147,27 @@
     <xf numFmtId="164" fontId="7" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="7" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -5102,20 +5231,14 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -5126,14 +5249,41 @@
     <xf numFmtId="164" fontId="3" fillId="2" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -29986,7 +30136,7 @@
       </c>
       <c r="K45" s="248"/>
       <c r="L45" s="12" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="M45" s="12" t="s">
         <v>76</v>
@@ -31246,7 +31396,7 @@
       <c r="J100" s="237"/>
       <c r="K100" s="237"/>
       <c r="L100" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="M100" s="3"/>
       <c r="N100" s="59"/>
@@ -31726,27 +31876,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="561" t="s">
+      <c r="A1" s="553" t="s">
         <v>745</v>
       </c>
-      <c r="B1" s="562"/>
-      <c r="C1" s="562"/>
-      <c r="D1" s="563"/>
-      <c r="E1" s="558" t="s">
+      <c r="B1" s="554"/>
+      <c r="C1" s="554"/>
+      <c r="D1" s="555"/>
+      <c r="E1" s="556" t="s">
         <v>746</v>
       </c>
-      <c r="F1" s="559"/>
-      <c r="G1" s="560"/>
+      <c r="F1" s="557"/>
+      <c r="G1" s="558"/>
       <c r="H1" s="1" t="s">
         <v>747</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="J1" s="556" t="s">
+      <c r="J1" s="559" t="s">
         <v>749</v>
       </c>
-      <c r="K1" s="557"/>
+      <c r="K1" s="560"/>
       <c r="L1" s="1" t="s">
         <v>750</v>
       </c>
@@ -31758,12 +31908,12 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="553" t="s">
+      <c r="A2" s="561" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="554"/>
-      <c r="C2" s="554"/>
-      <c r="D2" s="555"/>
+      <c r="B2" s="562"/>
+      <c r="C2" s="562"/>
+      <c r="D2" s="563"/>
       <c r="E2" s="246"/>
       <c r="F2" s="247"/>
       <c r="G2" s="248"/>
@@ -31866,11 +32016,13 @@
       <c r="F6" s="247"/>
       <c r="G6" s="248"/>
       <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="I6" s="4" t="s">
+        <v>197</v>
+      </c>
       <c r="J6" s="249"/>
       <c r="K6" s="248"/>
       <c r="L6" s="3" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="31"/>
@@ -31945,20 +32097,20 @@
       <c r="C10" s="364"/>
       <c r="D10" s="544"/>
       <c r="E10" s="548" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="F10" s="549"/>
       <c r="G10" s="550"/>
       <c r="H10" s="126" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="I10" s="32" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="J10" s="368"/>
       <c r="K10" s="367"/>
       <c r="L10" s="32" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="M10" s="32" t="s">
         <v>391</v>
@@ -31970,10 +32122,10 @@
       <c r="B11" s="228"/>
       <c r="C11" s="228"/>
       <c r="D11" s="386"/>
-      <c r="E11" s="530" t="s">
+      <c r="E11" s="527" t="s">
         <v>712</v>
       </c>
-      <c r="F11" s="531"/>
+      <c r="F11" s="528"/>
       <c r="G11" s="494"/>
       <c r="H11" s="76" t="s">
         <v>712</v>
@@ -32075,10 +32227,10 @@
       <c r="I15" s="3"/>
       <c r="J15" s="249"/>
       <c r="K15" s="248"/>
-      <c r="L15" s="3" t="s">
+      <c r="L15" s="3"/>
+      <c r="M15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="M15" s="3"/>
       <c r="N15" s="8"/>
     </row>
     <row r="16" spans="1:14" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -32099,10 +32251,10 @@
       </c>
       <c r="J16" s="350"/>
       <c r="K16" s="231"/>
-      <c r="L16" s="9" t="s">
+      <c r="L16" s="9"/>
+      <c r="M16" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="M16" s="9"/>
       <c r="N16" s="16"/>
     </row>
     <row r="17" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -32126,22 +32278,24 @@
       <c r="J17" s="249"/>
       <c r="K17" s="248"/>
       <c r="L17" s="12" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="M17" s="12"/>
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="507"/>
-      <c r="B18" s="508"/>
-      <c r="C18" s="508"/>
-      <c r="D18" s="509"/>
+      <c r="A18" s="506"/>
+      <c r="B18" s="507"/>
+      <c r="C18" s="507"/>
+      <c r="D18" s="508"/>
       <c r="E18" s="365" t="s">
         <v>763</v>
       </c>
       <c r="F18" s="366"/>
       <c r="G18" s="367"/>
-      <c r="H18" s="32"/>
+      <c r="H18" s="32" t="s">
+        <v>792</v>
+      </c>
       <c r="I18" s="32"/>
       <c r="J18" s="368" t="s">
         <v>122</v>
@@ -32156,22 +32310,22 @@
       </c>
     </row>
     <row r="19" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="507"/>
-      <c r="B19" s="508"/>
-      <c r="C19" s="508"/>
-      <c r="D19" s="509"/>
+      <c r="A19" s="506"/>
+      <c r="B19" s="507"/>
+      <c r="C19" s="507"/>
+      <c r="D19" s="508"/>
       <c r="E19" s="365" t="s">
         <v>760</v>
       </c>
       <c r="F19" s="366"/>
       <c r="G19" s="367"/>
       <c r="H19" s="32"/>
-      <c r="I19" s="105" t="s">
-        <v>219</v>
-      </c>
+      <c r="I19" s="105"/>
       <c r="J19" s="368"/>
       <c r="K19" s="367"/>
-      <c r="L19" s="32"/>
+      <c r="L19" s="105" t="s">
+        <v>219</v>
+      </c>
       <c r="M19" s="32"/>
       <c r="N19" s="35"/>
     </row>
@@ -32179,9 +32333,9 @@
       <c r="A20" s="250"/>
       <c r="B20" s="251"/>
       <c r="C20" s="251"/>
-      <c r="D20" s="506"/>
+      <c r="D20" s="509"/>
       <c r="E20" s="229" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="F20" s="230"/>
       <c r="G20" s="231"/>
@@ -32192,7 +32346,7 @@
       <c r="J20" s="350"/>
       <c r="K20" s="231"/>
       <c r="L20" s="9" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="M20" s="9" t="s">
         <v>759</v>
@@ -32273,9 +32427,7 @@
       </c>
       <c r="F23" s="247"/>
       <c r="G23" s="248"/>
-      <c r="H23" s="3" t="s">
-        <v>35</v>
-      </c>
+      <c r="H23" s="3"/>
       <c r="I23" s="3" t="s">
         <v>767</v>
       </c>
@@ -32311,7 +32463,7 @@
       <c r="M24" s="32"/>
       <c r="N24" s="39"/>
     </row>
-    <row r="25" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="227"/>
       <c r="B25" s="228"/>
       <c r="C25" s="228"/>
@@ -32420,7 +32572,7 @@
       <c r="F29" s="465"/>
       <c r="G29" s="466"/>
       <c r="H29" s="48" t="s">
-        <v>189</v>
+        <v>793</v>
       </c>
       <c r="I29" s="62" t="s">
         <v>175</v>
@@ -32508,10 +32660,10 @@
       <c r="B34" s="228"/>
       <c r="C34" s="228"/>
       <c r="D34" s="386"/>
-      <c r="E34" s="530" t="s">
+      <c r="E34" s="527" t="s">
         <v>760</v>
       </c>
-      <c r="F34" s="531"/>
+      <c r="F34" s="528"/>
       <c r="G34" s="494"/>
       <c r="H34" s="53"/>
       <c r="I34" s="9"/>
@@ -32533,7 +32685,7 @@
       <c r="C35" s="245"/>
       <c r="D35" s="421"/>
       <c r="E35" s="246" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="F35" s="247"/>
       <c r="G35" s="248"/>
@@ -32551,11 +32703,11 @@
       <c r="M35" s="13"/>
       <c r="N35" s="104"/>
     </row>
-    <row r="36" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="250"/>
       <c r="B36" s="251"/>
       <c r="C36" s="251"/>
-      <c r="D36" s="506"/>
+      <c r="D36" s="509"/>
       <c r="E36" s="229" t="s">
         <v>24</v>
       </c>
@@ -32582,8 +32734,8 @@
       <c r="B37" s="245"/>
       <c r="C37" s="245"/>
       <c r="D37" s="421"/>
-      <c r="E37" s="510"/>
-      <c r="F37" s="511"/>
+      <c r="E37" s="515"/>
+      <c r="F37" s="516"/>
       <c r="G37" s="298"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -32597,7 +32749,7 @@
       <c r="A38" s="250"/>
       <c r="B38" s="251"/>
       <c r="C38" s="251"/>
-      <c r="D38" s="506"/>
+      <c r="D38" s="509"/>
       <c r="E38" s="229" t="s">
         <v>758</v>
       </c>
@@ -32626,7 +32778,9 @@
       <c r="B39" s="245"/>
       <c r="C39" s="245"/>
       <c r="D39" s="421"/>
-      <c r="E39" s="246"/>
+      <c r="E39" s="246" t="s">
+        <v>197</v>
+      </c>
       <c r="F39" s="247"/>
       <c r="G39" s="248"/>
       <c r="H39" s="12"/>
@@ -32695,7 +32849,7 @@
       <c r="A42" s="250"/>
       <c r="B42" s="251"/>
       <c r="C42" s="251"/>
-      <c r="D42" s="506"/>
+      <c r="D42" s="509"/>
       <c r="E42" s="229" t="s">
         <v>32</v>
       </c>
@@ -32729,16 +32883,14 @@
       </c>
       <c r="F43" s="247"/>
       <c r="G43" s="248"/>
-      <c r="H43" s="3" t="s">
-        <v>189</v>
-      </c>
+      <c r="H43" s="3"/>
       <c r="I43" s="3" t="s">
-        <v>772</v>
+        <v>137</v>
       </c>
       <c r="J43" s="249"/>
       <c r="K43" s="248"/>
       <c r="L43" s="3" t="s">
-        <v>788</v>
+        <v>137</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>137</v>
@@ -32749,13 +32901,13 @@
       <c r="A44" s="250"/>
       <c r="B44" s="251"/>
       <c r="C44" s="251"/>
-      <c r="D44" s="506"/>
+      <c r="D44" s="509"/>
       <c r="E44" s="229"/>
       <c r="F44" s="230"/>
       <c r="G44" s="231"/>
       <c r="H44" s="6"/>
       <c r="I44" s="6" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="J44" s="350"/>
       <c r="K44" s="231"/>
@@ -32781,21 +32933,21 @@
         <v>716</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="J45" s="249"/>
       <c r="K45" s="248"/>
       <c r="L45" s="3" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="M45" s="3"/>
       <c r="N45" s="64"/>
     </row>
     <row r="46" spans="1:14" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="507"/>
-      <c r="B46" s="508"/>
-      <c r="C46" s="508"/>
-      <c r="D46" s="509"/>
+      <c r="A46" s="506"/>
+      <c r="B46" s="507"/>
+      <c r="C46" s="507"/>
+      <c r="D46" s="508"/>
       <c r="E46" s="365" t="s">
         <v>760</v>
       </c>
@@ -32817,7 +32969,7 @@
       <c r="A47" s="250"/>
       <c r="B47" s="251"/>
       <c r="C47" s="251"/>
-      <c r="D47" s="506"/>
+      <c r="D47" s="509"/>
       <c r="E47" s="229"/>
       <c r="F47" s="230"/>
       <c r="G47" s="231"/>
@@ -32836,7 +32988,9 @@
       <c r="B48" s="245"/>
       <c r="C48" s="245"/>
       <c r="D48" s="421"/>
-      <c r="E48" s="246"/>
+      <c r="E48" s="246" t="s">
+        <v>197</v>
+      </c>
       <c r="F48" s="247"/>
       <c r="G48" s="248"/>
       <c r="H48" s="12"/>
@@ -32851,9 +33005,9 @@
       <c r="A49" s="250"/>
       <c r="B49" s="251"/>
       <c r="C49" s="251"/>
-      <c r="D49" s="506"/>
-      <c r="E49" s="521"/>
-      <c r="F49" s="522"/>
+      <c r="D49" s="509"/>
+      <c r="E49" s="519"/>
+      <c r="F49" s="520"/>
       <c r="G49" s="473"/>
       <c r="H49" s="68"/>
       <c r="I49" s="68"/>
@@ -32921,16 +33075,14 @@
       </c>
       <c r="F52" s="436"/>
       <c r="G52" s="437"/>
-      <c r="H52" s="3" t="s">
-        <v>189</v>
-      </c>
+      <c r="H52" s="3"/>
       <c r="I52" s="3" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="J52" s="249"/>
       <c r="K52" s="248"/>
       <c r="L52" s="3" t="s">
-        <v>189</v>
+        <v>786</v>
       </c>
       <c r="M52" s="3"/>
       <c r="N52" s="8"/>
@@ -32939,7 +33091,7 @@
       <c r="A53" s="250"/>
       <c r="B53" s="251"/>
       <c r="C53" s="251"/>
-      <c r="D53" s="506"/>
+      <c r="D53" s="509"/>
       <c r="E53" s="229"/>
       <c r="F53" s="230"/>
       <c r="G53" s="231"/>
@@ -32947,7 +33099,9 @@
       <c r="I53" s="9"/>
       <c r="J53" s="350"/>
       <c r="K53" s="231"/>
-      <c r="L53" s="9"/>
+      <c r="L53" s="9" t="s">
+        <v>197</v>
+      </c>
       <c r="M53" s="9"/>
       <c r="N53" s="16"/>
     </row>
@@ -32958,7 +33112,9 @@
       <c r="B54" s="245"/>
       <c r="C54" s="245"/>
       <c r="D54" s="421"/>
-      <c r="E54" s="246"/>
+      <c r="E54" s="246" t="s">
+        <v>197</v>
+      </c>
       <c r="F54" s="247"/>
       <c r="G54" s="248"/>
       <c r="H54" s="12"/>
@@ -32973,7 +33129,7 @@
       <c r="A55" s="250"/>
       <c r="B55" s="251"/>
       <c r="C55" s="251"/>
-      <c r="D55" s="506"/>
+      <c r="D55" s="509"/>
       <c r="E55" s="229" t="s">
         <v>120</v>
       </c>
@@ -32986,7 +33142,7 @@
       <c r="J55" s="350"/>
       <c r="K55" s="231"/>
       <c r="L55" s="9" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="M55" s="9" t="s">
         <v>9</v>
@@ -33026,10 +33182,10 @@
       <c r="B57" s="525"/>
       <c r="C57" s="525"/>
       <c r="D57" s="526"/>
-      <c r="E57" s="530" t="s">
+      <c r="E57" s="527" t="s">
         <v>18</v>
       </c>
-      <c r="F57" s="531"/>
+      <c r="F57" s="528"/>
       <c r="G57" s="494"/>
       <c r="H57" s="21" t="s">
         <v>19</v>
@@ -33048,12 +33204,12 @@
       <c r="N57" s="183"/>
     </row>
     <row r="58" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="527" t="s">
+      <c r="A58" s="529" t="s">
         <v>63</v>
       </c>
-      <c r="B58" s="528"/>
-      <c r="C58" s="528"/>
-      <c r="D58" s="529"/>
+      <c r="B58" s="530"/>
+      <c r="C58" s="530"/>
+      <c r="D58" s="531"/>
       <c r="E58" s="246" t="s">
         <v>205</v>
       </c>
@@ -33063,12 +33219,12 @@
         <v>205</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="J58" s="249"/>
       <c r="K58" s="248"/>
       <c r="L58" s="3" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="M58" s="3"/>
       <c r="N58" s="49"/>
@@ -33119,7 +33275,7 @@
       <c r="A61" s="250"/>
       <c r="B61" s="251"/>
       <c r="C61" s="251"/>
-      <c r="D61" s="506"/>
+      <c r="D61" s="509"/>
       <c r="E61" s="229"/>
       <c r="F61" s="230"/>
       <c r="G61" s="231"/>
@@ -33161,7 +33317,7 @@
       <c r="A63" s="250"/>
       <c r="B63" s="251"/>
       <c r="C63" s="251"/>
-      <c r="D63" s="506"/>
+      <c r="D63" s="509"/>
       <c r="E63" s="229" t="s">
         <v>760</v>
       </c>
@@ -33183,20 +33339,20 @@
       <c r="C64" s="245"/>
       <c r="D64" s="421"/>
       <c r="E64" s="246" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="F64" s="247"/>
       <c r="G64" s="248"/>
       <c r="H64" s="4" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="J64" s="249"/>
       <c r="K64" s="248"/>
       <c r="L64" s="3" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="M64" s="3"/>
       <c r="N64" s="31"/>
@@ -33205,7 +33361,7 @@
       <c r="A65" s="250"/>
       <c r="B65" s="251"/>
       <c r="C65" s="251"/>
-      <c r="D65" s="506"/>
+      <c r="D65" s="509"/>
       <c r="E65" s="229"/>
       <c r="F65" s="230"/>
       <c r="G65" s="231"/>
@@ -33224,10 +33380,10 @@
       <c r="B66" s="245"/>
       <c r="C66" s="245"/>
       <c r="D66" s="421"/>
-      <c r="E66" s="510" t="s">
+      <c r="E66" s="515" t="s">
         <v>728</v>
       </c>
-      <c r="F66" s="511"/>
+      <c r="F66" s="516"/>
       <c r="G66" s="298"/>
       <c r="H66" s="13" t="s">
         <v>729</v>
@@ -33244,10 +33400,10 @@
       <c r="N66" s="104"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="507"/>
-      <c r="B67" s="508"/>
-      <c r="C67" s="508"/>
-      <c r="D67" s="509"/>
+      <c r="A67" s="506"/>
+      <c r="B67" s="507"/>
+      <c r="C67" s="507"/>
+      <c r="D67" s="508"/>
       <c r="E67" s="365"/>
       <c r="F67" s="366"/>
       <c r="G67" s="367"/>
@@ -33267,12 +33423,12 @@
       <c r="A68" s="250"/>
       <c r="B68" s="251"/>
       <c r="C68" s="251"/>
-      <c r="D68" s="506"/>
+      <c r="D68" s="509"/>
       <c r="E68" s="229"/>
       <c r="F68" s="230"/>
       <c r="G68" s="231"/>
       <c r="H68" s="10" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="I68" s="10"/>
       <c r="J68" s="472"/>
@@ -33303,19 +33459,19 @@
       </c>
       <c r="N69" s="78"/>
     </row>
-    <row r="70" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="250"/>
       <c r="B70" s="251"/>
       <c r="C70" s="251"/>
-      <c r="D70" s="506"/>
+      <c r="D70" s="509"/>
       <c r="E70" s="229"/>
       <c r="F70" s="230"/>
       <c r="G70" s="231"/>
       <c r="H70" s="86" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="J70" s="299"/>
       <c r="K70" s="300"/>
@@ -33355,7 +33511,7 @@
       <c r="A72" s="250"/>
       <c r="B72" s="251"/>
       <c r="C72" s="251"/>
-      <c r="D72" s="506"/>
+      <c r="D72" s="509"/>
       <c r="E72" s="229"/>
       <c r="F72" s="230"/>
       <c r="G72" s="231"/>
@@ -33391,7 +33547,7 @@
       <c r="A74" s="250"/>
       <c r="B74" s="251"/>
       <c r="C74" s="251"/>
-      <c r="D74" s="506"/>
+      <c r="D74" s="509"/>
       <c r="E74" s="229" t="s">
         <v>760</v>
       </c>
@@ -33427,7 +33583,7 @@
       <c r="A76" s="250"/>
       <c r="B76" s="251"/>
       <c r="C76" s="251"/>
-      <c r="D76" s="506"/>
+      <c r="D76" s="509"/>
       <c r="E76" s="439" t="s">
         <v>3</v>
       </c>
@@ -33483,7 +33639,7 @@
       <c r="A78" s="250"/>
       <c r="B78" s="251"/>
       <c r="C78" s="251"/>
-      <c r="D78" s="506"/>
+      <c r="D78" s="509"/>
       <c r="E78" s="229"/>
       <c r="F78" s="230"/>
       <c r="G78" s="231"/>
@@ -33553,7 +33709,7 @@
       <c r="A81" s="250"/>
       <c r="B81" s="251"/>
       <c r="C81" s="251"/>
-      <c r="D81" s="506"/>
+      <c r="D81" s="509"/>
       <c r="E81" s="229"/>
       <c r="F81" s="230"/>
       <c r="G81" s="231"/>
@@ -33601,7 +33757,7 @@
       <c r="A83" s="250"/>
       <c r="B83" s="251"/>
       <c r="C83" s="251"/>
-      <c r="D83" s="506"/>
+      <c r="D83" s="509"/>
       <c r="E83" s="229"/>
       <c r="F83" s="230"/>
       <c r="G83" s="231"/>
@@ -33620,14 +33776,24 @@
       <c r="B84" s="245"/>
       <c r="C84" s="245"/>
       <c r="D84" s="421"/>
-      <c r="E84" s="246"/>
+      <c r="E84" s="246" t="s">
+        <v>197</v>
+      </c>
       <c r="F84" s="247"/>
       <c r="G84" s="248"/>
-      <c r="H84" s="12"/>
-      <c r="I84" s="12"/>
-      <c r="J84" s="249"/>
+      <c r="H84" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I84" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="J84" s="249" t="s">
+        <v>32</v>
+      </c>
       <c r="K84" s="248"/>
-      <c r="L84" s="12"/>
+      <c r="L84" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="M84" s="12"/>
       <c r="N84" s="14"/>
     </row>
@@ -33635,15 +33801,21 @@
       <c r="A85" s="250"/>
       <c r="B85" s="251"/>
       <c r="C85" s="251"/>
-      <c r="D85" s="506"/>
-      <c r="E85" s="521"/>
-      <c r="F85" s="522"/>
+      <c r="D85" s="509"/>
+      <c r="E85" s="519"/>
+      <c r="F85" s="520"/>
       <c r="G85" s="473"/>
-      <c r="H85" s="68"/>
+      <c r="H85" s="68" t="s">
+        <v>32</v>
+      </c>
       <c r="I85" s="68"/>
-      <c r="J85" s="350"/>
+      <c r="J85" s="350" t="s">
+        <v>32</v>
+      </c>
       <c r="K85" s="231"/>
-      <c r="L85" s="68"/>
+      <c r="L85" s="68" t="s">
+        <v>32</v>
+      </c>
       <c r="M85" s="69"/>
       <c r="N85" s="70"/>
     </row>
@@ -33665,8 +33837,8 @@
       <c r="I86" s="99" t="s">
         <v>250</v>
       </c>
-      <c r="J86" s="519"/>
-      <c r="K86" s="520"/>
+      <c r="J86" s="521"/>
+      <c r="K86" s="522"/>
       <c r="L86" s="99" t="s">
         <v>250</v>
       </c>
@@ -33679,7 +33851,7 @@
       <c r="A87" s="250"/>
       <c r="B87" s="251"/>
       <c r="C87" s="251"/>
-      <c r="D87" s="506"/>
+      <c r="D87" s="509"/>
       <c r="E87" s="229"/>
       <c r="F87" s="230"/>
       <c r="G87" s="231"/>
@@ -33721,11 +33893,11 @@
       <c r="A89" s="250"/>
       <c r="B89" s="251"/>
       <c r="C89" s="251"/>
-      <c r="D89" s="506"/>
-      <c r="E89" s="512" t="s">
+      <c r="D89" s="509"/>
+      <c r="E89" s="513" t="s">
         <v>87</v>
       </c>
-      <c r="F89" s="513"/>
+      <c r="F89" s="514"/>
       <c r="G89" s="300"/>
       <c r="H89" s="6" t="s">
         <v>87</v>
@@ -33774,10 +33946,10 @@
       <c r="B91" s="245"/>
       <c r="C91" s="245"/>
       <c r="D91" s="421"/>
-      <c r="E91" s="510" t="s">
+      <c r="E91" s="515" t="s">
         <v>91</v>
       </c>
-      <c r="F91" s="511"/>
+      <c r="F91" s="516"/>
       <c r="G91" s="298"/>
       <c r="H91" s="13" t="s">
         <v>91</v>
@@ -33794,10 +33966,10 @@
       <c r="N91" s="104"/>
     </row>
     <row r="92" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="507"/>
-      <c r="B92" s="508"/>
-      <c r="C92" s="508"/>
-      <c r="D92" s="509"/>
+      <c r="A92" s="506"/>
+      <c r="B92" s="507"/>
+      <c r="C92" s="507"/>
+      <c r="D92" s="508"/>
       <c r="E92" s="365" t="s">
         <v>92</v>
       </c>
@@ -33818,15 +33990,15 @@
       <c r="N92" s="35"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A93" s="507"/>
-      <c r="B93" s="508"/>
-      <c r="C93" s="508"/>
-      <c r="D93" s="509"/>
-      <c r="E93" s="514" t="s">
+      <c r="A93" s="506"/>
+      <c r="B93" s="507"/>
+      <c r="C93" s="507"/>
+      <c r="D93" s="508"/>
+      <c r="E93" s="510" t="s">
         <v>93</v>
       </c>
-      <c r="F93" s="515"/>
-      <c r="G93" s="516"/>
+      <c r="F93" s="511"/>
+      <c r="G93" s="512"/>
       <c r="H93" s="34"/>
       <c r="I93" s="34" t="s">
         <v>93</v>
@@ -33843,9 +34015,9 @@
       <c r="A94" s="250"/>
       <c r="B94" s="251"/>
       <c r="C94" s="251"/>
-      <c r="D94" s="506"/>
-      <c r="E94" s="512"/>
-      <c r="F94" s="513"/>
+      <c r="D94" s="509"/>
+      <c r="E94" s="513"/>
+      <c r="F94" s="514"/>
       <c r="G94" s="300"/>
       <c r="H94" s="69"/>
       <c r="I94" s="68" t="s">
@@ -33874,7 +34046,7 @@
       <c r="J95" s="249"/>
       <c r="K95" s="248"/>
       <c r="L95" s="28" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="M95" s="28"/>
       <c r="N95" s="29"/>
@@ -33883,7 +34055,7 @@
       <c r="A96" s="250"/>
       <c r="B96" s="251"/>
       <c r="C96" s="251"/>
-      <c r="D96" s="506"/>
+      <c r="D96" s="509"/>
       <c r="E96" s="229"/>
       <c r="F96" s="230"/>
       <c r="G96" s="231"/>
@@ -33891,7 +34063,7 @@
         <v>18</v>
       </c>
       <c r="I96" s="9" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="J96" s="350"/>
       <c r="K96" s="231"/>
@@ -33981,7 +34153,7 @@
       <c r="C100" s="245"/>
       <c r="D100" s="421"/>
       <c r="E100" s="246" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="F100" s="247"/>
       <c r="G100" s="248"/>
@@ -33989,15 +34161,17 @@
       <c r="I100" s="48"/>
       <c r="J100" s="249"/>
       <c r="K100" s="248"/>
-      <c r="L100" s="3"/>
+      <c r="L100" s="3" t="s">
+        <v>794</v>
+      </c>
       <c r="M100" s="3"/>
       <c r="N100" s="59"/>
     </row>
     <row r="101" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="507"/>
-      <c r="B101" s="508"/>
-      <c r="C101" s="508"/>
-      <c r="D101" s="509"/>
+      <c r="A101" s="506"/>
+      <c r="B101" s="507"/>
+      <c r="C101" s="507"/>
+      <c r="D101" s="508"/>
       <c r="E101" s="365" t="s">
         <v>760</v>
       </c>
@@ -34019,14 +34193,14 @@
       <c r="A102" s="250"/>
       <c r="B102" s="251"/>
       <c r="C102" s="251"/>
-      <c r="D102" s="506"/>
+      <c r="D102" s="509"/>
       <c r="E102" s="229" t="s">
         <v>140</v>
       </c>
       <c r="F102" s="230"/>
       <c r="G102" s="231"/>
       <c r="H102" s="6" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="I102" s="9" t="s">
         <v>74</v>
@@ -34053,10 +34227,10 @@
       <c r="I103" s="113"/>
       <c r="J103" s="237"/>
       <c r="K103" s="237"/>
-      <c r="L103" s="3"/>
-      <c r="M103" s="3" t="s">
+      <c r="L103" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="M103" s="3"/>
       <c r="N103" s="8"/>
     </row>
     <row r="104" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -34075,10 +34249,10 @@
       </c>
       <c r="J104" s="232"/>
       <c r="K104" s="232"/>
-      <c r="L104" s="9"/>
-      <c r="M104" s="9" t="s">
+      <c r="L104" s="9" t="s">
         <v>24</v>
       </c>
+      <c r="M104" s="9"/>
       <c r="N104" s="16"/>
     </row>
     <row r="106" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -37124,6 +37298,2855 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEC36C20-B6DB-4E14-B203-48F45C7D5D47}">
+  <dimension ref="A1:N110"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="19.77734375" customWidth="1"/>
+    <col min="9" max="9" width="19.5546875" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" customWidth="1"/>
+    <col min="12" max="12" width="23.109375" customWidth="1"/>
+    <col min="13" max="13" width="19" customWidth="1"/>
+    <col min="14" max="14" width="15.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="553" t="s">
+        <v>795</v>
+      </c>
+      <c r="B1" s="554"/>
+      <c r="C1" s="554"/>
+      <c r="D1" s="555"/>
+      <c r="E1" s="556" t="s">
+        <v>796</v>
+      </c>
+      <c r="F1" s="557"/>
+      <c r="G1" s="558"/>
+      <c r="H1" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="J1" s="570" t="s">
+        <v>799</v>
+      </c>
+      <c r="K1" s="558"/>
+      <c r="L1" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="561" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="562"/>
+      <c r="C2" s="562"/>
+      <c r="D2" s="563"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="247"/>
+      <c r="G2" s="248"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="249"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="5"/>
+    </row>
+    <row r="3" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="227"/>
+      <c r="B3" s="228"/>
+      <c r="C3" s="228"/>
+      <c r="D3" s="386"/>
+      <c r="E3" s="229" t="s">
+        <v>804</v>
+      </c>
+      <c r="F3" s="230"/>
+      <c r="G3" s="231"/>
+      <c r="H3" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="J3" s="551"/>
+      <c r="K3" s="552"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9" t="s">
+        <v>756</v>
+      </c>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="244" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="245"/>
+      <c r="C4" s="245"/>
+      <c r="D4" s="421"/>
+      <c r="E4" s="246" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="247"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="249" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="248"/>
+      <c r="L4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="3"/>
+      <c r="N4" s="8"/>
+    </row>
+    <row r="5" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="227"/>
+      <c r="B5" s="228"/>
+      <c r="C5" s="228"/>
+      <c r="D5" s="386"/>
+      <c r="E5" s="229" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="230"/>
+      <c r="G5" s="231"/>
+      <c r="H5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="350" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="231"/>
+      <c r="L5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="9"/>
+      <c r="N5" s="16"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="244" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="245"/>
+      <c r="C6" s="245"/>
+      <c r="D6" s="421"/>
+      <c r="E6" s="246"/>
+      <c r="F6" s="247"/>
+      <c r="G6" s="248"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="249"/>
+      <c r="K6" s="248"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="31"/>
+    </row>
+    <row r="7" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="227"/>
+      <c r="B7" s="228"/>
+      <c r="C7" s="228"/>
+      <c r="D7" s="386"/>
+      <c r="E7" s="229" t="s">
+        <v>805</v>
+      </c>
+      <c r="F7" s="230"/>
+      <c r="G7" s="231"/>
+      <c r="H7" s="9" t="s">
+        <v>805</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>805</v>
+      </c>
+      <c r="J7" s="350" t="s">
+        <v>806</v>
+      </c>
+      <c r="K7" s="231"/>
+      <c r="L7" s="9" t="s">
+        <v>807</v>
+      </c>
+      <c r="M7" s="9"/>
+      <c r="N7" s="16"/>
+    </row>
+    <row r="8" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="262" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="263"/>
+      <c r="C8" s="263"/>
+      <c r="D8" s="264"/>
+      <c r="E8" s="361" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="362"/>
+      <c r="G8" s="269"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="268" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="269"/>
+      <c r="L8" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" s="122"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="244" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="245"/>
+      <c r="C9" s="245"/>
+      <c r="D9" s="421"/>
+      <c r="E9" s="535"/>
+      <c r="F9" s="536"/>
+      <c r="G9" s="537"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="249"/>
+      <c r="K9" s="248"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="8"/>
+    </row>
+    <row r="10" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="363"/>
+      <c r="B10" s="364"/>
+      <c r="C10" s="364"/>
+      <c r="D10" s="544"/>
+      <c r="E10" s="548" t="s">
+        <v>831</v>
+      </c>
+      <c r="F10" s="549"/>
+      <c r="G10" s="550"/>
+      <c r="H10" s="126" t="s">
+        <v>189</v>
+      </c>
+      <c r="I10" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="J10" s="368" t="s">
+        <v>189</v>
+      </c>
+      <c r="K10" s="367"/>
+      <c r="L10" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="M10" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="N10" s="39"/>
+    </row>
+    <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="227"/>
+      <c r="B11" s="228"/>
+      <c r="C11" s="228"/>
+      <c r="D11" s="386"/>
+      <c r="E11" s="527" t="s">
+        <v>712</v>
+      </c>
+      <c r="F11" s="528"/>
+      <c r="G11" s="494"/>
+      <c r="H11" s="76" t="s">
+        <v>712</v>
+      </c>
+      <c r="I11" s="76" t="s">
+        <v>712</v>
+      </c>
+      <c r="J11" s="493" t="s">
+        <v>712</v>
+      </c>
+      <c r="K11" s="494"/>
+      <c r="L11" s="76" t="s">
+        <v>712</v>
+      </c>
+      <c r="M11" s="188"/>
+      <c r="N11" s="189"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="323" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="324"/>
+      <c r="C12" s="324"/>
+      <c r="D12" s="371"/>
+      <c r="E12" s="535"/>
+      <c r="F12" s="536"/>
+      <c r="G12" s="537"/>
+      <c r="H12" s="190"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="249"/>
+      <c r="K12" s="248"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="191"/>
+    </row>
+    <row r="13" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="346"/>
+      <c r="B13" s="347"/>
+      <c r="C13" s="347"/>
+      <c r="D13" s="351"/>
+      <c r="E13" s="545" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="546"/>
+      <c r="G13" s="547"/>
+      <c r="H13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="350" t="s">
+        <v>13</v>
+      </c>
+      <c r="K13" s="231"/>
+      <c r="L13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="M13" s="9"/>
+      <c r="N13" s="26"/>
+    </row>
+    <row r="14" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="262" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="263"/>
+      <c r="C14" s="263"/>
+      <c r="D14" s="264"/>
+      <c r="E14" s="361" t="s">
+        <v>160</v>
+      </c>
+      <c r="F14" s="362"/>
+      <c r="G14" s="269"/>
+      <c r="H14" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="19"/>
+      <c r="J14" s="268" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="269"/>
+      <c r="L14" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="27"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="244" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="245"/>
+      <c r="C15" s="245"/>
+      <c r="D15" s="421"/>
+      <c r="E15" s="246"/>
+      <c r="F15" s="247"/>
+      <c r="G15" s="248"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="249"/>
+      <c r="K15" s="248"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="8"/>
+    </row>
+    <row r="16" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="227"/>
+      <c r="B16" s="228"/>
+      <c r="C16" s="228"/>
+      <c r="D16" s="386"/>
+      <c r="E16" s="229" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="230"/>
+      <c r="G16" s="231"/>
+      <c r="H16" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="91" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" s="295" t="s">
+        <v>47</v>
+      </c>
+      <c r="K16" s="296"/>
+      <c r="L16" s="91" t="s">
+        <v>47</v>
+      </c>
+      <c r="M16" s="91" t="s">
+        <v>47</v>
+      </c>
+      <c r="N16" s="93" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="244" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="245"/>
+      <c r="C17" s="245"/>
+      <c r="D17" s="421"/>
+      <c r="E17" s="246"/>
+      <c r="F17" s="247"/>
+      <c r="G17" s="248"/>
+      <c r="H17" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="I17" s="12"/>
+      <c r="J17" s="249"/>
+      <c r="K17" s="248"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="14"/>
+    </row>
+    <row r="18" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" s="506"/>
+      <c r="B18" s="507"/>
+      <c r="C18" s="507"/>
+      <c r="D18" s="508"/>
+      <c r="E18" s="365" t="s">
+        <v>830</v>
+      </c>
+      <c r="F18" s="366"/>
+      <c r="G18" s="367"/>
+      <c r="H18" s="32" t="s">
+        <v>336</v>
+      </c>
+      <c r="I18" s="32" t="s">
+        <v>808</v>
+      </c>
+      <c r="J18" s="368" t="s">
+        <v>808</v>
+      </c>
+      <c r="K18" s="367"/>
+      <c r="L18" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="M18" s="32"/>
+      <c r="N18" s="33" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="506"/>
+      <c r="B19" s="507"/>
+      <c r="C19" s="507"/>
+      <c r="D19" s="508"/>
+      <c r="E19" s="365"/>
+      <c r="F19" s="366"/>
+      <c r="G19" s="367"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="368"/>
+      <c r="K19" s="367"/>
+      <c r="L19" s="105"/>
+      <c r="M19" s="32"/>
+      <c r="N19" s="35"/>
+    </row>
+    <row r="20" spans="1:14" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="250"/>
+      <c r="B20" s="251"/>
+      <c r="C20" s="251"/>
+      <c r="D20" s="509"/>
+      <c r="E20" s="229"/>
+      <c r="F20" s="230"/>
+      <c r="G20" s="231"/>
+      <c r="H20" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>809</v>
+      </c>
+      <c r="J20" s="350" t="s">
+        <v>826</v>
+      </c>
+      <c r="K20" s="231"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="N20" s="11"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="244" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="245"/>
+      <c r="C21" s="245"/>
+      <c r="D21" s="421"/>
+      <c r="E21" s="246" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="247"/>
+      <c r="G21" s="248"/>
+      <c r="H21" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J21" s="297" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" s="298"/>
+      <c r="L21" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M21" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="N21" s="37" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="369"/>
+      <c r="B22" s="370"/>
+      <c r="C22" s="370"/>
+      <c r="D22" s="569"/>
+      <c r="E22" s="229" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" s="230"/>
+      <c r="G22" s="231"/>
+      <c r="H22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" s="350" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" s="231"/>
+      <c r="L22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22" s="38" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="272" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="273"/>
+      <c r="C23" s="273"/>
+      <c r="D23" s="301"/>
+      <c r="E23" s="247" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="247"/>
+      <c r="G23" s="248"/>
+      <c r="H23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J23" s="249" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23" s="248"/>
+      <c r="L23" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="M23" s="3"/>
+      <c r="N23" s="8"/>
+    </row>
+    <row r="24" spans="1:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="566"/>
+      <c r="B24" s="567"/>
+      <c r="C24" s="567"/>
+      <c r="D24" s="568"/>
+      <c r="E24" s="366" t="s">
+        <v>168</v>
+      </c>
+      <c r="F24" s="366"/>
+      <c r="G24" s="367"/>
+      <c r="H24" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="I24" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J24" s="368" t="s">
+        <v>168</v>
+      </c>
+      <c r="K24" s="367"/>
+      <c r="L24" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="M24" s="32"/>
+      <c r="N24" s="39"/>
+    </row>
+    <row r="25" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="379"/>
+      <c r="B25" s="380"/>
+      <c r="C25" s="380"/>
+      <c r="D25" s="565"/>
+      <c r="E25" s="454" t="s">
+        <v>127</v>
+      </c>
+      <c r="F25" s="454"/>
+      <c r="G25" s="425"/>
+      <c r="H25" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="J25" s="424" t="s">
+        <v>127</v>
+      </c>
+      <c r="K25" s="425"/>
+      <c r="L25" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="M25" s="6"/>
+      <c r="N25" s="38"/>
+    </row>
+    <row r="26" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="346" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="347"/>
+      <c r="C26" s="347"/>
+      <c r="D26" s="351"/>
+      <c r="E26" s="361" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" s="362"/>
+      <c r="G26" s="269"/>
+      <c r="H26" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="I26" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="J26" s="268"/>
+      <c r="K26" s="269"/>
+      <c r="L26" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="M26" s="17"/>
+      <c r="N26" s="40"/>
+    </row>
+    <row r="27" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="262" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="263"/>
+      <c r="C27" s="263"/>
+      <c r="D27" s="264"/>
+      <c r="E27" s="361"/>
+      <c r="F27" s="362"/>
+      <c r="G27" s="269"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="J27" s="268" t="s">
+        <v>135</v>
+      </c>
+      <c r="K27" s="269"/>
+      <c r="L27" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M27" s="19"/>
+      <c r="N27" s="20"/>
+    </row>
+    <row r="28" spans="1:14" ht="28.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="262" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="263"/>
+      <c r="C28" s="263"/>
+      <c r="D28" s="264"/>
+      <c r="E28" s="541"/>
+      <c r="F28" s="542"/>
+      <c r="G28" s="543"/>
+      <c r="H28" s="186"/>
+      <c r="I28" s="101"/>
+      <c r="J28" s="268"/>
+      <c r="K28" s="269"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="185" t="s">
+        <v>585</v>
+      </c>
+      <c r="N28" s="187"/>
+    </row>
+    <row r="29" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="244" t="s">
+        <v>524</v>
+      </c>
+      <c r="B29" s="245"/>
+      <c r="C29" s="245"/>
+      <c r="D29" s="421"/>
+      <c r="E29" s="464" t="s">
+        <v>175</v>
+      </c>
+      <c r="F29" s="465"/>
+      <c r="G29" s="466"/>
+      <c r="H29" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="I29" s="62" t="s">
+        <v>189</v>
+      </c>
+      <c r="J29" s="249" t="s">
+        <v>189</v>
+      </c>
+      <c r="K29" s="248"/>
+      <c r="L29" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="M29" s="48"/>
+      <c r="N29" s="49"/>
+    </row>
+    <row r="30" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="227"/>
+      <c r="B30" s="228"/>
+      <c r="C30" s="228"/>
+      <c r="D30" s="386"/>
+      <c r="E30" s="336"/>
+      <c r="F30" s="337"/>
+      <c r="G30" s="338"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="97"/>
+      <c r="J30" s="350"/>
+      <c r="K30" s="231"/>
+      <c r="L30" s="50" t="s">
+        <v>189</v>
+      </c>
+      <c r="M30" s="50"/>
+      <c r="N30" s="52"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="323" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="324"/>
+      <c r="C31" s="324"/>
+      <c r="D31" s="371"/>
+      <c r="E31" s="538"/>
+      <c r="F31" s="539"/>
+      <c r="G31" s="540"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="249"/>
+      <c r="K31" s="248"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="56"/>
+      <c r="N31" s="57"/>
+    </row>
+    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="346"/>
+      <c r="B32" s="347"/>
+      <c r="C32" s="347"/>
+      <c r="D32" s="351"/>
+      <c r="E32" s="336"/>
+      <c r="F32" s="337"/>
+      <c r="G32" s="338"/>
+      <c r="H32" s="159"/>
+      <c r="I32" s="159"/>
+      <c r="J32" s="350"/>
+      <c r="K32" s="231"/>
+      <c r="L32" s="135"/>
+      <c r="M32" s="159"/>
+      <c r="N32" s="136"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="244" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="245"/>
+      <c r="C33" s="245"/>
+      <c r="D33" s="421"/>
+      <c r="E33" s="246"/>
+      <c r="F33" s="247"/>
+      <c r="G33" s="248"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="249"/>
+      <c r="K33" s="248"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="49"/>
+    </row>
+    <row r="34" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="227"/>
+      <c r="B34" s="228"/>
+      <c r="C34" s="228"/>
+      <c r="D34" s="386"/>
+      <c r="E34" s="527" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" s="528"/>
+      <c r="G34" s="494"/>
+      <c r="H34" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J34" s="350" t="s">
+        <v>32</v>
+      </c>
+      <c r="K34" s="231"/>
+      <c r="L34" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="N34" s="54"/>
+    </row>
+    <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="244" t="s">
+        <v>255</v>
+      </c>
+      <c r="B35" s="245"/>
+      <c r="C35" s="245"/>
+      <c r="D35" s="421"/>
+      <c r="E35" s="246" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35" s="247"/>
+      <c r="G35" s="248"/>
+      <c r="H35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="249" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" s="248"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="104"/>
+    </row>
+    <row r="36" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="250"/>
+      <c r="B36" s="251"/>
+      <c r="C36" s="251"/>
+      <c r="D36" s="509"/>
+      <c r="E36" s="229" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" s="230"/>
+      <c r="G36" s="231"/>
+      <c r="H36" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J36" s="350" t="s">
+        <v>24</v>
+      </c>
+      <c r="K36" s="231"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="38"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="244" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="245"/>
+      <c r="C37" s="245"/>
+      <c r="D37" s="421"/>
+      <c r="E37" s="515"/>
+      <c r="F37" s="516"/>
+      <c r="G37" s="298"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="249"/>
+      <c r="K37" s="248"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="138"/>
+    </row>
+    <row r="38" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="250"/>
+      <c r="B38" s="251"/>
+      <c r="C38" s="251"/>
+      <c r="D38" s="509"/>
+      <c r="E38" s="229" t="s">
+        <v>758</v>
+      </c>
+      <c r="F38" s="230"/>
+      <c r="G38" s="231"/>
+      <c r="H38" s="9" t="s">
+        <v>769</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="J38" s="350"/>
+      <c r="K38" s="231"/>
+      <c r="L38" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="M38" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="N38" s="16"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="244" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="245"/>
+      <c r="C39" s="245"/>
+      <c r="D39" s="421"/>
+      <c r="E39" s="246"/>
+      <c r="F39" s="247"/>
+      <c r="G39" s="248"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="137"/>
+      <c r="J39" s="249"/>
+      <c r="K39" s="248"/>
+      <c r="L39" s="12"/>
+      <c r="M39" s="137"/>
+      <c r="N39" s="94"/>
+    </row>
+    <row r="40" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="227"/>
+      <c r="B40" s="228"/>
+      <c r="C40" s="228"/>
+      <c r="D40" s="386"/>
+      <c r="E40" s="229" t="s">
+        <v>50</v>
+      </c>
+      <c r="F40" s="230"/>
+      <c r="G40" s="231"/>
+      <c r="H40" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="J40" s="350" t="s">
+        <v>50</v>
+      </c>
+      <c r="K40" s="231"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="16"/>
+    </row>
+    <row r="41" spans="1:14" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="244" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="245"/>
+      <c r="C41" s="245"/>
+      <c r="D41" s="421"/>
+      <c r="E41" s="535" t="s">
+        <v>829</v>
+      </c>
+      <c r="F41" s="536"/>
+      <c r="G41" s="537"/>
+      <c r="H41" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J41" s="249" t="s">
+        <v>189</v>
+      </c>
+      <c r="K41" s="248"/>
+      <c r="L41" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M41" s="12"/>
+      <c r="N41" s="14"/>
+    </row>
+    <row r="42" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="250"/>
+      <c r="B42" s="251"/>
+      <c r="C42" s="251"/>
+      <c r="D42" s="509"/>
+      <c r="E42" s="229"/>
+      <c r="F42" s="230"/>
+      <c r="G42" s="231"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J42" s="350"/>
+      <c r="K42" s="231"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="63"/>
+      <c r="N42" s="30"/>
+    </row>
+    <row r="43" spans="1:14" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="244" t="s">
+        <v>523</v>
+      </c>
+      <c r="B43" s="245"/>
+      <c r="C43" s="245"/>
+      <c r="D43" s="421"/>
+      <c r="E43" s="246" t="s">
+        <v>189</v>
+      </c>
+      <c r="F43" s="247"/>
+      <c r="G43" s="248"/>
+      <c r="H43" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J43" s="249" t="s">
+        <v>189</v>
+      </c>
+      <c r="K43" s="248"/>
+      <c r="L43" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="N43" s="31"/>
+    </row>
+    <row r="44" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="250"/>
+      <c r="B44" s="251"/>
+      <c r="C44" s="251"/>
+      <c r="D44" s="509"/>
+      <c r="E44" s="453"/>
+      <c r="F44" s="454"/>
+      <c r="G44" s="425"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="424"/>
+      <c r="K44" s="425"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="63"/>
+      <c r="N44" s="30"/>
+    </row>
+    <row r="45" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="244" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="245"/>
+      <c r="C45" s="245"/>
+      <c r="D45" s="245"/>
+      <c r="E45" s="236" t="s">
+        <v>811</v>
+      </c>
+      <c r="F45" s="237"/>
+      <c r="G45" s="237"/>
+      <c r="H45" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="J45" s="237" t="s">
+        <v>811</v>
+      </c>
+      <c r="K45" s="237"/>
+      <c r="L45" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="M45" s="3"/>
+      <c r="N45" s="64"/>
+    </row>
+    <row r="46" spans="1:14" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="506"/>
+      <c r="B46" s="507"/>
+      <c r="C46" s="507"/>
+      <c r="D46" s="507"/>
+      <c r="E46" s="220" t="s">
+        <v>819</v>
+      </c>
+      <c r="F46" s="221"/>
+      <c r="G46" s="221"/>
+      <c r="H46" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="I46" s="32"/>
+      <c r="J46" s="221"/>
+      <c r="K46" s="221"/>
+      <c r="L46" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="M46" s="32"/>
+      <c r="N46" s="33"/>
+    </row>
+    <row r="47" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="250"/>
+      <c r="B47" s="251"/>
+      <c r="C47" s="251"/>
+      <c r="D47" s="251"/>
+      <c r="E47" s="252"/>
+      <c r="F47" s="232"/>
+      <c r="G47" s="232"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="232"/>
+      <c r="K47" s="232"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="65"/>
+      <c r="N47" s="11"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48" s="244" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="245"/>
+      <c r="C48" s="245"/>
+      <c r="D48" s="421"/>
+      <c r="E48" s="281"/>
+      <c r="F48" s="282"/>
+      <c r="G48" s="283"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="284"/>
+      <c r="K48" s="283"/>
+      <c r="L48" s="12"/>
+      <c r="M48" s="66"/>
+      <c r="N48" s="67"/>
+    </row>
+    <row r="49" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="250"/>
+      <c r="B49" s="251"/>
+      <c r="C49" s="251"/>
+      <c r="D49" s="509"/>
+      <c r="E49" s="519"/>
+      <c r="F49" s="520"/>
+      <c r="G49" s="473"/>
+      <c r="H49" s="68"/>
+      <c r="I49" s="68"/>
+      <c r="J49" s="299"/>
+      <c r="K49" s="300"/>
+      <c r="L49" s="68"/>
+      <c r="M49" s="69"/>
+      <c r="N49" s="70"/>
+    </row>
+    <row r="50" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="323" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="324"/>
+      <c r="C50" s="324"/>
+      <c r="D50" s="371"/>
+      <c r="E50" s="246" t="s">
+        <v>823</v>
+      </c>
+      <c r="F50" s="247"/>
+      <c r="G50" s="248"/>
+      <c r="H50" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J50" s="249" t="s">
+        <v>86</v>
+      </c>
+      <c r="K50" s="248"/>
+      <c r="L50" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="M50" s="4"/>
+      <c r="N50" s="29"/>
+    </row>
+    <row r="51" spans="1:14" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="532"/>
+      <c r="B51" s="533"/>
+      <c r="C51" s="533"/>
+      <c r="D51" s="534"/>
+      <c r="E51" s="453"/>
+      <c r="F51" s="454"/>
+      <c r="G51" s="425"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J51" s="350" t="s">
+        <v>87</v>
+      </c>
+      <c r="K51" s="231"/>
+      <c r="L51" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="M51" s="6"/>
+      <c r="N51" s="38"/>
+    </row>
+    <row r="52" spans="1:14" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="244" t="s">
+        <v>710</v>
+      </c>
+      <c r="B52" s="245"/>
+      <c r="C52" s="245"/>
+      <c r="D52" s="245"/>
+      <c r="E52" s="236" t="s">
+        <v>813</v>
+      </c>
+      <c r="F52" s="237"/>
+      <c r="G52" s="237"/>
+      <c r="H52" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J52" s="237" t="s">
+        <v>813</v>
+      </c>
+      <c r="K52" s="237"/>
+      <c r="L52" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="M52" s="3"/>
+      <c r="N52" s="8"/>
+    </row>
+    <row r="53" spans="1:14" ht="52.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="250"/>
+      <c r="B53" s="251"/>
+      <c r="C53" s="251"/>
+      <c r="D53" s="251"/>
+      <c r="E53" s="252" t="s">
+        <v>819</v>
+      </c>
+      <c r="F53" s="232"/>
+      <c r="G53" s="232"/>
+      <c r="H53" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="J53" s="232" t="s">
+        <v>189</v>
+      </c>
+      <c r="K53" s="232"/>
+      <c r="L53" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="M53" s="9"/>
+      <c r="N53" s="16"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54" s="244" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" s="245"/>
+      <c r="C54" s="245"/>
+      <c r="D54" s="421"/>
+      <c r="E54" s="281"/>
+      <c r="F54" s="282"/>
+      <c r="G54" s="283"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="284"/>
+      <c r="K54" s="283"/>
+      <c r="L54" s="12"/>
+      <c r="M54" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="N54" s="72"/>
+    </row>
+    <row r="55" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="250"/>
+      <c r="B55" s="251"/>
+      <c r="C55" s="251"/>
+      <c r="D55" s="509"/>
+      <c r="E55" s="229" t="s">
+        <v>120</v>
+      </c>
+      <c r="F55" s="230"/>
+      <c r="G55" s="231"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="J55" s="350" t="s">
+        <v>19</v>
+      </c>
+      <c r="K55" s="231"/>
+      <c r="L55" s="9"/>
+      <c r="M55" s="9"/>
+      <c r="N55" s="73"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" s="244" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="245"/>
+      <c r="C56" s="245"/>
+      <c r="D56" s="421"/>
+      <c r="E56" s="246" t="s">
+        <v>32</v>
+      </c>
+      <c r="F56" s="247"/>
+      <c r="G56" s="248"/>
+      <c r="H56" s="181" t="s">
+        <v>32</v>
+      </c>
+      <c r="I56" s="181" t="s">
+        <v>32</v>
+      </c>
+      <c r="J56" s="249" t="s">
+        <v>32</v>
+      </c>
+      <c r="K56" s="248"/>
+      <c r="L56" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M56" s="28"/>
+      <c r="N56" s="182"/>
+    </row>
+    <row r="57" spans="1:14" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="524"/>
+      <c r="B57" s="525"/>
+      <c r="C57" s="525"/>
+      <c r="D57" s="526"/>
+      <c r="E57" s="527"/>
+      <c r="F57" s="528"/>
+      <c r="G57" s="494"/>
+      <c r="H57" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I57" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" s="493" t="s">
+        <v>18</v>
+      </c>
+      <c r="K57" s="494"/>
+      <c r="L57" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="M57" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N57" s="183"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58" s="529" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58" s="530"/>
+      <c r="C58" s="530"/>
+      <c r="D58" s="531"/>
+      <c r="E58" s="246" t="s">
+        <v>205</v>
+      </c>
+      <c r="F58" s="247"/>
+      <c r="G58" s="248"/>
+      <c r="H58" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J58" s="249" t="s">
+        <v>189</v>
+      </c>
+      <c r="K58" s="248"/>
+      <c r="L58" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M58" s="3"/>
+      <c r="N58" s="49"/>
+    </row>
+    <row r="59" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="524"/>
+      <c r="B59" s="525"/>
+      <c r="C59" s="525"/>
+      <c r="D59" s="526"/>
+      <c r="E59" s="229"/>
+      <c r="F59" s="230"/>
+      <c r="G59" s="231"/>
+      <c r="H59" s="21"/>
+      <c r="I59" s="21"/>
+      <c r="J59" s="350"/>
+      <c r="K59" s="231"/>
+      <c r="L59" s="9"/>
+      <c r="M59" s="51"/>
+      <c r="N59" s="52"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60" s="244" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" s="245"/>
+      <c r="C60" s="245"/>
+      <c r="D60" s="421"/>
+      <c r="E60" s="246" t="s">
+        <v>65</v>
+      </c>
+      <c r="F60" s="247"/>
+      <c r="G60" s="248"/>
+      <c r="H60" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="I60" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="J60" s="249" t="s">
+        <v>65</v>
+      </c>
+      <c r="K60" s="248"/>
+      <c r="L60" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="M60" s="12"/>
+      <c r="N60" s="78"/>
+    </row>
+    <row r="61" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="250"/>
+      <c r="B61" s="251"/>
+      <c r="C61" s="251"/>
+      <c r="D61" s="509"/>
+      <c r="E61" s="229"/>
+      <c r="F61" s="230"/>
+      <c r="G61" s="231"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="350"/>
+      <c r="K61" s="231"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="63"/>
+      <c r="N61" s="30"/>
+    </row>
+    <row r="62" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="244" t="s">
+        <v>66</v>
+      </c>
+      <c r="B62" s="245"/>
+      <c r="C62" s="245"/>
+      <c r="D62" s="421"/>
+      <c r="E62" s="246" t="s">
+        <v>26</v>
+      </c>
+      <c r="F62" s="247"/>
+      <c r="G62" s="248"/>
+      <c r="H62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J62" s="249" t="s">
+        <v>26</v>
+      </c>
+      <c r="K62" s="248"/>
+      <c r="L62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M62" s="3"/>
+      <c r="N62" s="31"/>
+    </row>
+    <row r="63" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="250"/>
+      <c r="B63" s="251"/>
+      <c r="C63" s="251"/>
+      <c r="D63" s="509"/>
+      <c r="E63" s="229"/>
+      <c r="F63" s="230"/>
+      <c r="G63" s="231"/>
+      <c r="H63" s="68"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="350"/>
+      <c r="K63" s="231"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="6"/>
+      <c r="N63" s="30"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="244" t="s">
+        <v>709</v>
+      </c>
+      <c r="B64" s="245"/>
+      <c r="C64" s="245"/>
+      <c r="D64" s="421"/>
+      <c r="E64" s="246" t="s">
+        <v>784</v>
+      </c>
+      <c r="F64" s="247"/>
+      <c r="G64" s="248"/>
+      <c r="H64" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J64" s="249" t="s">
+        <v>189</v>
+      </c>
+      <c r="K64" s="248"/>
+      <c r="L64" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M64" s="3"/>
+      <c r="N64" s="31"/>
+    </row>
+    <row r="65" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="250"/>
+      <c r="B65" s="251"/>
+      <c r="C65" s="251"/>
+      <c r="D65" s="509"/>
+      <c r="E65" s="229"/>
+      <c r="F65" s="230"/>
+      <c r="G65" s="231"/>
+      <c r="H65" s="10"/>
+      <c r="I65" s="9"/>
+      <c r="J65" s="350"/>
+      <c r="K65" s="231"/>
+      <c r="L65" s="9"/>
+      <c r="M65" s="9"/>
+      <c r="N65" s="11"/>
+    </row>
+    <row r="66" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="244" t="s">
+        <v>67</v>
+      </c>
+      <c r="B66" s="245"/>
+      <c r="C66" s="245"/>
+      <c r="D66" s="421"/>
+      <c r="E66" s="515" t="s">
+        <v>728</v>
+      </c>
+      <c r="F66" s="516"/>
+      <c r="G66" s="298"/>
+      <c r="H66" s="13" t="s">
+        <v>729</v>
+      </c>
+      <c r="I66" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J66" s="474" t="s">
+        <v>27</v>
+      </c>
+      <c r="K66" s="475"/>
+      <c r="L66" s="13" t="s">
+        <v>729</v>
+      </c>
+      <c r="M66" s="13"/>
+      <c r="N66" s="104"/>
+    </row>
+    <row r="67" spans="1:14" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="506"/>
+      <c r="B67" s="507"/>
+      <c r="C67" s="507"/>
+      <c r="D67" s="508"/>
+      <c r="E67" s="365"/>
+      <c r="F67" s="366"/>
+      <c r="G67" s="367"/>
+      <c r="H67" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="I67" s="32" t="s">
+        <v>815</v>
+      </c>
+      <c r="J67" s="368" t="s">
+        <v>815</v>
+      </c>
+      <c r="K67" s="367"/>
+      <c r="L67" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="M67" s="32"/>
+      <c r="N67" s="33"/>
+    </row>
+    <row r="68" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="250"/>
+      <c r="B68" s="251"/>
+      <c r="C68" s="251"/>
+      <c r="D68" s="509"/>
+      <c r="E68" s="229"/>
+      <c r="F68" s="230"/>
+      <c r="G68" s="231"/>
+      <c r="H68" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="I68" s="10"/>
+      <c r="J68" s="472"/>
+      <c r="K68" s="473"/>
+      <c r="L68" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="M68" s="10"/>
+      <c r="N68" s="81"/>
+    </row>
+    <row r="69" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A69" s="244" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69" s="245"/>
+      <c r="C69" s="245"/>
+      <c r="D69" s="421"/>
+      <c r="E69" s="246"/>
+      <c r="F69" s="247"/>
+      <c r="G69" s="248"/>
+      <c r="H69" s="12"/>
+      <c r="I69" s="137"/>
+      <c r="J69" s="249"/>
+      <c r="K69" s="248"/>
+      <c r="L69" s="56"/>
+      <c r="M69" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="N69" s="78"/>
+    </row>
+    <row r="70" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="275"/>
+      <c r="B70" s="276"/>
+      <c r="C70" s="276"/>
+      <c r="D70" s="564"/>
+      <c r="E70" s="453"/>
+      <c r="F70" s="454"/>
+      <c r="G70" s="425"/>
+      <c r="H70" s="86" t="s">
+        <v>816</v>
+      </c>
+      <c r="I70" s="6"/>
+      <c r="J70" s="430" t="s">
+        <v>807</v>
+      </c>
+      <c r="K70" s="431"/>
+      <c r="L70" s="6"/>
+      <c r="M70" s="87"/>
+      <c r="N70" s="70"/>
+    </row>
+    <row r="71" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A71" s="244" t="s">
+        <v>803</v>
+      </c>
+      <c r="B71" s="245"/>
+      <c r="C71" s="245"/>
+      <c r="D71" s="245"/>
+      <c r="E71" s="246" t="s">
+        <v>692</v>
+      </c>
+      <c r="F71" s="247"/>
+      <c r="G71" s="248"/>
+      <c r="H71" s="79" t="s">
+        <v>827</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="J71" s="297" t="s">
+        <v>828</v>
+      </c>
+      <c r="K71" s="298"/>
+      <c r="L71" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M71" s="28"/>
+      <c r="N71" s="88"/>
+    </row>
+    <row r="72" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="250"/>
+      <c r="B72" s="251"/>
+      <c r="C72" s="251"/>
+      <c r="D72" s="251"/>
+      <c r="E72" s="229"/>
+      <c r="F72" s="230"/>
+      <c r="G72" s="231"/>
+      <c r="H72" s="80"/>
+      <c r="I72" s="9"/>
+      <c r="J72" s="299"/>
+      <c r="K72" s="300"/>
+      <c r="L72" s="9"/>
+      <c r="M72" s="89"/>
+      <c r="N72" s="90"/>
+    </row>
+    <row r="73" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A73" s="289" t="s">
+        <v>708</v>
+      </c>
+      <c r="B73" s="290"/>
+      <c r="C73" s="290"/>
+      <c r="D73" s="388"/>
+      <c r="E73" s="281" t="s">
+        <v>76</v>
+      </c>
+      <c r="F73" s="282"/>
+      <c r="G73" s="283"/>
+      <c r="H73" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="I73" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="J73" s="284" t="s">
+        <v>76</v>
+      </c>
+      <c r="K73" s="283"/>
+      <c r="L73" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="M73" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="N73" s="67"/>
+    </row>
+    <row r="74" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="250"/>
+      <c r="B74" s="251"/>
+      <c r="C74" s="251"/>
+      <c r="D74" s="509"/>
+      <c r="E74" s="229"/>
+      <c r="F74" s="230"/>
+      <c r="G74" s="231"/>
+      <c r="H74" s="80"/>
+      <c r="I74" s="9"/>
+      <c r="J74" s="299"/>
+      <c r="K74" s="300"/>
+      <c r="L74" s="9"/>
+      <c r="M74" s="89"/>
+      <c r="N74" s="90"/>
+    </row>
+    <row r="75" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A75" s="244" t="s">
+        <v>70</v>
+      </c>
+      <c r="B75" s="245"/>
+      <c r="C75" s="245"/>
+      <c r="D75" s="421"/>
+      <c r="E75" s="246"/>
+      <c r="F75" s="247"/>
+      <c r="G75" s="248"/>
+      <c r="H75" s="56"/>
+      <c r="I75" s="12"/>
+      <c r="J75" s="249"/>
+      <c r="K75" s="248"/>
+      <c r="L75" s="12"/>
+      <c r="M75" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="N75" s="67"/>
+    </row>
+    <row r="76" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="250"/>
+      <c r="B76" s="251"/>
+      <c r="C76" s="251"/>
+      <c r="D76" s="509"/>
+      <c r="E76" s="229"/>
+      <c r="F76" s="230"/>
+      <c r="G76" s="231"/>
+      <c r="H76" s="86"/>
+      <c r="I76" s="6"/>
+      <c r="J76" s="299"/>
+      <c r="K76" s="300"/>
+      <c r="L76" s="87"/>
+      <c r="M76" s="87"/>
+      <c r="N76" s="70"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" s="244" t="s">
+        <v>72</v>
+      </c>
+      <c r="B77" s="245"/>
+      <c r="C77" s="245"/>
+      <c r="D77" s="421"/>
+      <c r="E77" s="246"/>
+      <c r="F77" s="247"/>
+      <c r="G77" s="248"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="249"/>
+      <c r="K77" s="248"/>
+      <c r="L77" s="3"/>
+      <c r="M77" s="3"/>
+      <c r="N77" s="8"/>
+    </row>
+    <row r="78" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="250"/>
+      <c r="B78" s="251"/>
+      <c r="C78" s="251"/>
+      <c r="D78" s="509"/>
+      <c r="E78" s="229"/>
+      <c r="F78" s="230"/>
+      <c r="G78" s="231"/>
+      <c r="H78" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="J78" s="493"/>
+      <c r="K78" s="494"/>
+      <c r="L78" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="M78" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="N78" s="16"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A79" s="244" t="s">
+        <v>75</v>
+      </c>
+      <c r="B79" s="245"/>
+      <c r="C79" s="245"/>
+      <c r="D79" s="421"/>
+      <c r="E79" s="412" t="s">
+        <v>47</v>
+      </c>
+      <c r="F79" s="413"/>
+      <c r="G79" s="414"/>
+      <c r="H79" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="I79" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="J79" s="523" t="s">
+        <v>47</v>
+      </c>
+      <c r="K79" s="414"/>
+      <c r="L79" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="M79" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="N79" s="176" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="250"/>
+      <c r="B80" s="251"/>
+      <c r="C80" s="251"/>
+      <c r="D80" s="509"/>
+      <c r="E80" s="229"/>
+      <c r="F80" s="230"/>
+      <c r="G80" s="231"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6"/>
+      <c r="J80" s="350"/>
+      <c r="K80" s="231"/>
+      <c r="L80" s="6"/>
+      <c r="M80" s="6"/>
+      <c r="N80" s="38"/>
+    </row>
+    <row r="81" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="262" t="s">
+        <v>77</v>
+      </c>
+      <c r="B81" s="263"/>
+      <c r="C81" s="263"/>
+      <c r="D81" s="264"/>
+      <c r="E81" s="361" t="s">
+        <v>39</v>
+      </c>
+      <c r="F81" s="362"/>
+      <c r="G81" s="269"/>
+      <c r="H81" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="I81" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="J81" s="268"/>
+      <c r="K81" s="269"/>
+      <c r="L81" s="44"/>
+      <c r="M81" s="44"/>
+      <c r="N81" s="95"/>
+    </row>
+    <row r="82" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A82" s="244" t="s">
+        <v>78</v>
+      </c>
+      <c r="B82" s="245"/>
+      <c r="C82" s="245"/>
+      <c r="D82" s="421"/>
+      <c r="E82" s="246" t="s">
+        <v>79</v>
+      </c>
+      <c r="F82" s="247"/>
+      <c r="G82" s="248"/>
+      <c r="H82" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J82" s="249" t="s">
+        <v>79</v>
+      </c>
+      <c r="K82" s="248"/>
+      <c r="L82" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="M82" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="N82" s="31"/>
+    </row>
+    <row r="83" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="250"/>
+      <c r="B83" s="251"/>
+      <c r="C83" s="251"/>
+      <c r="D83" s="509"/>
+      <c r="E83" s="229"/>
+      <c r="F83" s="230"/>
+      <c r="G83" s="231"/>
+      <c r="H83" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="J83" s="350"/>
+      <c r="K83" s="231"/>
+      <c r="L83" s="9"/>
+      <c r="M83" s="9"/>
+      <c r="N83" s="11"/>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A84" s="244" t="s">
+        <v>80</v>
+      </c>
+      <c r="B84" s="245"/>
+      <c r="C84" s="245"/>
+      <c r="D84" s="421"/>
+      <c r="E84" s="412" t="s">
+        <v>47</v>
+      </c>
+      <c r="F84" s="413"/>
+      <c r="G84" s="414"/>
+      <c r="H84" s="196" t="s">
+        <v>47</v>
+      </c>
+      <c r="I84" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="J84" s="523" t="s">
+        <v>47</v>
+      </c>
+      <c r="K84" s="414"/>
+      <c r="L84" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="M84" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="N84" s="85" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="250"/>
+      <c r="B85" s="251"/>
+      <c r="C85" s="251"/>
+      <c r="D85" s="509"/>
+      <c r="E85" s="229"/>
+      <c r="F85" s="230"/>
+      <c r="G85" s="231"/>
+      <c r="H85" s="9"/>
+      <c r="I85" s="97"/>
+      <c r="J85" s="350"/>
+      <c r="K85" s="231"/>
+      <c r="L85" s="9"/>
+      <c r="M85" s="9"/>
+      <c r="N85" s="98"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A86" s="244" t="s">
+        <v>82</v>
+      </c>
+      <c r="B86" s="245"/>
+      <c r="C86" s="245"/>
+      <c r="D86" s="421"/>
+      <c r="E86" s="246"/>
+      <c r="F86" s="247"/>
+      <c r="G86" s="248"/>
+      <c r="H86" s="12"/>
+      <c r="I86" s="12"/>
+      <c r="J86" s="249"/>
+      <c r="K86" s="248"/>
+      <c r="L86" s="12"/>
+      <c r="M86" s="12"/>
+      <c r="N86" s="14"/>
+    </row>
+    <row r="87" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="250"/>
+      <c r="B87" s="251"/>
+      <c r="C87" s="251"/>
+      <c r="D87" s="509"/>
+      <c r="E87" s="519"/>
+      <c r="F87" s="520"/>
+      <c r="G87" s="473"/>
+      <c r="H87" s="68"/>
+      <c r="I87" s="68"/>
+      <c r="J87" s="350"/>
+      <c r="K87" s="231"/>
+      <c r="L87" s="68"/>
+      <c r="M87" s="69"/>
+      <c r="N87" s="70"/>
+    </row>
+    <row r="88" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A88" s="244" t="s">
+        <v>83</v>
+      </c>
+      <c r="B88" s="245"/>
+      <c r="C88" s="245"/>
+      <c r="D88" s="421"/>
+      <c r="E88" s="246" t="s">
+        <v>49</v>
+      </c>
+      <c r="F88" s="247"/>
+      <c r="G88" s="248"/>
+      <c r="H88" s="99" t="s">
+        <v>49</v>
+      </c>
+      <c r="I88" s="99" t="s">
+        <v>49</v>
+      </c>
+      <c r="J88" s="521" t="s">
+        <v>49</v>
+      </c>
+      <c r="K88" s="522"/>
+      <c r="L88" s="99" t="s">
+        <v>49</v>
+      </c>
+      <c r="M88" s="99" t="s">
+        <v>84</v>
+      </c>
+      <c r="N88" s="64"/>
+    </row>
+    <row r="89" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="250"/>
+      <c r="B89" s="251"/>
+      <c r="C89" s="251"/>
+      <c r="D89" s="509"/>
+      <c r="E89" s="229"/>
+      <c r="F89" s="230"/>
+      <c r="G89" s="231"/>
+      <c r="H89" s="146"/>
+      <c r="I89" s="146"/>
+      <c r="J89" s="517"/>
+      <c r="K89" s="518"/>
+      <c r="L89" s="146"/>
+      <c r="M89" s="146"/>
+      <c r="N89" s="90"/>
+    </row>
+    <row r="90" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A90" s="244" t="s">
+        <v>85</v>
+      </c>
+      <c r="B90" s="245"/>
+      <c r="C90" s="245"/>
+      <c r="D90" s="421"/>
+      <c r="E90" s="246" t="s">
+        <v>86</v>
+      </c>
+      <c r="F90" s="247"/>
+      <c r="G90" s="248"/>
+      <c r="H90" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="I90" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="J90" s="249" t="s">
+        <v>181</v>
+      </c>
+      <c r="K90" s="248"/>
+      <c r="L90" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="M90" s="12"/>
+      <c r="N90" s="145"/>
+    </row>
+    <row r="91" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="250"/>
+      <c r="B91" s="251"/>
+      <c r="C91" s="251"/>
+      <c r="D91" s="509"/>
+      <c r="E91" s="513" t="s">
+        <v>87</v>
+      </c>
+      <c r="F91" s="514"/>
+      <c r="G91" s="300"/>
+      <c r="H91" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="I91" s="6"/>
+      <c r="J91" s="350"/>
+      <c r="K91" s="231"/>
+      <c r="L91" s="6"/>
+      <c r="M91" s="6"/>
+      <c r="N91" s="70"/>
+    </row>
+    <row r="92" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="262" t="s">
+        <v>88</v>
+      </c>
+      <c r="B92" s="263"/>
+      <c r="C92" s="263"/>
+      <c r="D92" s="264"/>
+      <c r="E92" s="265" t="s">
+        <v>39</v>
+      </c>
+      <c r="F92" s="266"/>
+      <c r="G92" s="267"/>
+      <c r="H92" s="101" t="s">
+        <v>39</v>
+      </c>
+      <c r="I92" s="101"/>
+      <c r="J92" s="268" t="s">
+        <v>39</v>
+      </c>
+      <c r="K92" s="269"/>
+      <c r="L92" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="M92" s="192"/>
+      <c r="N92" s="102"/>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A93" s="244" t="s">
+        <v>90</v>
+      </c>
+      <c r="B93" s="245"/>
+      <c r="C93" s="245"/>
+      <c r="D93" s="421"/>
+      <c r="E93" s="515" t="s">
+        <v>91</v>
+      </c>
+      <c r="F93" s="516"/>
+      <c r="G93" s="298"/>
+      <c r="H93" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="I93" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="J93" s="297" t="s">
+        <v>91</v>
+      </c>
+      <c r="K93" s="298"/>
+      <c r="L93" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="M93" s="12"/>
+      <c r="N93" s="104"/>
+    </row>
+    <row r="94" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A94" s="506"/>
+      <c r="B94" s="507"/>
+      <c r="C94" s="507"/>
+      <c r="D94" s="508"/>
+      <c r="E94" s="365" t="s">
+        <v>92</v>
+      </c>
+      <c r="F94" s="366"/>
+      <c r="G94" s="367"/>
+      <c r="H94" s="105" t="s">
+        <v>94</v>
+      </c>
+      <c r="I94" s="105" t="s">
+        <v>92</v>
+      </c>
+      <c r="J94" s="368" t="s">
+        <v>817</v>
+      </c>
+      <c r="K94" s="367"/>
+      <c r="L94" s="105" t="s">
+        <v>92</v>
+      </c>
+      <c r="M94" s="6" t="s">
+        <v>818</v>
+      </c>
+      <c r="N94" s="35"/>
+    </row>
+    <row r="95" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A95" s="506"/>
+      <c r="B95" s="507"/>
+      <c r="C95" s="507"/>
+      <c r="D95" s="508"/>
+      <c r="E95" s="510" t="s">
+        <v>93</v>
+      </c>
+      <c r="F95" s="511"/>
+      <c r="G95" s="512"/>
+      <c r="H95" s="34"/>
+      <c r="I95" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="J95" s="368"/>
+      <c r="K95" s="367"/>
+      <c r="L95" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="M95" s="107"/>
+      <c r="N95" s="108"/>
+    </row>
+    <row r="96" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="250"/>
+      <c r="B96" s="251"/>
+      <c r="C96" s="251"/>
+      <c r="D96" s="509"/>
+      <c r="E96" s="513"/>
+      <c r="F96" s="514"/>
+      <c r="G96" s="300"/>
+      <c r="H96" s="69"/>
+      <c r="I96" s="68"/>
+      <c r="J96" s="350"/>
+      <c r="K96" s="231"/>
+      <c r="L96" s="87" t="s">
+        <v>94</v>
+      </c>
+      <c r="M96" s="87"/>
+      <c r="N96" s="70"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A97" s="244" t="s">
+        <v>96</v>
+      </c>
+      <c r="B97" s="245"/>
+      <c r="C97" s="245"/>
+      <c r="D97" s="421"/>
+      <c r="E97" s="246"/>
+      <c r="F97" s="247"/>
+      <c r="G97" s="248"/>
+      <c r="H97" s="71"/>
+      <c r="I97" s="3"/>
+      <c r="J97" s="249"/>
+      <c r="K97" s="248"/>
+      <c r="L97" s="28"/>
+      <c r="M97" s="28"/>
+      <c r="N97" s="29"/>
+    </row>
+    <row r="98" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="250"/>
+      <c r="B98" s="251"/>
+      <c r="C98" s="251"/>
+      <c r="D98" s="509"/>
+      <c r="E98" s="229" t="s">
+        <v>18</v>
+      </c>
+      <c r="F98" s="230"/>
+      <c r="G98" s="231"/>
+      <c r="H98" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I98" s="9"/>
+      <c r="J98" s="350"/>
+      <c r="K98" s="231"/>
+      <c r="L98" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M98" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="N98" s="109"/>
+    </row>
+    <row r="99" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="262" t="s">
+        <v>97</v>
+      </c>
+      <c r="B99" s="263"/>
+      <c r="C99" s="263"/>
+      <c r="D99" s="264"/>
+      <c r="E99" s="361" t="s">
+        <v>39</v>
+      </c>
+      <c r="F99" s="362"/>
+      <c r="G99" s="269"/>
+      <c r="H99" s="110" t="s">
+        <v>39</v>
+      </c>
+      <c r="I99" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="J99" s="268" t="s">
+        <v>39</v>
+      </c>
+      <c r="K99" s="269"/>
+      <c r="L99" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M99" s="19"/>
+      <c r="N99" s="111"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A100" s="244" t="s">
+        <v>98</v>
+      </c>
+      <c r="B100" s="245"/>
+      <c r="C100" s="245"/>
+      <c r="D100" s="421"/>
+      <c r="E100" s="412" t="s">
+        <v>47</v>
+      </c>
+      <c r="F100" s="413"/>
+      <c r="G100" s="414"/>
+      <c r="H100" s="198" t="s">
+        <v>47</v>
+      </c>
+      <c r="I100" s="198" t="s">
+        <v>47</v>
+      </c>
+      <c r="J100" s="503" t="s">
+        <v>47</v>
+      </c>
+      <c r="K100" s="504"/>
+      <c r="L100" s="198" t="s">
+        <v>47</v>
+      </c>
+      <c r="M100" s="133" t="s">
+        <v>47</v>
+      </c>
+      <c r="N100" s="112"/>
+    </row>
+    <row r="101" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="227"/>
+      <c r="B101" s="228"/>
+      <c r="C101" s="228"/>
+      <c r="D101" s="386"/>
+      <c r="E101" s="229"/>
+      <c r="F101" s="230"/>
+      <c r="G101" s="231"/>
+      <c r="H101" s="159"/>
+      <c r="I101" s="68"/>
+      <c r="J101" s="472"/>
+      <c r="K101" s="473"/>
+      <c r="L101" s="68"/>
+      <c r="M101" s="6"/>
+      <c r="N101" s="166"/>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A102" s="244" t="s">
+        <v>101</v>
+      </c>
+      <c r="B102" s="245"/>
+      <c r="C102" s="245"/>
+      <c r="D102" s="421"/>
+      <c r="E102" s="246"/>
+      <c r="F102" s="247"/>
+      <c r="G102" s="248"/>
+      <c r="H102" s="48"/>
+      <c r="I102" s="48"/>
+      <c r="J102" s="249"/>
+      <c r="K102" s="248"/>
+      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
+      <c r="N102" s="59"/>
+    </row>
+    <row r="103" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A103" s="506"/>
+      <c r="B103" s="507"/>
+      <c r="C103" s="507"/>
+      <c r="D103" s="508"/>
+      <c r="E103" s="365" t="s">
+        <v>832</v>
+      </c>
+      <c r="F103" s="366"/>
+      <c r="G103" s="367"/>
+      <c r="H103" s="32" t="s">
+        <v>663</v>
+      </c>
+      <c r="I103" s="32"/>
+      <c r="J103" s="368" t="s">
+        <v>822</v>
+      </c>
+      <c r="K103" s="367"/>
+      <c r="L103" s="32" t="s">
+        <v>663</v>
+      </c>
+      <c r="M103" s="32"/>
+      <c r="N103" s="33"/>
+    </row>
+    <row r="104" spans="1:14" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="250"/>
+      <c r="B104" s="251"/>
+      <c r="C104" s="251"/>
+      <c r="D104" s="509"/>
+      <c r="E104" s="229" t="s">
+        <v>820</v>
+      </c>
+      <c r="F104" s="230"/>
+      <c r="G104" s="231"/>
+      <c r="H104" s="6" t="s">
+        <v>821</v>
+      </c>
+      <c r="I104" s="6" t="s">
+        <v>821</v>
+      </c>
+      <c r="J104" s="350" t="s">
+        <v>825</v>
+      </c>
+      <c r="K104" s="231"/>
+      <c r="L104" s="6"/>
+      <c r="M104" s="6"/>
+      <c r="N104" s="70"/>
+    </row>
+    <row r="105" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A105" s="209" t="s">
+        <v>103</v>
+      </c>
+      <c r="B105" s="210"/>
+      <c r="C105" s="210"/>
+      <c r="D105" s="210"/>
+      <c r="E105" s="211"/>
+      <c r="F105" s="212"/>
+      <c r="G105" s="212"/>
+      <c r="H105" s="47"/>
+      <c r="I105" s="113"/>
+      <c r="J105" s="237"/>
+      <c r="K105" s="237"/>
+      <c r="L105" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M105" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N105" s="8"/>
+    </row>
+    <row r="106" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="213"/>
+      <c r="B106" s="214"/>
+      <c r="C106" s="214"/>
+      <c r="D106" s="214"/>
+      <c r="E106" s="252"/>
+      <c r="F106" s="232"/>
+      <c r="G106" s="232"/>
+      <c r="H106" s="50"/>
+      <c r="I106" s="132" t="s">
+        <v>16</v>
+      </c>
+      <c r="J106" s="232"/>
+      <c r="K106" s="232"/>
+      <c r="L106" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M106" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N106" s="16"/>
+    </row>
+    <row r="108" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="109" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="200" t="s">
+        <v>104</v>
+      </c>
+      <c r="B109" s="201"/>
+      <c r="C109" s="201"/>
+      <c r="D109" s="201"/>
+      <c r="E109" s="202" t="s">
+        <v>105</v>
+      </c>
+      <c r="F109" s="203"/>
+      <c r="G109" s="204"/>
+      <c r="H109" s="116" t="s">
+        <v>105</v>
+      </c>
+      <c r="I109" s="116" t="s">
+        <v>105</v>
+      </c>
+      <c r="J109" s="202" t="s">
+        <v>105</v>
+      </c>
+      <c r="K109" s="204"/>
+      <c r="L109" s="116" t="s">
+        <v>105</v>
+      </c>
+      <c r="M109" s="117"/>
+      <c r="N109" s="118"/>
+    </row>
+    <row r="110" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="205" t="s">
+        <v>106</v>
+      </c>
+      <c r="B110" s="206"/>
+      <c r="C110" s="206"/>
+      <c r="D110" s="207"/>
+      <c r="E110" s="208" t="s">
+        <v>107</v>
+      </c>
+      <c r="F110" s="203"/>
+      <c r="G110" s="204"/>
+      <c r="H110" s="119" t="s">
+        <v>107</v>
+      </c>
+      <c r="I110" s="119"/>
+      <c r="J110" s="208" t="s">
+        <v>107</v>
+      </c>
+      <c r="K110" s="204"/>
+      <c r="L110" s="119" t="s">
+        <v>107</v>
+      </c>
+      <c r="M110" s="117"/>
+      <c r="N110" s="118"/>
+    </row>
+  </sheetData>
+  <mergeCells count="324">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="E52:G52"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="J57:K57"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="J62:K62"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="E60:G60"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="E65:G65"/>
+    <mergeCell ref="J65:K65"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="E66:G66"/>
+    <mergeCell ref="J66:K66"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="J63:K63"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="J64:K64"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="J69:K69"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="E70:G70"/>
+    <mergeCell ref="J70:K70"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="E67:G67"/>
+    <mergeCell ref="J67:K67"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="E68:G68"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="E75:G75"/>
+    <mergeCell ref="J75:K75"/>
+    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="E76:G76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="J73:K73"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="E79:G79"/>
+    <mergeCell ref="J79:K79"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="E80:G80"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="E78:G78"/>
+    <mergeCell ref="J78:K78"/>
+    <mergeCell ref="A83:D83"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="E84:G84"/>
+    <mergeCell ref="J84:K84"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="E81:G81"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="A82:D82"/>
+    <mergeCell ref="E82:G82"/>
+    <mergeCell ref="J82:K82"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="E87:G87"/>
+    <mergeCell ref="J87:K87"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="E88:G88"/>
+    <mergeCell ref="J88:K88"/>
+    <mergeCell ref="A85:D85"/>
+    <mergeCell ref="E85:G85"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="A86:D86"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="A91:D91"/>
+    <mergeCell ref="E91:G91"/>
+    <mergeCell ref="J91:K91"/>
+    <mergeCell ref="A92:D92"/>
+    <mergeCell ref="E92:G92"/>
+    <mergeCell ref="J92:K92"/>
+    <mergeCell ref="A89:D89"/>
+    <mergeCell ref="E89:G89"/>
+    <mergeCell ref="J89:K89"/>
+    <mergeCell ref="A90:D90"/>
+    <mergeCell ref="E90:G90"/>
+    <mergeCell ref="J90:K90"/>
+    <mergeCell ref="A95:D95"/>
+    <mergeCell ref="E95:G95"/>
+    <mergeCell ref="J95:K95"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="E96:G96"/>
+    <mergeCell ref="J96:K96"/>
+    <mergeCell ref="A93:D93"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="J93:K93"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="E94:G94"/>
+    <mergeCell ref="J94:K94"/>
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="E100:G100"/>
+    <mergeCell ref="J100:K100"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="E97:G97"/>
+    <mergeCell ref="J97:K97"/>
+    <mergeCell ref="A98:D98"/>
+    <mergeCell ref="E98:G98"/>
+    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="A110:D110"/>
+    <mergeCell ref="E110:G110"/>
+    <mergeCell ref="J110:K110"/>
+    <mergeCell ref="A105:D105"/>
+    <mergeCell ref="E105:G105"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="A106:D106"/>
+    <mergeCell ref="E106:G106"/>
+    <mergeCell ref="J106:K106"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="E71:G71"/>
+    <mergeCell ref="E72:G72"/>
+    <mergeCell ref="J71:K71"/>
+    <mergeCell ref="J72:K72"/>
+    <mergeCell ref="A109:D109"/>
+    <mergeCell ref="E109:G109"/>
+    <mergeCell ref="J109:K109"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="E103:G103"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="A104:D104"/>
+    <mergeCell ref="E104:G104"/>
+    <mergeCell ref="J104:K104"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="E101:G101"/>
+    <mergeCell ref="J101:K101"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="E102:G102"/>
+    <mergeCell ref="J102:K102"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="E99:G99"/>
+    <mergeCell ref="J99:K99"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E8CC0A6-04D1-4654-B7BA-A41959CEFC83}">
   <dimension ref="A1:N98"/>
